--- a/Community_Testing_Credentials.xlsx
+++ b/Community_Testing_Credentials.xlsx
@@ -429,7 +429,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Admin / Staff</v>
+        <v>Community Admin</v>
       </c>
       <c r="B2" t="str">
         <v>Community Admin</v>
@@ -507,7 +507,7 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Tenant</v>
+        <v>Resident Tenant</v>
       </c>
       <c r="B5" t="str">
         <v>Rahul Mehta (Tenant 1)</v>
@@ -533,7 +533,7 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Tenant</v>
+        <v>Resident Tenant</v>
       </c>
       <c r="B6" t="str">
         <v>Aisha Khan (Tenant 2)</v>
@@ -750,7 +750,7 @@
         <v>SCEN-003</v>
       </c>
       <c r="B4" t="str">
-        <v>Tenant (tenant1)</v>
+        <v>Resident Tenant (tenant1)</v>
       </c>
       <c r="C4" t="str">
         <v>Outstanding Balance &amp; Pay Now Trigger</v>

--- a/Community_Testing_Credentials.xlsx
+++ b/Community_Testing_Credentials.xlsx
@@ -3,9 +3,13 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="User Credentials" sheetId="1" r:id="rId1"/>
-    <sheet name="Villas &amp; Units" sheetId="2" r:id="rId2"/>
-    <sheet name="Testing Scenarios" sheetId="3" r:id="rId3"/>
+    <sheet name="Master Credentials" sheetId="1" r:id="rId1"/>
+    <sheet name="Greenfield Credentials" sheetId="2" r:id="rId2"/>
+    <sheet name="Sunrise Credentials" sheetId="3" r:id="rId3"/>
+    <sheet name="Palm Credentials" sheetId="4" r:id="rId4"/>
+    <sheet name="Roles &amp; Access Matrix" sheetId="5" r:id="rId5"/>
+    <sheet name="Testing Scenarios" sheetId="6" r:id="rId6"/>
+    <sheet name="Seed Summary" sheetId="7" r:id="rId7"/>
   </sheets>
 </workbook>
 </file>
@@ -399,316 +403,4912 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:K67"/>
+  <cols>
+    <col min="1" max="1" width="6.83203125" customWidth="1"/>
+    <col min="2" max="2" width="28.83203125" customWidth="1"/>
+    <col min="3" max="3" width="18.83203125" customWidth="1"/>
+    <col min="4" max="4" width="22.83203125" customWidth="1"/>
+    <col min="5" max="5" width="30.83203125" customWidth="1"/>
+    <col min="6" max="6" width="18.83203125" customWidth="1"/>
+    <col min="7" max="7" width="20.83203125" customWidth="1"/>
+    <col min="8" max="8" width="16.83203125" customWidth="1"/>
+    <col min="9" max="9" width="16.83203125" customWidth="1"/>
+    <col min="10" max="10" width="10.83203125" customWidth="1"/>
+    <col min="11" max="11" width="60.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>Role / Type</v>
+        <v>S.No</v>
       </c>
       <c r="B1" t="str">
-        <v>Name</v>
+        <v>Community Name</v>
       </c>
       <c r="C1" t="str">
+        <v>Role / Category</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Full Name</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Email / Login</v>
+      </c>
+      <c r="F1" t="str">
+        <v>Password</v>
+      </c>
+      <c r="G1" t="str">
         <v>Username</v>
       </c>
-      <c r="D1" t="str">
-        <v>Email</v>
-      </c>
-      <c r="E1" t="str">
-        <v>Password</v>
-      </c>
-      <c r="F1" t="str">
+      <c r="H1" t="str">
+        <v>Phone</v>
+      </c>
+      <c r="I1" t="str">
         <v>Assigned Unit</v>
       </c>
-      <c r="G1" t="str">
-        <v>Residency Type</v>
-      </c>
-      <c r="H1" t="str">
-        <v>Testing Context</v>
+      <c r="J1" t="str">
+        <v>Status</v>
+      </c>
+      <c r="K1" t="str">
+        <v>Key Testing Focus</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="str">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="str">
+        <v>PLATFORM GLOBAL</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Super Admin</v>
+      </c>
+      <c r="D2" t="str">
+        <v>Super Admin</v>
+      </c>
+      <c r="E2" t="str">
+        <v>admin@enterprise.com</v>
+      </c>
+      <c r="F2" t="str">
+        <v>SuperAdminPwd@123</v>
+      </c>
+      <c r="G2" t="str">
+        <v>superadmin</v>
+      </c>
+      <c r="H2" t="str">
+        <v>+919900000000</v>
+      </c>
+      <c r="I2" t="str">
+        <v>All / Platform</v>
+      </c>
+      <c r="J2" t="str">
+        <v>Active</v>
+      </c>
+      <c r="K2" t="str">
+        <v>Global administration, community creation, system configuration.</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Greenfield Heights Community</v>
+      </c>
+      <c r="C3" t="str">
         <v>Community Admin</v>
       </c>
-      <c r="B2" t="str">
+      <c r="D3" t="str">
+        <v>Rohit Bose</v>
+      </c>
+      <c r="E3" t="str">
+        <v>admin1@greenfield.com</v>
+      </c>
+      <c r="F3" t="str">
+        <v>Test@1234</v>
+      </c>
+      <c r="G3" t="str">
+        <v>admin1_greenfield</v>
+      </c>
+      <c r="H3" t="str">
+        <v>+9198101000</v>
+      </c>
+      <c r="I3" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="J3" t="str">
+        <v>Active</v>
+      </c>
+      <c r="K3" t="str">
+        <v>Full Admin controls, user setup, billing, complaints assignment, notice publishing.</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Greenfield Heights Community</v>
+      </c>
+      <c r="C4" t="str">
         <v>Community Admin</v>
       </c>
-      <c r="C2" t="str">
-        <v>admin</v>
-      </c>
-      <c r="D2" t="str">
-        <v>admin@mygate.com</v>
-      </c>
-      <c r="E2" t="str">
-        <v>Password@123</v>
-      </c>
-      <c r="F2" t="str">
+      <c r="D4" t="str">
+        <v>Harish Kumar</v>
+      </c>
+      <c r="E4" t="str">
+        <v>admin2@greenfield.com</v>
+      </c>
+      <c r="F4" t="str">
+        <v>Test@1234</v>
+      </c>
+      <c r="G4" t="str">
+        <v>admin2_greenfield</v>
+      </c>
+      <c r="H4" t="str">
+        <v>+9198101001</v>
+      </c>
+      <c r="I4" t="str">
         <v>N/A</v>
       </c>
-      <c r="G2" t="str">
-        <v>None</v>
-      </c>
-      <c r="H2" t="str">
-        <v>Manage assessments, view ledger, verify offline cheque payments.</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
+      <c r="J4" t="str">
+        <v>Active</v>
+      </c>
+      <c r="K4" t="str">
+        <v>Full Admin controls, user setup, billing, complaints assignment, notice publishing.</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Greenfield Heights Community</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Facility Manager</v>
+      </c>
+      <c r="D5" t="str">
+        <v>Sanjay Kapoor</v>
+      </c>
+      <c r="E5" t="str">
+        <v>fm1@greenfield.com</v>
+      </c>
+      <c r="F5" t="str">
+        <v>Test@1234</v>
+      </c>
+      <c r="G5" t="str">
+        <v>fm1_greenfield</v>
+      </c>
+      <c r="H5" t="str">
+        <v>+9198101002</v>
+      </c>
+      <c r="I5" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="J5" t="str">
+        <v>Active</v>
+      </c>
+      <c r="K5" t="str">
+        <v>Amenity scheduling, maintenance slots, ticket updates, facility inspection.</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Greenfield Heights Community</v>
+      </c>
+      <c r="C6" t="str">
+        <v>Facility Manager</v>
+      </c>
+      <c r="D6" t="str">
+        <v>Zara Sharma</v>
+      </c>
+      <c r="E6" t="str">
+        <v>fm2@greenfield.com</v>
+      </c>
+      <c r="F6" t="str">
+        <v>Test@1234</v>
+      </c>
+      <c r="G6" t="str">
+        <v>fm2_greenfield</v>
+      </c>
+      <c r="H6" t="str">
+        <v>+9198101003</v>
+      </c>
+      <c r="I6" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="J6" t="str">
+        <v>Active</v>
+      </c>
+      <c r="K6" t="str">
+        <v>Amenity scheduling, maintenance slots, ticket updates, facility inspection.</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="str">
+        <v>Greenfield Heights Community</v>
+      </c>
+      <c r="C7" t="str">
+        <v>Security Guard</v>
+      </c>
+      <c r="D7" t="str">
+        <v>Vikram Mehta</v>
+      </c>
+      <c r="E7" t="str">
+        <v>guard1@greenfield.com</v>
+      </c>
+      <c r="F7" t="str">
+        <v>Test@1234</v>
+      </c>
+      <c r="G7" t="str">
+        <v>guard1_greenfield</v>
+      </c>
+      <c r="H7" t="str">
+        <v>+9198101004</v>
+      </c>
+      <c r="I7" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="J7" t="str">
+        <v>Active</v>
+      </c>
+      <c r="K7" t="str">
+        <v>Gate entry/exit scanner, visitor verification, passcode validation.</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Greenfield Heights Community</v>
+      </c>
+      <c r="C8" t="str">
+        <v>Security Guard</v>
+      </c>
+      <c r="D8" t="str">
+        <v>Siddharth Gupta</v>
+      </c>
+      <c r="E8" t="str">
+        <v>guard2@greenfield.com</v>
+      </c>
+      <c r="F8" t="str">
+        <v>Test@1234</v>
+      </c>
+      <c r="G8" t="str">
+        <v>guard2_greenfield</v>
+      </c>
+      <c r="H8" t="str">
+        <v>+9198101005</v>
+      </c>
+      <c r="I8" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="J8" t="str">
+        <v>Active</v>
+      </c>
+      <c r="K8" t="str">
+        <v>Gate entry/exit scanner, visitor verification, passcode validation.</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="str">
+        <v>Greenfield Heights Community</v>
+      </c>
+      <c r="C9" t="str">
         <v>Resident Owner</v>
       </c>
-      <c r="B3" t="str">
-        <v>Rajesh Kumar (Owner 1)</v>
-      </c>
-      <c r="C3" t="str">
-        <v>owner1</v>
-      </c>
-      <c r="D3" t="str">
-        <v>owner1@mygate.com</v>
-      </c>
-      <c r="E3" t="str">
-        <v>Password@123</v>
-      </c>
-      <c r="F3" t="str">
-        <v>Villa A-101</v>
-      </c>
-      <c r="G3" t="str">
+      <c r="D9" t="str">
+        <v>Ishaan Sinha</v>
+      </c>
+      <c r="E9" t="str">
+        <v>owner1@greenfield.com</v>
+      </c>
+      <c r="F9" t="str">
+        <v>Test@1234</v>
+      </c>
+      <c r="G9" t="str">
+        <v>owner1_greenfield</v>
+      </c>
+      <c r="H9" t="str">
+        <v>+9198101006</v>
+      </c>
+      <c r="I9" t="str">
+        <v>A-101</v>
+      </c>
+      <c r="J9" t="str">
+        <v>Active</v>
+      </c>
+      <c r="K9" t="str">
+        <v>Financial dashboard, tenant arrears, visitor pass generation, amenity booking.</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="str">
+        <v>Greenfield Heights Community</v>
+      </c>
+      <c r="C10" t="str">
         <v>Resident Owner</v>
       </c>
-      <c r="H3" t="str">
-        <v>View ₹5,000 outstanding security fund invoice. View Tenant Arrears (Tenant 2 clearing Cheque ₹7,000).</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>Resident Owner (Non-Res)</v>
-      </c>
-      <c r="B4" t="str">
-        <v>Vikram Singh (Owner 2)</v>
-      </c>
-      <c r="C4" t="str">
-        <v>owner2</v>
-      </c>
-      <c r="D4" t="str">
-        <v>owner2@mygate.com</v>
-      </c>
-      <c r="E4" t="str">
-        <v>Password@123</v>
-      </c>
-      <c r="F4" t="str">
-        <v>Villa A-102 (Leased)</v>
-      </c>
-      <c r="G4" t="str">
-        <v>Non-Resident Owner</v>
-      </c>
-      <c r="H4" t="str">
-        <v>View Tenant Arrears (Tenant 1 outstanding Maintenance ₹7,000).</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
+      <c r="D10" t="str">
+        <v>Bhavna Shah</v>
+      </c>
+      <c r="E10" t="str">
+        <v>owner2@greenfield.com</v>
+      </c>
+      <c r="F10" t="str">
+        <v>Test@1234</v>
+      </c>
+      <c r="G10" t="str">
+        <v>owner2_greenfield</v>
+      </c>
+      <c r="H10" t="str">
+        <v>+9198101007</v>
+      </c>
+      <c r="I10" t="str">
+        <v>A-102</v>
+      </c>
+      <c r="J10" t="str">
+        <v>Active</v>
+      </c>
+      <c r="K10" t="str">
+        <v>Financial dashboard, tenant arrears, visitor pass generation, amenity booking.</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="str">
+        <v>Greenfield Heights Community</v>
+      </c>
+      <c r="C11" t="str">
+        <v>Resident Owner</v>
+      </c>
+      <c r="D11" t="str">
+        <v>Aditi Ghosh</v>
+      </c>
+      <c r="E11" t="str">
+        <v>owner3@greenfield.com</v>
+      </c>
+      <c r="F11" t="str">
+        <v>Test@1234</v>
+      </c>
+      <c r="G11" t="str">
+        <v>owner3_greenfield</v>
+      </c>
+      <c r="H11" t="str">
+        <v>+9198101008</v>
+      </c>
+      <c r="I11" t="str">
+        <v>A-103</v>
+      </c>
+      <c r="J11" t="str">
+        <v>Active</v>
+      </c>
+      <c r="K11" t="str">
+        <v>Financial dashboard, tenant arrears, visitor pass generation, amenity booking.</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="str">
+        <v>Greenfield Heights Community</v>
+      </c>
+      <c r="C12" t="str">
+        <v>Resident Owner</v>
+      </c>
+      <c r="D12" t="str">
+        <v>Rajesh Mehta</v>
+      </c>
+      <c r="E12" t="str">
+        <v>owner4@greenfield.com</v>
+      </c>
+      <c r="F12" t="str">
+        <v>Test@1234</v>
+      </c>
+      <c r="G12" t="str">
+        <v>owner4_greenfield</v>
+      </c>
+      <c r="H12" t="str">
+        <v>+9198101009</v>
+      </c>
+      <c r="I12" t="str">
+        <v>A-104</v>
+      </c>
+      <c r="J12" t="str">
+        <v>Active</v>
+      </c>
+      <c r="K12" t="str">
+        <v>Financial dashboard, tenant arrears, visitor pass generation, amenity booking.</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" t="str">
+        <v>Greenfield Heights Community</v>
+      </c>
+      <c r="C13" t="str">
+        <v>Resident Owner</v>
+      </c>
+      <c r="D13" t="str">
+        <v>Siddharth Iyer</v>
+      </c>
+      <c r="E13" t="str">
+        <v>owner5@greenfield.com</v>
+      </c>
+      <c r="F13" t="str">
+        <v>Test@1234</v>
+      </c>
+      <c r="G13" t="str">
+        <v>owner5_greenfield</v>
+      </c>
+      <c r="H13" t="str">
+        <v>+9198101010</v>
+      </c>
+      <c r="I13" t="str">
+        <v>A-105</v>
+      </c>
+      <c r="J13" t="str">
+        <v>Active</v>
+      </c>
+      <c r="K13" t="str">
+        <v>Financial dashboard, tenant arrears, visitor pass generation, amenity booking.</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" t="str">
+        <v>Greenfield Heights Community</v>
+      </c>
+      <c r="C14" t="str">
+        <v>Resident Owner</v>
+      </c>
+      <c r="D14" t="str">
+        <v>Rahul Patel</v>
+      </c>
+      <c r="E14" t="str">
+        <v>owner6@greenfield.com</v>
+      </c>
+      <c r="F14" t="str">
+        <v>Test@1234</v>
+      </c>
+      <c r="G14" t="str">
+        <v>owner6_greenfield</v>
+      </c>
+      <c r="H14" t="str">
+        <v>+9198101011</v>
+      </c>
+      <c r="I14" t="str">
+        <v>A-106</v>
+      </c>
+      <c r="J14" t="str">
+        <v>Active</v>
+      </c>
+      <c r="K14" t="str">
+        <v>Financial dashboard, tenant arrears, visitor pass generation, amenity booking.</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" t="str">
+        <v>Greenfield Heights Community</v>
+      </c>
+      <c r="C15" t="str">
+        <v>Resident Owner</v>
+      </c>
+      <c r="D15" t="str">
+        <v>Priya Verma</v>
+      </c>
+      <c r="E15" t="str">
+        <v>owner7@greenfield.com</v>
+      </c>
+      <c r="F15" t="str">
+        <v>Test@1234</v>
+      </c>
+      <c r="G15" t="str">
+        <v>owner7_greenfield</v>
+      </c>
+      <c r="H15" t="str">
+        <v>+9198101012</v>
+      </c>
+      <c r="I15" t="str">
+        <v>A-107</v>
+      </c>
+      <c r="J15" t="str">
+        <v>Active</v>
+      </c>
+      <c r="K15" t="str">
+        <v>Financial dashboard, tenant arrears, visitor pass generation, amenity booking.</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" t="str">
+        <v>Greenfield Heights Community</v>
+      </c>
+      <c r="C16" t="str">
+        <v>Resident Owner</v>
+      </c>
+      <c r="D16" t="str">
+        <v>Tanvi Shah</v>
+      </c>
+      <c r="E16" t="str">
+        <v>owner8@greenfield.com</v>
+      </c>
+      <c r="F16" t="str">
+        <v>Test@1234</v>
+      </c>
+      <c r="G16" t="str">
+        <v>owner8_greenfield</v>
+      </c>
+      <c r="H16" t="str">
+        <v>+9198101013</v>
+      </c>
+      <c r="I16" t="str">
+        <v>A-108</v>
+      </c>
+      <c r="J16" t="str">
+        <v>Active</v>
+      </c>
+      <c r="K16" t="str">
+        <v>Financial dashboard, tenant arrears, visitor pass generation, amenity booking.</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" t="str">
+        <v>Greenfield Heights Community</v>
+      </c>
+      <c r="C17" t="str">
+        <v>Resident Owner</v>
+      </c>
+      <c r="D17" t="str">
+        <v>Jaya Mehta</v>
+      </c>
+      <c r="E17" t="str">
+        <v>owner9@greenfield.com</v>
+      </c>
+      <c r="F17" t="str">
+        <v>Test@1234</v>
+      </c>
+      <c r="G17" t="str">
+        <v>owner9_greenfield</v>
+      </c>
+      <c r="H17" t="str">
+        <v>+9198101014</v>
+      </c>
+      <c r="I17" t="str">
+        <v>A-109</v>
+      </c>
+      <c r="J17" t="str">
+        <v>Active</v>
+      </c>
+      <c r="K17" t="str">
+        <v>Financial dashboard, tenant arrears, visitor pass generation, amenity booking.</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" t="str">
+        <v>Greenfield Heights Community</v>
+      </c>
+      <c r="C18" t="str">
+        <v>Resident Owner</v>
+      </c>
+      <c r="D18" t="str">
+        <v>Sahil Kumar</v>
+      </c>
+      <c r="E18" t="str">
+        <v>owner10@greenfield.com</v>
+      </c>
+      <c r="F18" t="str">
+        <v>Test@1234</v>
+      </c>
+      <c r="G18" t="str">
+        <v>owner10_greenfield</v>
+      </c>
+      <c r="H18" t="str">
+        <v>+9198101015</v>
+      </c>
+      <c r="I18" t="str">
+        <v>A-110</v>
+      </c>
+      <c r="J18" t="str">
+        <v>Active</v>
+      </c>
+      <c r="K18" t="str">
+        <v>Financial dashboard, tenant arrears, visitor pass generation, amenity booking.</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" t="str">
+        <v>Greenfield Heights Community</v>
+      </c>
+      <c r="C19" t="str">
         <v>Resident Tenant</v>
       </c>
-      <c r="B5" t="str">
-        <v>Rahul Mehta (Tenant 1)</v>
-      </c>
-      <c r="C5" t="str">
-        <v>tenant1</v>
-      </c>
-      <c r="D5" t="str">
-        <v>tenant1@mygate.com</v>
-      </c>
-      <c r="E5" t="str">
-        <v>Password@123</v>
-      </c>
-      <c r="F5" t="str">
-        <v>Villa A-102</v>
-      </c>
-      <c r="G5" t="str">
-        <v>Tenant</v>
-      </c>
-      <c r="H5" t="str">
-        <v>View ₹7,000 outstanding maintenance invoice. Submit offline NEFT/Cheque pay ref.</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
+      <c r="D19" t="str">
+        <v>Siddharth Mehta</v>
+      </c>
+      <c r="E19" t="str">
+        <v>tenant1@greenfield.com</v>
+      </c>
+      <c r="F19" t="str">
+        <v>Test@1234</v>
+      </c>
+      <c r="G19" t="str">
+        <v>tenant1_greenfield</v>
+      </c>
+      <c r="H19" t="str">
+        <v>+9198101016</v>
+      </c>
+      <c r="I19" t="str">
+        <v>B-101</v>
+      </c>
+      <c r="J19" t="str">
+        <v>Active</v>
+      </c>
+      <c r="K19" t="str">
+        <v>Raise complaints, pay invoices, book amenities, create guest visitor passes.</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" t="str">
+        <v>Greenfield Heights Community</v>
+      </c>
+      <c r="C20" t="str">
         <v>Resident Tenant</v>
       </c>
-      <c r="B6" t="str">
-        <v>Aisha Khan (Tenant 2)</v>
-      </c>
-      <c r="C6" t="str">
-        <v>tenant2</v>
-      </c>
-      <c r="D6" t="str">
-        <v>tenant2@mygate.com</v>
-      </c>
-      <c r="E6" t="str">
-        <v>Password@123</v>
-      </c>
-      <c r="F6" t="str">
-        <v>Villa B-201</v>
-      </c>
-      <c r="G6" t="str">
-        <v>Tenant</v>
-      </c>
-      <c r="H6" t="str">
-        <v>View ₹7,000 invoice currently in VERIFICATION_PENDING status.</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
+      <c r="D20" t="str">
+        <v>Harish Banerjee</v>
+      </c>
+      <c r="E20" t="str">
+        <v>tenant2@greenfield.com</v>
+      </c>
+      <c r="F20" t="str">
+        <v>Test@1234</v>
+      </c>
+      <c r="G20" t="str">
+        <v>tenant2_greenfield</v>
+      </c>
+      <c r="H20" t="str">
+        <v>+9198101017</v>
+      </c>
+      <c r="I20" t="str">
+        <v>B-102</v>
+      </c>
+      <c r="J20" t="str">
+        <v>Active</v>
+      </c>
+      <c r="K20" t="str">
+        <v>Raise complaints, pay invoices, book amenities, create guest visitor passes.</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" t="str">
+        <v>Greenfield Heights Community</v>
+      </c>
+      <c r="C21" t="str">
+        <v>Resident Tenant</v>
+      </c>
+      <c r="D21" t="str">
+        <v>Chirag Rao</v>
+      </c>
+      <c r="E21" t="str">
+        <v>tenant3@greenfield.com</v>
+      </c>
+      <c r="F21" t="str">
+        <v>Test@1234</v>
+      </c>
+      <c r="G21" t="str">
+        <v>tenant3_greenfield</v>
+      </c>
+      <c r="H21" t="str">
+        <v>+9198101018</v>
+      </c>
+      <c r="I21" t="str">
+        <v>B-103</v>
+      </c>
+      <c r="J21" t="str">
+        <v>Active</v>
+      </c>
+      <c r="K21" t="str">
+        <v>Raise complaints, pay invoices, book amenities, create guest visitor passes.</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22" t="str">
+        <v>Greenfield Heights Community</v>
+      </c>
+      <c r="C22" t="str">
+        <v>Resident Tenant</v>
+      </c>
+      <c r="D22" t="str">
+        <v>Yamini Gupta</v>
+      </c>
+      <c r="E22" t="str">
+        <v>tenant4@greenfield.com</v>
+      </c>
+      <c r="F22" t="str">
+        <v>Test@1234</v>
+      </c>
+      <c r="G22" t="str">
+        <v>tenant4_greenfield</v>
+      </c>
+      <c r="H22" t="str">
+        <v>+9198101019</v>
+      </c>
+      <c r="I22" t="str">
+        <v>B-104</v>
+      </c>
+      <c r="J22" t="str">
+        <v>Active</v>
+      </c>
+      <c r="K22" t="str">
+        <v>Raise complaints, pay invoices, book amenities, create guest visitor passes.</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23" t="str">
+        <v>Greenfield Heights Community</v>
+      </c>
+      <c r="C23" t="str">
+        <v>Resident Tenant</v>
+      </c>
+      <c r="D23" t="str">
+        <v>Rajesh Banerjee</v>
+      </c>
+      <c r="E23" t="str">
+        <v>tenant5@greenfield.com</v>
+      </c>
+      <c r="F23" t="str">
+        <v>Test@1234</v>
+      </c>
+      <c r="G23" t="str">
+        <v>tenant5_greenfield</v>
+      </c>
+      <c r="H23" t="str">
+        <v>+9198101020</v>
+      </c>
+      <c r="I23" t="str">
+        <v>B-105</v>
+      </c>
+      <c r="J23" t="str">
+        <v>Active</v>
+      </c>
+      <c r="K23" t="str">
+        <v>Raise complaints, pay invoices, book amenities, create guest visitor passes.</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24" t="str">
+        <v>Greenfield Heights Community</v>
+      </c>
+      <c r="C24" t="str">
+        <v>Resident Tenant</v>
+      </c>
+      <c r="D24" t="str">
+        <v>Kavya Patel</v>
+      </c>
+      <c r="E24" t="str">
+        <v>tenant6@greenfield.com</v>
+      </c>
+      <c r="F24" t="str">
+        <v>Test@1234</v>
+      </c>
+      <c r="G24" t="str">
+        <v>tenant6_greenfield</v>
+      </c>
+      <c r="H24" t="str">
+        <v>+9198101021</v>
+      </c>
+      <c r="I24" t="str">
+        <v>B-106</v>
+      </c>
+      <c r="J24" t="str">
+        <v>Active</v>
+      </c>
+      <c r="K24" t="str">
+        <v>Raise complaints, pay invoices, book amenities, create guest visitor passes.</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25" t="str">
+        <v>Greenfield Heights Community</v>
+      </c>
+      <c r="C25" t="str">
+        <v>Resident Tenant</v>
+      </c>
+      <c r="D25" t="str">
+        <v>Ananya Banerjee</v>
+      </c>
+      <c r="E25" t="str">
+        <v>tenant7@greenfield.com</v>
+      </c>
+      <c r="F25" t="str">
+        <v>Test@1234</v>
+      </c>
+      <c r="G25" t="str">
+        <v>tenant7_greenfield</v>
+      </c>
+      <c r="H25" t="str">
+        <v>+9198101022</v>
+      </c>
+      <c r="I25" t="str">
+        <v>B-107</v>
+      </c>
+      <c r="J25" t="str">
+        <v>Active</v>
+      </c>
+      <c r="K25" t="str">
+        <v>Raise complaints, pay invoices, book amenities, create guest visitor passes.</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26" t="str">
+        <v>Greenfield Heights Community</v>
+      </c>
+      <c r="C26" t="str">
+        <v>Resident Tenant</v>
+      </c>
+      <c r="D26" t="str">
+        <v>Vinay Banerjee</v>
+      </c>
+      <c r="E26" t="str">
+        <v>tenant8@greenfield.com</v>
+      </c>
+      <c r="F26" t="str">
+        <v>Test@1234</v>
+      </c>
+      <c r="G26" t="str">
+        <v>tenant8_greenfield</v>
+      </c>
+      <c r="H26" t="str">
+        <v>+9198101023</v>
+      </c>
+      <c r="I26" t="str">
+        <v>B-108</v>
+      </c>
+      <c r="J26" t="str">
+        <v>Active</v>
+      </c>
+      <c r="K26" t="str">
+        <v>Raise complaints, pay invoices, book amenities, create guest visitor passes.</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27" t="str">
+        <v>Greenfield Heights Community</v>
+      </c>
+      <c r="C27" t="str">
+        <v>Resident Tenant</v>
+      </c>
+      <c r="D27" t="str">
+        <v>Divya Singh</v>
+      </c>
+      <c r="E27" t="str">
+        <v>tenant9@greenfield.com</v>
+      </c>
+      <c r="F27" t="str">
+        <v>Test@1234</v>
+      </c>
+      <c r="G27" t="str">
+        <v>tenant9_greenfield</v>
+      </c>
+      <c r="H27" t="str">
+        <v>+9198101024</v>
+      </c>
+      <c r="I27" t="str">
+        <v>B-109</v>
+      </c>
+      <c r="J27" t="str">
+        <v>Active</v>
+      </c>
+      <c r="K27" t="str">
+        <v>Raise complaints, pay invoices, book amenities, create guest visitor passes.</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28" t="str">
+        <v>Greenfield Heights Community</v>
+      </c>
+      <c r="C28" t="str">
+        <v>Resident Tenant</v>
+      </c>
+      <c r="D28" t="str">
+        <v>Kavya Bose</v>
+      </c>
+      <c r="E28" t="str">
+        <v>tenant10@greenfield.com</v>
+      </c>
+      <c r="F28" t="str">
+        <v>Test@1234</v>
+      </c>
+      <c r="G28" t="str">
+        <v>tenant10_greenfield</v>
+      </c>
+      <c r="H28" t="str">
+        <v>+9198101025</v>
+      </c>
+      <c r="I28" t="str">
+        <v>B-110</v>
+      </c>
+      <c r="J28" t="str">
+        <v>Active</v>
+      </c>
+      <c r="K28" t="str">
+        <v>Raise complaints, pay invoices, book amenities, create guest visitor passes.</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29" t="str">
+        <v>Greenfield Heights Community</v>
+      </c>
+      <c r="C29" t="str">
+        <v>Family Member</v>
+      </c>
+      <c r="D29" t="str">
+        <v>Farhan Pandey</v>
+      </c>
+      <c r="E29" t="str">
+        <v>family1@greenfield.com</v>
+      </c>
+      <c r="F29" t="str">
+        <v>Test@1234</v>
+      </c>
+      <c r="G29" t="str">
+        <v>family1_greenfield</v>
+      </c>
+      <c r="H29" t="str">
+        <v>+9198101026</v>
+      </c>
+      <c r="I29" t="str">
+        <v>A-101</v>
+      </c>
+      <c r="J29" t="str">
+        <v>Active</v>
+      </c>
+      <c r="K29" t="str">
+        <v>View notices, view community events, raise quick complaints.</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30" t="str">
+        <v>Greenfield Heights Community</v>
+      </c>
+      <c r="C30" t="str">
+        <v>Family Member</v>
+      </c>
+      <c r="D30" t="str">
+        <v>Varun Ghosh</v>
+      </c>
+      <c r="E30" t="str">
+        <v>family2@greenfield.com</v>
+      </c>
+      <c r="F30" t="str">
+        <v>Test@1234</v>
+      </c>
+      <c r="G30" t="str">
+        <v>family2_greenfield</v>
+      </c>
+      <c r="H30" t="str">
+        <v>+9198101027</v>
+      </c>
+      <c r="I30" t="str">
+        <v>A-102</v>
+      </c>
+      <c r="J30" t="str">
+        <v>Active</v>
+      </c>
+      <c r="K30" t="str">
+        <v>View notices, view community events, raise quick complaints.</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="B31" t="str">
+        <v>Greenfield Heights Community</v>
+      </c>
+      <c r="C31" t="str">
+        <v>Family Member</v>
+      </c>
+      <c r="D31" t="str">
+        <v>Nisha Rao</v>
+      </c>
+      <c r="E31" t="str">
+        <v>family3@greenfield.com</v>
+      </c>
+      <c r="F31" t="str">
+        <v>Test@1234</v>
+      </c>
+      <c r="G31" t="str">
+        <v>family3_greenfield</v>
+      </c>
+      <c r="H31" t="str">
+        <v>+9198101028</v>
+      </c>
+      <c r="I31" t="str">
+        <v>A-103</v>
+      </c>
+      <c r="J31" t="str">
+        <v>Active</v>
+      </c>
+      <c r="K31" t="str">
+        <v>View notices, view community events, raise quick complaints.</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>31</v>
+      </c>
+      <c r="B32" t="str">
+        <v>Greenfield Heights Community</v>
+      </c>
+      <c r="C32" t="str">
+        <v>Family Member</v>
+      </c>
+      <c r="D32" t="str">
+        <v>Rajesh Nair</v>
+      </c>
+      <c r="E32" t="str">
+        <v>family4@greenfield.com</v>
+      </c>
+      <c r="F32" t="str">
+        <v>Test@1234</v>
+      </c>
+      <c r="G32" t="str">
+        <v>family4_greenfield</v>
+      </c>
+      <c r="H32" t="str">
+        <v>+9198101029</v>
+      </c>
+      <c r="I32" t="str">
+        <v>A-104</v>
+      </c>
+      <c r="J32" t="str">
+        <v>Active</v>
+      </c>
+      <c r="K32" t="str">
+        <v>View notices, view community events, raise quick complaints.</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>32</v>
+      </c>
+      <c r="B33" t="str">
+        <v>Sunrise Valley Estates</v>
+      </c>
+      <c r="C33" t="str">
+        <v>Community Admin</v>
+      </c>
+      <c r="D33" t="str">
+        <v>Varun Pandey</v>
+      </c>
+      <c r="E33" t="str">
+        <v>admin1@sunrisevalley.com</v>
+      </c>
+      <c r="F33" t="str">
+        <v>Test@1234</v>
+      </c>
+      <c r="G33" t="str">
+        <v>admin1_sunrise</v>
+      </c>
+      <c r="H33" t="str">
+        <v>+9198201000</v>
+      </c>
+      <c r="I33" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="J33" t="str">
+        <v>Active</v>
+      </c>
+      <c r="K33" t="str">
+        <v>Full Admin controls, user setup, billing, complaints assignment, notice publishing.</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>33</v>
+      </c>
+      <c r="B34" t="str">
+        <v>Sunrise Valley Estates</v>
+      </c>
+      <c r="C34" t="str">
+        <v>Facility Manager</v>
+      </c>
+      <c r="D34" t="str">
+        <v>Neeraj Kapoor</v>
+      </c>
+      <c r="E34" t="str">
+        <v>fm1@sunrisevalley.com</v>
+      </c>
+      <c r="F34" t="str">
+        <v>Test@1234</v>
+      </c>
+      <c r="G34" t="str">
+        <v>fm1_sunrise</v>
+      </c>
+      <c r="H34" t="str">
+        <v>+9198201001</v>
+      </c>
+      <c r="I34" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="J34" t="str">
+        <v>Active</v>
+      </c>
+      <c r="K34" t="str">
+        <v>Amenity scheduling, maintenance slots, ticket updates, facility inspection.</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>34</v>
+      </c>
+      <c r="B35" t="str">
+        <v>Sunrise Valley Estates</v>
+      </c>
+      <c r="C35" t="str">
         <v>Security Guard</v>
       </c>
-      <c r="B7" t="str">
-        <v>Bahadur Singh (Guard 1)</v>
-      </c>
-      <c r="C7" t="str">
-        <v>guard1</v>
-      </c>
-      <c r="D7" t="str">
-        <v>guard1@mygate.com</v>
-      </c>
-      <c r="E7" t="str">
-        <v>Password@123</v>
-      </c>
-      <c r="F7" t="str">
-        <v>Gate Entrance</v>
-      </c>
-      <c r="G7" t="str">
-        <v>None</v>
-      </c>
-      <c r="H7" t="str">
-        <v>Gate checkpoint control (visitor scanner, log book).</v>
+      <c r="D35" t="str">
+        <v>Farhan Choudhury</v>
+      </c>
+      <c r="E35" t="str">
+        <v>guard1@sunrisevalley.com</v>
+      </c>
+      <c r="F35" t="str">
+        <v>Test@1234</v>
+      </c>
+      <c r="G35" t="str">
+        <v>guard1_sunrise</v>
+      </c>
+      <c r="H35" t="str">
+        <v>+9198201002</v>
+      </c>
+      <c r="I35" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="J35" t="str">
+        <v>Active</v>
+      </c>
+      <c r="K35" t="str">
+        <v>Gate entry/exit scanner, visitor verification, passcode validation.</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>35</v>
+      </c>
+      <c r="B36" t="str">
+        <v>Sunrise Valley Estates</v>
+      </c>
+      <c r="C36" t="str">
+        <v>Security Guard</v>
+      </c>
+      <c r="D36" t="str">
+        <v>Dev Mishra</v>
+      </c>
+      <c r="E36" t="str">
+        <v>guard2@sunrisevalley.com</v>
+      </c>
+      <c r="F36" t="str">
+        <v>Test@1234</v>
+      </c>
+      <c r="G36" t="str">
+        <v>guard2_sunrise</v>
+      </c>
+      <c r="H36" t="str">
+        <v>+9198201003</v>
+      </c>
+      <c r="I36" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="J36" t="str">
+        <v>Active</v>
+      </c>
+      <c r="K36" t="str">
+        <v>Gate entry/exit scanner, visitor verification, passcode validation.</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>36</v>
+      </c>
+      <c r="B37" t="str">
+        <v>Sunrise Valley Estates</v>
+      </c>
+      <c r="C37" t="str">
+        <v>Resident Owner</v>
+      </c>
+      <c r="D37" t="str">
+        <v>Dev Singh</v>
+      </c>
+      <c r="E37" t="str">
+        <v>owner1@sunrisevalley.com</v>
+      </c>
+      <c r="F37" t="str">
+        <v>Test@1234</v>
+      </c>
+      <c r="G37" t="str">
+        <v>owner1_sunrise</v>
+      </c>
+      <c r="H37" t="str">
+        <v>+9198201004</v>
+      </c>
+      <c r="I37" t="str">
+        <v>P1-01</v>
+      </c>
+      <c r="J37" t="str">
+        <v>Active</v>
+      </c>
+      <c r="K37" t="str">
+        <v>Financial dashboard, tenant arrears, visitor pass generation, amenity booking.</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>37</v>
+      </c>
+      <c r="B38" t="str">
+        <v>Sunrise Valley Estates</v>
+      </c>
+      <c r="C38" t="str">
+        <v>Resident Owner</v>
+      </c>
+      <c r="D38" t="str">
+        <v>Sahil Agarwal</v>
+      </c>
+      <c r="E38" t="str">
+        <v>owner2@sunrisevalley.com</v>
+      </c>
+      <c r="F38" t="str">
+        <v>Test@1234</v>
+      </c>
+      <c r="G38" t="str">
+        <v>owner2_sunrise</v>
+      </c>
+      <c r="H38" t="str">
+        <v>+9198201005</v>
+      </c>
+      <c r="I38" t="str">
+        <v>P1-02</v>
+      </c>
+      <c r="J38" t="str">
+        <v>Active</v>
+      </c>
+      <c r="K38" t="str">
+        <v>Financial dashboard, tenant arrears, visitor pass generation, amenity booking.</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>38</v>
+      </c>
+      <c r="B39" t="str">
+        <v>Sunrise Valley Estates</v>
+      </c>
+      <c r="C39" t="str">
+        <v>Resident Owner</v>
+      </c>
+      <c r="D39" t="str">
+        <v>Vinay Agarwal</v>
+      </c>
+      <c r="E39" t="str">
+        <v>owner3@sunrisevalley.com</v>
+      </c>
+      <c r="F39" t="str">
+        <v>Test@1234</v>
+      </c>
+      <c r="G39" t="str">
+        <v>owner3_sunrise</v>
+      </c>
+      <c r="H39" t="str">
+        <v>+9198201006</v>
+      </c>
+      <c r="I39" t="str">
+        <v>P1-03</v>
+      </c>
+      <c r="J39" t="str">
+        <v>Active</v>
+      </c>
+      <c r="K39" t="str">
+        <v>Financial dashboard, tenant arrears, visitor pass generation, amenity booking.</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>39</v>
+      </c>
+      <c r="B40" t="str">
+        <v>Sunrise Valley Estates</v>
+      </c>
+      <c r="C40" t="str">
+        <v>Resident Owner</v>
+      </c>
+      <c r="D40" t="str">
+        <v>Aarav Desai</v>
+      </c>
+      <c r="E40" t="str">
+        <v>owner4@sunrisevalley.com</v>
+      </c>
+      <c r="F40" t="str">
+        <v>Test@1234</v>
+      </c>
+      <c r="G40" t="str">
+        <v>owner4_sunrise</v>
+      </c>
+      <c r="H40" t="str">
+        <v>+9198201007</v>
+      </c>
+      <c r="I40" t="str">
+        <v>P1-04</v>
+      </c>
+      <c r="J40" t="str">
+        <v>Active</v>
+      </c>
+      <c r="K40" t="str">
+        <v>Financial dashboard, tenant arrears, visitor pass generation, amenity booking.</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>40</v>
+      </c>
+      <c r="B41" t="str">
+        <v>Sunrise Valley Estates</v>
+      </c>
+      <c r="C41" t="str">
+        <v>Resident Owner</v>
+      </c>
+      <c r="D41" t="str">
+        <v>Siddharth Shah</v>
+      </c>
+      <c r="E41" t="str">
+        <v>owner5@sunrisevalley.com</v>
+      </c>
+      <c r="F41" t="str">
+        <v>Test@1234</v>
+      </c>
+      <c r="G41" t="str">
+        <v>owner5_sunrise</v>
+      </c>
+      <c r="H41" t="str">
+        <v>+9198201008</v>
+      </c>
+      <c r="I41" t="str">
+        <v>P1-05</v>
+      </c>
+      <c r="J41" t="str">
+        <v>Active</v>
+      </c>
+      <c r="K41" t="str">
+        <v>Financial dashboard, tenant arrears, visitor pass generation, amenity booking.</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>41</v>
+      </c>
+      <c r="B42" t="str">
+        <v>Sunrise Valley Estates</v>
+      </c>
+      <c r="C42" t="str">
+        <v>Resident Owner</v>
+      </c>
+      <c r="D42" t="str">
+        <v>Kavya Singh</v>
+      </c>
+      <c r="E42" t="str">
+        <v>owner6@sunrisevalley.com</v>
+      </c>
+      <c r="F42" t="str">
+        <v>Test@1234</v>
+      </c>
+      <c r="G42" t="str">
+        <v>owner6_sunrise</v>
+      </c>
+      <c r="H42" t="str">
+        <v>+9198201009</v>
+      </c>
+      <c r="I42" t="str">
+        <v>P1-06</v>
+      </c>
+      <c r="J42" t="str">
+        <v>Active</v>
+      </c>
+      <c r="K42" t="str">
+        <v>Financial dashboard, tenant arrears, visitor pass generation, amenity booking.</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>42</v>
+      </c>
+      <c r="B43" t="str">
+        <v>Sunrise Valley Estates</v>
+      </c>
+      <c r="C43" t="str">
+        <v>Resident Owner</v>
+      </c>
+      <c r="D43" t="str">
+        <v>Nisha Bose</v>
+      </c>
+      <c r="E43" t="str">
+        <v>owner7@sunrisevalley.com</v>
+      </c>
+      <c r="F43" t="str">
+        <v>Test@1234</v>
+      </c>
+      <c r="G43" t="str">
+        <v>owner7_sunrise</v>
+      </c>
+      <c r="H43" t="str">
+        <v>+9198201010</v>
+      </c>
+      <c r="I43" t="str">
+        <v>P1-07</v>
+      </c>
+      <c r="J43" t="str">
+        <v>Active</v>
+      </c>
+      <c r="K43" t="str">
+        <v>Financial dashboard, tenant arrears, visitor pass generation, amenity booking.</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>43</v>
+      </c>
+      <c r="B44" t="str">
+        <v>Sunrise Valley Estates</v>
+      </c>
+      <c r="C44" t="str">
+        <v>Resident Tenant</v>
+      </c>
+      <c r="D44" t="str">
+        <v>Tanvi Pillai</v>
+      </c>
+      <c r="E44" t="str">
+        <v>tenant1@sunrisevalley.com</v>
+      </c>
+      <c r="F44" t="str">
+        <v>Test@1234</v>
+      </c>
+      <c r="G44" t="str">
+        <v>tenant1_sunrise</v>
+      </c>
+      <c r="H44" t="str">
+        <v>+9198201011</v>
+      </c>
+      <c r="I44" t="str">
+        <v>P1-08</v>
+      </c>
+      <c r="J44" t="str">
+        <v>Active</v>
+      </c>
+      <c r="K44" t="str">
+        <v>Raise complaints, pay invoices, book amenities, create guest visitor passes.</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>44</v>
+      </c>
+      <c r="B45" t="str">
+        <v>Sunrise Valley Estates</v>
+      </c>
+      <c r="C45" t="str">
+        <v>Resident Tenant</v>
+      </c>
+      <c r="D45" t="str">
+        <v>Ananya Jain</v>
+      </c>
+      <c r="E45" t="str">
+        <v>tenant2@sunrisevalley.com</v>
+      </c>
+      <c r="F45" t="str">
+        <v>Test@1234</v>
+      </c>
+      <c r="G45" t="str">
+        <v>tenant2_sunrise</v>
+      </c>
+      <c r="H45" t="str">
+        <v>+9198201012</v>
+      </c>
+      <c r="I45" t="str">
+        <v>P1-09</v>
+      </c>
+      <c r="J45" t="str">
+        <v>Active</v>
+      </c>
+      <c r="K45" t="str">
+        <v>Raise complaints, pay invoices, book amenities, create guest visitor passes.</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>45</v>
+      </c>
+      <c r="B46" t="str">
+        <v>Sunrise Valley Estates</v>
+      </c>
+      <c r="C46" t="str">
+        <v>Resident Tenant</v>
+      </c>
+      <c r="D46" t="str">
+        <v>Deepa Shah</v>
+      </c>
+      <c r="E46" t="str">
+        <v>tenant3@sunrisevalley.com</v>
+      </c>
+      <c r="F46" t="str">
+        <v>Test@1234</v>
+      </c>
+      <c r="G46" t="str">
+        <v>tenant3_sunrise</v>
+      </c>
+      <c r="H46" t="str">
+        <v>+9198201013</v>
+      </c>
+      <c r="I46" t="str">
+        <v>P1-10</v>
+      </c>
+      <c r="J46" t="str">
+        <v>Active</v>
+      </c>
+      <c r="K46" t="str">
+        <v>Raise complaints, pay invoices, book amenities, create guest visitor passes.</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>46</v>
+      </c>
+      <c r="B47" t="str">
+        <v>Sunrise Valley Estates</v>
+      </c>
+      <c r="C47" t="str">
+        <v>Resident Tenant</v>
+      </c>
+      <c r="D47" t="str">
+        <v>Pooja Kumar</v>
+      </c>
+      <c r="E47" t="str">
+        <v>tenant4@sunrisevalley.com</v>
+      </c>
+      <c r="F47" t="str">
+        <v>Test@1234</v>
+      </c>
+      <c r="G47" t="str">
+        <v>tenant4_sunrise</v>
+      </c>
+      <c r="H47" t="str">
+        <v>+9198201014</v>
+      </c>
+      <c r="I47" t="str">
+        <v>P2-01</v>
+      </c>
+      <c r="J47" t="str">
+        <v>Active</v>
+      </c>
+      <c r="K47" t="str">
+        <v>Raise complaints, pay invoices, book amenities, create guest visitor passes.</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>47</v>
+      </c>
+      <c r="B48" t="str">
+        <v>Sunrise Valley Estates</v>
+      </c>
+      <c r="C48" t="str">
+        <v>Resident Tenant</v>
+      </c>
+      <c r="D48" t="str">
+        <v>Rohit Patel</v>
+      </c>
+      <c r="E48" t="str">
+        <v>tenant5@sunrisevalley.com</v>
+      </c>
+      <c r="F48" t="str">
+        <v>Test@1234</v>
+      </c>
+      <c r="G48" t="str">
+        <v>tenant5_sunrise</v>
+      </c>
+      <c r="H48" t="str">
+        <v>+9198201015</v>
+      </c>
+      <c r="I48" t="str">
+        <v>P2-02</v>
+      </c>
+      <c r="J48" t="str">
+        <v>Active</v>
+      </c>
+      <c r="K48" t="str">
+        <v>Raise complaints, pay invoices, book amenities, create guest visitor passes.</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>48</v>
+      </c>
+      <c r="B49" t="str">
+        <v>Sunrise Valley Estates</v>
+      </c>
+      <c r="C49" t="str">
+        <v>Resident Tenant</v>
+      </c>
+      <c r="D49" t="str">
+        <v>Lakshmi Sharma</v>
+      </c>
+      <c r="E49" t="str">
+        <v>tenant6@sunrisevalley.com</v>
+      </c>
+      <c r="F49" t="str">
+        <v>Test@1234</v>
+      </c>
+      <c r="G49" t="str">
+        <v>tenant6_sunrise</v>
+      </c>
+      <c r="H49" t="str">
+        <v>+9198201016</v>
+      </c>
+      <c r="I49" t="str">
+        <v>P2-03</v>
+      </c>
+      <c r="J49" t="str">
+        <v>Active</v>
+      </c>
+      <c r="K49" t="str">
+        <v>Raise complaints, pay invoices, book amenities, create guest visitor passes.</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>49</v>
+      </c>
+      <c r="B50" t="str">
+        <v>Sunrise Valley Estates</v>
+      </c>
+      <c r="C50" t="str">
+        <v>Resident Tenant</v>
+      </c>
+      <c r="D50" t="str">
+        <v>Aarav Sinha</v>
+      </c>
+      <c r="E50" t="str">
+        <v>tenant7@sunrisevalley.com</v>
+      </c>
+      <c r="F50" t="str">
+        <v>Test@1234</v>
+      </c>
+      <c r="G50" t="str">
+        <v>tenant7_sunrise</v>
+      </c>
+      <c r="H50" t="str">
+        <v>+9198201017</v>
+      </c>
+      <c r="I50" t="str">
+        <v>P2-04</v>
+      </c>
+      <c r="J50" t="str">
+        <v>Active</v>
+      </c>
+      <c r="K50" t="str">
+        <v>Raise complaints, pay invoices, book amenities, create guest visitor passes.</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>50</v>
+      </c>
+      <c r="B51" t="str">
+        <v>Sunrise Valley Estates</v>
+      </c>
+      <c r="C51" t="str">
+        <v>Family Member</v>
+      </c>
+      <c r="D51" t="str">
+        <v>Zara Joshi</v>
+      </c>
+      <c r="E51" t="str">
+        <v>family1@sunrisevalley.com</v>
+      </c>
+      <c r="F51" t="str">
+        <v>Test@1234</v>
+      </c>
+      <c r="G51" t="str">
+        <v>family1_sunrise</v>
+      </c>
+      <c r="H51" t="str">
+        <v>+9198201018</v>
+      </c>
+      <c r="I51" t="str">
+        <v>P1-01</v>
+      </c>
+      <c r="J51" t="str">
+        <v>Active</v>
+      </c>
+      <c r="K51" t="str">
+        <v>View notices, view community events, raise quick complaints.</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>51</v>
+      </c>
+      <c r="B52" t="str">
+        <v>Sunrise Valley Estates</v>
+      </c>
+      <c r="C52" t="str">
+        <v>Family Member</v>
+      </c>
+      <c r="D52" t="str">
+        <v>Jaya Kumar</v>
+      </c>
+      <c r="E52" t="str">
+        <v>family2@sunrisevalley.com</v>
+      </c>
+      <c r="F52" t="str">
+        <v>Test@1234</v>
+      </c>
+      <c r="G52" t="str">
+        <v>family2_sunrise</v>
+      </c>
+      <c r="H52" t="str">
+        <v>+9198201019</v>
+      </c>
+      <c r="I52" t="str">
+        <v>P1-02</v>
+      </c>
+      <c r="J52" t="str">
+        <v>Active</v>
+      </c>
+      <c r="K52" t="str">
+        <v>View notices, view community events, raise quick complaints.</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>52</v>
+      </c>
+      <c r="B53" t="str">
+        <v>Palm Meadows Residency</v>
+      </c>
+      <c r="C53" t="str">
+        <v>Community Admin</v>
+      </c>
+      <c r="D53" t="str">
+        <v>Rajesh Kapoor</v>
+      </c>
+      <c r="E53" t="str">
+        <v>admin1@palmmeadows.com</v>
+      </c>
+      <c r="F53" t="str">
+        <v>Test@1234</v>
+      </c>
+      <c r="G53" t="str">
+        <v>admin1_palm</v>
+      </c>
+      <c r="H53" t="str">
+        <v>+9198301000</v>
+      </c>
+      <c r="I53" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="J53" t="str">
+        <v>Active</v>
+      </c>
+      <c r="K53" t="str">
+        <v>Full Admin controls, user setup, billing, complaints assignment, notice publishing.</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>53</v>
+      </c>
+      <c r="B54" t="str">
+        <v>Palm Meadows Residency</v>
+      </c>
+      <c r="C54" t="str">
+        <v>Facility Manager</v>
+      </c>
+      <c r="D54" t="str">
+        <v>Zara Iyer</v>
+      </c>
+      <c r="E54" t="str">
+        <v>fm1@palmmeadows.com</v>
+      </c>
+      <c r="F54" t="str">
+        <v>Test@1234</v>
+      </c>
+      <c r="G54" t="str">
+        <v>fm1_palm</v>
+      </c>
+      <c r="H54" t="str">
+        <v>+9198301001</v>
+      </c>
+      <c r="I54" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="J54" t="str">
+        <v>Active</v>
+      </c>
+      <c r="K54" t="str">
+        <v>Amenity scheduling, maintenance slots, ticket updates, facility inspection.</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>54</v>
+      </c>
+      <c r="B55" t="str">
+        <v>Palm Meadows Residency</v>
+      </c>
+      <c r="C55" t="str">
+        <v>Security Guard</v>
+      </c>
+      <c r="D55" t="str">
+        <v>Neeraj Menon</v>
+      </c>
+      <c r="E55" t="str">
+        <v>guard1@palmmeadows.com</v>
+      </c>
+      <c r="F55" t="str">
+        <v>Test@1234</v>
+      </c>
+      <c r="G55" t="str">
+        <v>guard1_palm</v>
+      </c>
+      <c r="H55" t="str">
+        <v>+9198301002</v>
+      </c>
+      <c r="I55" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="J55" t="str">
+        <v>Active</v>
+      </c>
+      <c r="K55" t="str">
+        <v>Gate entry/exit scanner, visitor verification, passcode validation.</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>55</v>
+      </c>
+      <c r="B56" t="str">
+        <v>Palm Meadows Residency</v>
+      </c>
+      <c r="C56" t="str">
+        <v>Resident Owner</v>
+      </c>
+      <c r="D56" t="str">
+        <v>Usha Rao</v>
+      </c>
+      <c r="E56" t="str">
+        <v>owner1@palmmeadows.com</v>
+      </c>
+      <c r="F56" t="str">
+        <v>Test@1234</v>
+      </c>
+      <c r="G56" t="str">
+        <v>owner1_palm</v>
+      </c>
+      <c r="H56" t="str">
+        <v>+9198301003</v>
+      </c>
+      <c r="I56" t="str">
+        <v>T1-101</v>
+      </c>
+      <c r="J56" t="str">
+        <v>Active</v>
+      </c>
+      <c r="K56" t="str">
+        <v>Financial dashboard, tenant arrears, visitor pass generation, amenity booking.</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>56</v>
+      </c>
+      <c r="B57" t="str">
+        <v>Palm Meadows Residency</v>
+      </c>
+      <c r="C57" t="str">
+        <v>Resident Owner</v>
+      </c>
+      <c r="D57" t="str">
+        <v>Sahil Chauhan</v>
+      </c>
+      <c r="E57" t="str">
+        <v>owner2@palmmeadows.com</v>
+      </c>
+      <c r="F57" t="str">
+        <v>Test@1234</v>
+      </c>
+      <c r="G57" t="str">
+        <v>owner2_palm</v>
+      </c>
+      <c r="H57" t="str">
+        <v>+9198301004</v>
+      </c>
+      <c r="I57" t="str">
+        <v>T1-102</v>
+      </c>
+      <c r="J57" t="str">
+        <v>Active</v>
+      </c>
+      <c r="K57" t="str">
+        <v>Financial dashboard, tenant arrears, visitor pass generation, amenity booking.</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>57</v>
+      </c>
+      <c r="B58" t="str">
+        <v>Palm Meadows Residency</v>
+      </c>
+      <c r="C58" t="str">
+        <v>Resident Owner</v>
+      </c>
+      <c r="D58" t="str">
+        <v>Seema Banerjee</v>
+      </c>
+      <c r="E58" t="str">
+        <v>owner3@palmmeadows.com</v>
+      </c>
+      <c r="F58" t="str">
+        <v>Test@1234</v>
+      </c>
+      <c r="G58" t="str">
+        <v>owner3_palm</v>
+      </c>
+      <c r="H58" t="str">
+        <v>+9198301005</v>
+      </c>
+      <c r="I58" t="str">
+        <v>T1-103</v>
+      </c>
+      <c r="J58" t="str">
+        <v>Active</v>
+      </c>
+      <c r="K58" t="str">
+        <v>Financial dashboard, tenant arrears, visitor pass generation, amenity booking.</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>58</v>
+      </c>
+      <c r="B59" t="str">
+        <v>Palm Meadows Residency</v>
+      </c>
+      <c r="C59" t="str">
+        <v>Resident Owner</v>
+      </c>
+      <c r="D59" t="str">
+        <v>Tushar Sinha</v>
+      </c>
+      <c r="E59" t="str">
+        <v>owner4@palmmeadows.com</v>
+      </c>
+      <c r="F59" t="str">
+        <v>Test@1234</v>
+      </c>
+      <c r="G59" t="str">
+        <v>owner4_palm</v>
+      </c>
+      <c r="H59" t="str">
+        <v>+9198301006</v>
+      </c>
+      <c r="I59" t="str">
+        <v>T1-104</v>
+      </c>
+      <c r="J59" t="str">
+        <v>Active</v>
+      </c>
+      <c r="K59" t="str">
+        <v>Financial dashboard, tenant arrears, visitor pass generation, amenity booking.</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>59</v>
+      </c>
+      <c r="B60" t="str">
+        <v>Palm Meadows Residency</v>
+      </c>
+      <c r="C60" t="str">
+        <v>Resident Owner</v>
+      </c>
+      <c r="D60" t="str">
+        <v>Shiv Shah</v>
+      </c>
+      <c r="E60" t="str">
+        <v>owner5@palmmeadows.com</v>
+      </c>
+      <c r="F60" t="str">
+        <v>Test@1234</v>
+      </c>
+      <c r="G60" t="str">
+        <v>owner5_palm</v>
+      </c>
+      <c r="H60" t="str">
+        <v>+9198301007</v>
+      </c>
+      <c r="I60" t="str">
+        <v>T1-105</v>
+      </c>
+      <c r="J60" t="str">
+        <v>Active</v>
+      </c>
+      <c r="K60" t="str">
+        <v>Financial dashboard, tenant arrears, visitor pass generation, amenity booking.</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>60</v>
+      </c>
+      <c r="B61" t="str">
+        <v>Palm Meadows Residency</v>
+      </c>
+      <c r="C61" t="str">
+        <v>Resident Tenant</v>
+      </c>
+      <c r="D61" t="str">
+        <v>Siddharth Verma</v>
+      </c>
+      <c r="E61" t="str">
+        <v>tenant1@palmmeadows.com</v>
+      </c>
+      <c r="F61" t="str">
+        <v>Test@1234</v>
+      </c>
+      <c r="G61" t="str">
+        <v>tenant1_palm</v>
+      </c>
+      <c r="H61" t="str">
+        <v>+9198301008</v>
+      </c>
+      <c r="I61" t="str">
+        <v>T1-106</v>
+      </c>
+      <c r="J61" t="str">
+        <v>Active</v>
+      </c>
+      <c r="K61" t="str">
+        <v>Raise complaints, pay invoices, book amenities, create guest visitor passes.</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>61</v>
+      </c>
+      <c r="B62" t="str">
+        <v>Palm Meadows Residency</v>
+      </c>
+      <c r="C62" t="str">
+        <v>Resident Tenant</v>
+      </c>
+      <c r="D62" t="str">
+        <v>Simran Tiwari</v>
+      </c>
+      <c r="E62" t="str">
+        <v>tenant2@palmmeadows.com</v>
+      </c>
+      <c r="F62" t="str">
+        <v>Test@1234</v>
+      </c>
+      <c r="G62" t="str">
+        <v>tenant2_palm</v>
+      </c>
+      <c r="H62" t="str">
+        <v>+9198301009</v>
+      </c>
+      <c r="I62" t="str">
+        <v>T1-107</v>
+      </c>
+      <c r="J62" t="str">
+        <v>Active</v>
+      </c>
+      <c r="K62" t="str">
+        <v>Raise complaints, pay invoices, book amenities, create guest visitor passes.</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>62</v>
+      </c>
+      <c r="B63" t="str">
+        <v>Palm Meadows Residency</v>
+      </c>
+      <c r="C63" t="str">
+        <v>Resident Tenant</v>
+      </c>
+      <c r="D63" t="str">
+        <v>Priya Das</v>
+      </c>
+      <c r="E63" t="str">
+        <v>tenant3@palmmeadows.com</v>
+      </c>
+      <c r="F63" t="str">
+        <v>Test@1234</v>
+      </c>
+      <c r="G63" t="str">
+        <v>tenant3_palm</v>
+      </c>
+      <c r="H63" t="str">
+        <v>+9198301010</v>
+      </c>
+      <c r="I63" t="str">
+        <v>T1-108</v>
+      </c>
+      <c r="J63" t="str">
+        <v>Active</v>
+      </c>
+      <c r="K63" t="str">
+        <v>Raise complaints, pay invoices, book amenities, create guest visitor passes.</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>63</v>
+      </c>
+      <c r="B64" t="str">
+        <v>Palm Meadows Residency</v>
+      </c>
+      <c r="C64" t="str">
+        <v>Resident Tenant</v>
+      </c>
+      <c r="D64" t="str">
+        <v>Suresh Das</v>
+      </c>
+      <c r="E64" t="str">
+        <v>tenant4@palmmeadows.com</v>
+      </c>
+      <c r="F64" t="str">
+        <v>Test@1234</v>
+      </c>
+      <c r="G64" t="str">
+        <v>tenant4_palm</v>
+      </c>
+      <c r="H64" t="str">
+        <v>+9198301011</v>
+      </c>
+      <c r="I64" t="str">
+        <v>T2-101</v>
+      </c>
+      <c r="J64" t="str">
+        <v>Active</v>
+      </c>
+      <c r="K64" t="str">
+        <v>Raise complaints, pay invoices, book amenities, create guest visitor passes.</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>64</v>
+      </c>
+      <c r="B65" t="str">
+        <v>Palm Meadows Residency</v>
+      </c>
+      <c r="C65" t="str">
+        <v>Resident Tenant</v>
+      </c>
+      <c r="D65" t="str">
+        <v>Sangeeta Reddy</v>
+      </c>
+      <c r="E65" t="str">
+        <v>tenant5@palmmeadows.com</v>
+      </c>
+      <c r="F65" t="str">
+        <v>Test@1234</v>
+      </c>
+      <c r="G65" t="str">
+        <v>tenant5_palm</v>
+      </c>
+      <c r="H65" t="str">
+        <v>+9198301012</v>
+      </c>
+      <c r="I65" t="str">
+        <v>T2-102</v>
+      </c>
+      <c r="J65" t="str">
+        <v>Active</v>
+      </c>
+      <c r="K65" t="str">
+        <v>Raise complaints, pay invoices, book amenities, create guest visitor passes.</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>65</v>
+      </c>
+      <c r="B66" t="str">
+        <v>Palm Meadows Residency</v>
+      </c>
+      <c r="C66" t="str">
+        <v>Family Member</v>
+      </c>
+      <c r="D66" t="str">
+        <v>Vishal Kumar</v>
+      </c>
+      <c r="E66" t="str">
+        <v>family1@palmmeadows.com</v>
+      </c>
+      <c r="F66" t="str">
+        <v>Test@1234</v>
+      </c>
+      <c r="G66" t="str">
+        <v>family1_palm</v>
+      </c>
+      <c r="H66" t="str">
+        <v>+9198301013</v>
+      </c>
+      <c r="I66" t="str">
+        <v>T1-101</v>
+      </c>
+      <c r="J66" t="str">
+        <v>Active</v>
+      </c>
+      <c r="K66" t="str">
+        <v>View notices, view community events, raise quick complaints.</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>66</v>
+      </c>
+      <c r="B67" t="str">
+        <v>Palm Meadows Residency</v>
+      </c>
+      <c r="C67" t="str">
+        <v>Family Member</v>
+      </c>
+      <c r="D67" t="str">
+        <v>Arjun Rao</v>
+      </c>
+      <c r="E67" t="str">
+        <v>family2@palmmeadows.com</v>
+      </c>
+      <c r="F67" t="str">
+        <v>Test@1234</v>
+      </c>
+      <c r="G67" t="str">
+        <v>family2_palm</v>
+      </c>
+      <c r="H67" t="str">
+        <v>+9198301014</v>
+      </c>
+      <c r="I67" t="str">
+        <v>T1-102</v>
+      </c>
+      <c r="J67" t="str">
+        <v>Active</v>
+      </c>
+      <c r="K67" t="str">
+        <v>View notices, view community events, raise quick complaints.</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K67"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:K31"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>Unit Number</v>
+        <v>S.No</v>
       </c>
       <c r="B1" t="str">
-        <v>Block</v>
+        <v>Community Name</v>
       </c>
       <c r="C1" t="str">
-        <v>Type</v>
+        <v>Role / Category</v>
       </c>
       <c r="D1" t="str">
+        <v>Full Name</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Email / Login</v>
+      </c>
+      <c r="F1" t="str">
+        <v>Password</v>
+      </c>
+      <c r="G1" t="str">
+        <v>Username</v>
+      </c>
+      <c r="H1" t="str">
+        <v>Phone</v>
+      </c>
+      <c r="I1" t="str">
+        <v>Assigned Unit</v>
+      </c>
+      <c r="J1" t="str">
         <v>Status</v>
       </c>
-      <c r="E1" t="str">
-        <v>Primary Resident</v>
-      </c>
-      <c r="F1" t="str">
-        <v>Owner</v>
-      </c>
-      <c r="G1" t="str">
-        <v>Current Invoices</v>
+      <c r="K1" t="str">
+        <v>Key Testing Focus</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="str">
-        <v>Villa A-101</v>
+      <c r="A2">
+        <v>2</v>
       </c>
       <c r="B2" t="str">
-        <v>Block A</v>
+        <v>Greenfield Heights Community</v>
       </c>
       <c r="C2" t="str">
-        <v>Villa</v>
+        <v>Community Admin</v>
       </c>
       <c r="D2" t="str">
-        <v>Occupied</v>
+        <v>Rohit Bose</v>
       </c>
       <c r="E2" t="str">
-        <v>Rajesh Kumar (Owner 1)</v>
+        <v>admin1@greenfield.com</v>
       </c>
       <c r="F2" t="str">
-        <v>Rajesh Kumar (Owner 1)</v>
+        <v>Test@1234</v>
       </c>
       <c r="G2" t="str">
-        <v>INV-2026-07-001 (Paid: ₹7,000), INV-2026-07-002 (Unpaid: ₹5,000)</v>
+        <v>admin1_greenfield</v>
+      </c>
+      <c r="H2" t="str">
+        <v>+9198101000</v>
+      </c>
+      <c r="I2" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="J2" t="str">
+        <v>Active</v>
+      </c>
+      <c r="K2" t="str">
+        <v>Full Admin controls, user setup, billing, complaints assignment, notice publishing.</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="str">
-        <v>Villa A-102</v>
+      <c r="A3">
+        <v>3</v>
       </c>
       <c r="B3" t="str">
-        <v>Block A</v>
+        <v>Greenfield Heights Community</v>
       </c>
       <c r="C3" t="str">
-        <v>Villa</v>
+        <v>Community Admin</v>
       </c>
       <c r="D3" t="str">
-        <v>Occupied</v>
+        <v>Harish Kumar</v>
       </c>
       <c r="E3" t="str">
-        <v>Rahul Mehta (Tenant 1)</v>
+        <v>admin2@greenfield.com</v>
       </c>
       <c r="F3" t="str">
-        <v>Vikram Singh (Owner 2)</v>
+        <v>Test@1234</v>
       </c>
       <c r="G3" t="str">
-        <v>INV-2026-07-003 (Unpaid: ₹7,000)</v>
+        <v>admin2_greenfield</v>
+      </c>
+      <c r="H3" t="str">
+        <v>+9198101001</v>
+      </c>
+      <c r="I3" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="J3" t="str">
+        <v>Active</v>
+      </c>
+      <c r="K3" t="str">
+        <v>Full Admin controls, user setup, billing, complaints assignment, notice publishing.</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="str">
-        <v>Villa B-201</v>
+      <c r="A4">
+        <v>4</v>
       </c>
       <c r="B4" t="str">
-        <v>Block B</v>
+        <v>Greenfield Heights Community</v>
       </c>
       <c r="C4" t="str">
-        <v>Villa</v>
+        <v>Facility Manager</v>
       </c>
       <c r="D4" t="str">
-        <v>Occupied</v>
+        <v>Sanjay Kapoor</v>
       </c>
       <c r="E4" t="str">
-        <v>Aisha Khan (Tenant 2)</v>
+        <v>fm1@greenfield.com</v>
       </c>
       <c r="F4" t="str">
-        <v>Rajesh Kumar (Owner 1)</v>
+        <v>Test@1234</v>
       </c>
       <c r="G4" t="str">
-        <v>INV-2026-07-004 (Verification Pending: ₹7,000)</v>
+        <v>fm1_greenfield</v>
+      </c>
+      <c r="H4" t="str">
+        <v>+9198101002</v>
+      </c>
+      <c r="I4" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="J4" t="str">
+        <v>Active</v>
+      </c>
+      <c r="K4" t="str">
+        <v>Amenity scheduling, maintenance slots, ticket updates, facility inspection.</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>5</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Greenfield Heights Community</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Facility Manager</v>
+      </c>
+      <c r="D5" t="str">
+        <v>Zara Sharma</v>
+      </c>
+      <c r="E5" t="str">
+        <v>fm2@greenfield.com</v>
+      </c>
+      <c r="F5" t="str">
+        <v>Test@1234</v>
+      </c>
+      <c r="G5" t="str">
+        <v>fm2_greenfield</v>
+      </c>
+      <c r="H5" t="str">
+        <v>+9198101003</v>
+      </c>
+      <c r="I5" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="J5" t="str">
+        <v>Active</v>
+      </c>
+      <c r="K5" t="str">
+        <v>Amenity scheduling, maintenance slots, ticket updates, facility inspection.</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>6</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Greenfield Heights Community</v>
+      </c>
+      <c r="C6" t="str">
+        <v>Security Guard</v>
+      </c>
+      <c r="D6" t="str">
+        <v>Vikram Mehta</v>
+      </c>
+      <c r="E6" t="str">
+        <v>guard1@greenfield.com</v>
+      </c>
+      <c r="F6" t="str">
+        <v>Test@1234</v>
+      </c>
+      <c r="G6" t="str">
+        <v>guard1_greenfield</v>
+      </c>
+      <c r="H6" t="str">
+        <v>+9198101004</v>
+      </c>
+      <c r="I6" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="J6" t="str">
+        <v>Active</v>
+      </c>
+      <c r="K6" t="str">
+        <v>Gate entry/exit scanner, visitor verification, passcode validation.</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>7</v>
+      </c>
+      <c r="B7" t="str">
+        <v>Greenfield Heights Community</v>
+      </c>
+      <c r="C7" t="str">
+        <v>Security Guard</v>
+      </c>
+      <c r="D7" t="str">
+        <v>Siddharth Gupta</v>
+      </c>
+      <c r="E7" t="str">
+        <v>guard2@greenfield.com</v>
+      </c>
+      <c r="F7" t="str">
+        <v>Test@1234</v>
+      </c>
+      <c r="G7" t="str">
+        <v>guard2_greenfield</v>
+      </c>
+      <c r="H7" t="str">
+        <v>+9198101005</v>
+      </c>
+      <c r="I7" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="J7" t="str">
+        <v>Active</v>
+      </c>
+      <c r="K7" t="str">
+        <v>Gate entry/exit scanner, visitor verification, passcode validation.</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>8</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Greenfield Heights Community</v>
+      </c>
+      <c r="C8" t="str">
+        <v>Resident Owner</v>
+      </c>
+      <c r="D8" t="str">
+        <v>Ishaan Sinha</v>
+      </c>
+      <c r="E8" t="str">
+        <v>owner1@greenfield.com</v>
+      </c>
+      <c r="F8" t="str">
+        <v>Test@1234</v>
+      </c>
+      <c r="G8" t="str">
+        <v>owner1_greenfield</v>
+      </c>
+      <c r="H8" t="str">
+        <v>+9198101006</v>
+      </c>
+      <c r="I8" t="str">
+        <v>A-101</v>
+      </c>
+      <c r="J8" t="str">
+        <v>Active</v>
+      </c>
+      <c r="K8" t="str">
+        <v>Financial dashboard, tenant arrears, visitor pass generation, amenity booking.</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>9</v>
+      </c>
+      <c r="B9" t="str">
+        <v>Greenfield Heights Community</v>
+      </c>
+      <c r="C9" t="str">
+        <v>Resident Owner</v>
+      </c>
+      <c r="D9" t="str">
+        <v>Bhavna Shah</v>
+      </c>
+      <c r="E9" t="str">
+        <v>owner2@greenfield.com</v>
+      </c>
+      <c r="F9" t="str">
+        <v>Test@1234</v>
+      </c>
+      <c r="G9" t="str">
+        <v>owner2_greenfield</v>
+      </c>
+      <c r="H9" t="str">
+        <v>+9198101007</v>
+      </c>
+      <c r="I9" t="str">
+        <v>A-102</v>
+      </c>
+      <c r="J9" t="str">
+        <v>Active</v>
+      </c>
+      <c r="K9" t="str">
+        <v>Financial dashboard, tenant arrears, visitor pass generation, amenity booking.</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>10</v>
+      </c>
+      <c r="B10" t="str">
+        <v>Greenfield Heights Community</v>
+      </c>
+      <c r="C10" t="str">
+        <v>Resident Owner</v>
+      </c>
+      <c r="D10" t="str">
+        <v>Aditi Ghosh</v>
+      </c>
+      <c r="E10" t="str">
+        <v>owner3@greenfield.com</v>
+      </c>
+      <c r="F10" t="str">
+        <v>Test@1234</v>
+      </c>
+      <c r="G10" t="str">
+        <v>owner3_greenfield</v>
+      </c>
+      <c r="H10" t="str">
+        <v>+9198101008</v>
+      </c>
+      <c r="I10" t="str">
+        <v>A-103</v>
+      </c>
+      <c r="J10" t="str">
+        <v>Active</v>
+      </c>
+      <c r="K10" t="str">
+        <v>Financial dashboard, tenant arrears, visitor pass generation, amenity booking.</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>11</v>
+      </c>
+      <c r="B11" t="str">
+        <v>Greenfield Heights Community</v>
+      </c>
+      <c r="C11" t="str">
+        <v>Resident Owner</v>
+      </c>
+      <c r="D11" t="str">
+        <v>Rajesh Mehta</v>
+      </c>
+      <c r="E11" t="str">
+        <v>owner4@greenfield.com</v>
+      </c>
+      <c r="F11" t="str">
+        <v>Test@1234</v>
+      </c>
+      <c r="G11" t="str">
+        <v>owner4_greenfield</v>
+      </c>
+      <c r="H11" t="str">
+        <v>+9198101009</v>
+      </c>
+      <c r="I11" t="str">
+        <v>A-104</v>
+      </c>
+      <c r="J11" t="str">
+        <v>Active</v>
+      </c>
+      <c r="K11" t="str">
+        <v>Financial dashboard, tenant arrears, visitor pass generation, amenity booking.</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>12</v>
+      </c>
+      <c r="B12" t="str">
+        <v>Greenfield Heights Community</v>
+      </c>
+      <c r="C12" t="str">
+        <v>Resident Owner</v>
+      </c>
+      <c r="D12" t="str">
+        <v>Siddharth Iyer</v>
+      </c>
+      <c r="E12" t="str">
+        <v>owner5@greenfield.com</v>
+      </c>
+      <c r="F12" t="str">
+        <v>Test@1234</v>
+      </c>
+      <c r="G12" t="str">
+        <v>owner5_greenfield</v>
+      </c>
+      <c r="H12" t="str">
+        <v>+9198101010</v>
+      </c>
+      <c r="I12" t="str">
+        <v>A-105</v>
+      </c>
+      <c r="J12" t="str">
+        <v>Active</v>
+      </c>
+      <c r="K12" t="str">
+        <v>Financial dashboard, tenant arrears, visitor pass generation, amenity booking.</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>13</v>
+      </c>
+      <c r="B13" t="str">
+        <v>Greenfield Heights Community</v>
+      </c>
+      <c r="C13" t="str">
+        <v>Resident Owner</v>
+      </c>
+      <c r="D13" t="str">
+        <v>Rahul Patel</v>
+      </c>
+      <c r="E13" t="str">
+        <v>owner6@greenfield.com</v>
+      </c>
+      <c r="F13" t="str">
+        <v>Test@1234</v>
+      </c>
+      <c r="G13" t="str">
+        <v>owner6_greenfield</v>
+      </c>
+      <c r="H13" t="str">
+        <v>+9198101011</v>
+      </c>
+      <c r="I13" t="str">
+        <v>A-106</v>
+      </c>
+      <c r="J13" t="str">
+        <v>Active</v>
+      </c>
+      <c r="K13" t="str">
+        <v>Financial dashboard, tenant arrears, visitor pass generation, amenity booking.</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>14</v>
+      </c>
+      <c r="B14" t="str">
+        <v>Greenfield Heights Community</v>
+      </c>
+      <c r="C14" t="str">
+        <v>Resident Owner</v>
+      </c>
+      <c r="D14" t="str">
+        <v>Priya Verma</v>
+      </c>
+      <c r="E14" t="str">
+        <v>owner7@greenfield.com</v>
+      </c>
+      <c r="F14" t="str">
+        <v>Test@1234</v>
+      </c>
+      <c r="G14" t="str">
+        <v>owner7_greenfield</v>
+      </c>
+      <c r="H14" t="str">
+        <v>+9198101012</v>
+      </c>
+      <c r="I14" t="str">
+        <v>A-107</v>
+      </c>
+      <c r="J14" t="str">
+        <v>Active</v>
+      </c>
+      <c r="K14" t="str">
+        <v>Financial dashboard, tenant arrears, visitor pass generation, amenity booking.</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>15</v>
+      </c>
+      <c r="B15" t="str">
+        <v>Greenfield Heights Community</v>
+      </c>
+      <c r="C15" t="str">
+        <v>Resident Owner</v>
+      </c>
+      <c r="D15" t="str">
+        <v>Tanvi Shah</v>
+      </c>
+      <c r="E15" t="str">
+        <v>owner8@greenfield.com</v>
+      </c>
+      <c r="F15" t="str">
+        <v>Test@1234</v>
+      </c>
+      <c r="G15" t="str">
+        <v>owner8_greenfield</v>
+      </c>
+      <c r="H15" t="str">
+        <v>+9198101013</v>
+      </c>
+      <c r="I15" t="str">
+        <v>A-108</v>
+      </c>
+      <c r="J15" t="str">
+        <v>Active</v>
+      </c>
+      <c r="K15" t="str">
+        <v>Financial dashboard, tenant arrears, visitor pass generation, amenity booking.</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>16</v>
+      </c>
+      <c r="B16" t="str">
+        <v>Greenfield Heights Community</v>
+      </c>
+      <c r="C16" t="str">
+        <v>Resident Owner</v>
+      </c>
+      <c r="D16" t="str">
+        <v>Jaya Mehta</v>
+      </c>
+      <c r="E16" t="str">
+        <v>owner9@greenfield.com</v>
+      </c>
+      <c r="F16" t="str">
+        <v>Test@1234</v>
+      </c>
+      <c r="G16" t="str">
+        <v>owner9_greenfield</v>
+      </c>
+      <c r="H16" t="str">
+        <v>+9198101014</v>
+      </c>
+      <c r="I16" t="str">
+        <v>A-109</v>
+      </c>
+      <c r="J16" t="str">
+        <v>Active</v>
+      </c>
+      <c r="K16" t="str">
+        <v>Financial dashboard, tenant arrears, visitor pass generation, amenity booking.</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>17</v>
+      </c>
+      <c r="B17" t="str">
+        <v>Greenfield Heights Community</v>
+      </c>
+      <c r="C17" t="str">
+        <v>Resident Owner</v>
+      </c>
+      <c r="D17" t="str">
+        <v>Sahil Kumar</v>
+      </c>
+      <c r="E17" t="str">
+        <v>owner10@greenfield.com</v>
+      </c>
+      <c r="F17" t="str">
+        <v>Test@1234</v>
+      </c>
+      <c r="G17" t="str">
+        <v>owner10_greenfield</v>
+      </c>
+      <c r="H17" t="str">
+        <v>+9198101015</v>
+      </c>
+      <c r="I17" t="str">
+        <v>A-110</v>
+      </c>
+      <c r="J17" t="str">
+        <v>Active</v>
+      </c>
+      <c r="K17" t="str">
+        <v>Financial dashboard, tenant arrears, visitor pass generation, amenity booking.</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>18</v>
+      </c>
+      <c r="B18" t="str">
+        <v>Greenfield Heights Community</v>
+      </c>
+      <c r="C18" t="str">
+        <v>Resident Tenant</v>
+      </c>
+      <c r="D18" t="str">
+        <v>Siddharth Mehta</v>
+      </c>
+      <c r="E18" t="str">
+        <v>tenant1@greenfield.com</v>
+      </c>
+      <c r="F18" t="str">
+        <v>Test@1234</v>
+      </c>
+      <c r="G18" t="str">
+        <v>tenant1_greenfield</v>
+      </c>
+      <c r="H18" t="str">
+        <v>+9198101016</v>
+      </c>
+      <c r="I18" t="str">
+        <v>B-101</v>
+      </c>
+      <c r="J18" t="str">
+        <v>Active</v>
+      </c>
+      <c r="K18" t="str">
+        <v>Raise complaints, pay invoices, book amenities, create guest visitor passes.</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>19</v>
+      </c>
+      <c r="B19" t="str">
+        <v>Greenfield Heights Community</v>
+      </c>
+      <c r="C19" t="str">
+        <v>Resident Tenant</v>
+      </c>
+      <c r="D19" t="str">
+        <v>Harish Banerjee</v>
+      </c>
+      <c r="E19" t="str">
+        <v>tenant2@greenfield.com</v>
+      </c>
+      <c r="F19" t="str">
+        <v>Test@1234</v>
+      </c>
+      <c r="G19" t="str">
+        <v>tenant2_greenfield</v>
+      </c>
+      <c r="H19" t="str">
+        <v>+9198101017</v>
+      </c>
+      <c r="I19" t="str">
+        <v>B-102</v>
+      </c>
+      <c r="J19" t="str">
+        <v>Active</v>
+      </c>
+      <c r="K19" t="str">
+        <v>Raise complaints, pay invoices, book amenities, create guest visitor passes.</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>20</v>
+      </c>
+      <c r="B20" t="str">
+        <v>Greenfield Heights Community</v>
+      </c>
+      <c r="C20" t="str">
+        <v>Resident Tenant</v>
+      </c>
+      <c r="D20" t="str">
+        <v>Chirag Rao</v>
+      </c>
+      <c r="E20" t="str">
+        <v>tenant3@greenfield.com</v>
+      </c>
+      <c r="F20" t="str">
+        <v>Test@1234</v>
+      </c>
+      <c r="G20" t="str">
+        <v>tenant3_greenfield</v>
+      </c>
+      <c r="H20" t="str">
+        <v>+9198101018</v>
+      </c>
+      <c r="I20" t="str">
+        <v>B-103</v>
+      </c>
+      <c r="J20" t="str">
+        <v>Active</v>
+      </c>
+      <c r="K20" t="str">
+        <v>Raise complaints, pay invoices, book amenities, create guest visitor passes.</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>21</v>
+      </c>
+      <c r="B21" t="str">
+        <v>Greenfield Heights Community</v>
+      </c>
+      <c r="C21" t="str">
+        <v>Resident Tenant</v>
+      </c>
+      <c r="D21" t="str">
+        <v>Yamini Gupta</v>
+      </c>
+      <c r="E21" t="str">
+        <v>tenant4@greenfield.com</v>
+      </c>
+      <c r="F21" t="str">
+        <v>Test@1234</v>
+      </c>
+      <c r="G21" t="str">
+        <v>tenant4_greenfield</v>
+      </c>
+      <c r="H21" t="str">
+        <v>+9198101019</v>
+      </c>
+      <c r="I21" t="str">
+        <v>B-104</v>
+      </c>
+      <c r="J21" t="str">
+        <v>Active</v>
+      </c>
+      <c r="K21" t="str">
+        <v>Raise complaints, pay invoices, book amenities, create guest visitor passes.</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>22</v>
+      </c>
+      <c r="B22" t="str">
+        <v>Greenfield Heights Community</v>
+      </c>
+      <c r="C22" t="str">
+        <v>Resident Tenant</v>
+      </c>
+      <c r="D22" t="str">
+        <v>Rajesh Banerjee</v>
+      </c>
+      <c r="E22" t="str">
+        <v>tenant5@greenfield.com</v>
+      </c>
+      <c r="F22" t="str">
+        <v>Test@1234</v>
+      </c>
+      <c r="G22" t="str">
+        <v>tenant5_greenfield</v>
+      </c>
+      <c r="H22" t="str">
+        <v>+9198101020</v>
+      </c>
+      <c r="I22" t="str">
+        <v>B-105</v>
+      </c>
+      <c r="J22" t="str">
+        <v>Active</v>
+      </c>
+      <c r="K22" t="str">
+        <v>Raise complaints, pay invoices, book amenities, create guest visitor passes.</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>23</v>
+      </c>
+      <c r="B23" t="str">
+        <v>Greenfield Heights Community</v>
+      </c>
+      <c r="C23" t="str">
+        <v>Resident Tenant</v>
+      </c>
+      <c r="D23" t="str">
+        <v>Kavya Patel</v>
+      </c>
+      <c r="E23" t="str">
+        <v>tenant6@greenfield.com</v>
+      </c>
+      <c r="F23" t="str">
+        <v>Test@1234</v>
+      </c>
+      <c r="G23" t="str">
+        <v>tenant6_greenfield</v>
+      </c>
+      <c r="H23" t="str">
+        <v>+9198101021</v>
+      </c>
+      <c r="I23" t="str">
+        <v>B-106</v>
+      </c>
+      <c r="J23" t="str">
+        <v>Active</v>
+      </c>
+      <c r="K23" t="str">
+        <v>Raise complaints, pay invoices, book amenities, create guest visitor passes.</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>24</v>
+      </c>
+      <c r="B24" t="str">
+        <v>Greenfield Heights Community</v>
+      </c>
+      <c r="C24" t="str">
+        <v>Resident Tenant</v>
+      </c>
+      <c r="D24" t="str">
+        <v>Ananya Banerjee</v>
+      </c>
+      <c r="E24" t="str">
+        <v>tenant7@greenfield.com</v>
+      </c>
+      <c r="F24" t="str">
+        <v>Test@1234</v>
+      </c>
+      <c r="G24" t="str">
+        <v>tenant7_greenfield</v>
+      </c>
+      <c r="H24" t="str">
+        <v>+9198101022</v>
+      </c>
+      <c r="I24" t="str">
+        <v>B-107</v>
+      </c>
+      <c r="J24" t="str">
+        <v>Active</v>
+      </c>
+      <c r="K24" t="str">
+        <v>Raise complaints, pay invoices, book amenities, create guest visitor passes.</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>25</v>
+      </c>
+      <c r="B25" t="str">
+        <v>Greenfield Heights Community</v>
+      </c>
+      <c r="C25" t="str">
+        <v>Resident Tenant</v>
+      </c>
+      <c r="D25" t="str">
+        <v>Vinay Banerjee</v>
+      </c>
+      <c r="E25" t="str">
+        <v>tenant8@greenfield.com</v>
+      </c>
+      <c r="F25" t="str">
+        <v>Test@1234</v>
+      </c>
+      <c r="G25" t="str">
+        <v>tenant8_greenfield</v>
+      </c>
+      <c r="H25" t="str">
+        <v>+9198101023</v>
+      </c>
+      <c r="I25" t="str">
+        <v>B-108</v>
+      </c>
+      <c r="J25" t="str">
+        <v>Active</v>
+      </c>
+      <c r="K25" t="str">
+        <v>Raise complaints, pay invoices, book amenities, create guest visitor passes.</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>26</v>
+      </c>
+      <c r="B26" t="str">
+        <v>Greenfield Heights Community</v>
+      </c>
+      <c r="C26" t="str">
+        <v>Resident Tenant</v>
+      </c>
+      <c r="D26" t="str">
+        <v>Divya Singh</v>
+      </c>
+      <c r="E26" t="str">
+        <v>tenant9@greenfield.com</v>
+      </c>
+      <c r="F26" t="str">
+        <v>Test@1234</v>
+      </c>
+      <c r="G26" t="str">
+        <v>tenant9_greenfield</v>
+      </c>
+      <c r="H26" t="str">
+        <v>+9198101024</v>
+      </c>
+      <c r="I26" t="str">
+        <v>B-109</v>
+      </c>
+      <c r="J26" t="str">
+        <v>Active</v>
+      </c>
+      <c r="K26" t="str">
+        <v>Raise complaints, pay invoices, book amenities, create guest visitor passes.</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>27</v>
+      </c>
+      <c r="B27" t="str">
+        <v>Greenfield Heights Community</v>
+      </c>
+      <c r="C27" t="str">
+        <v>Resident Tenant</v>
+      </c>
+      <c r="D27" t="str">
+        <v>Kavya Bose</v>
+      </c>
+      <c r="E27" t="str">
+        <v>tenant10@greenfield.com</v>
+      </c>
+      <c r="F27" t="str">
+        <v>Test@1234</v>
+      </c>
+      <c r="G27" t="str">
+        <v>tenant10_greenfield</v>
+      </c>
+      <c r="H27" t="str">
+        <v>+9198101025</v>
+      </c>
+      <c r="I27" t="str">
+        <v>B-110</v>
+      </c>
+      <c r="J27" t="str">
+        <v>Active</v>
+      </c>
+      <c r="K27" t="str">
+        <v>Raise complaints, pay invoices, book amenities, create guest visitor passes.</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>28</v>
+      </c>
+      <c r="B28" t="str">
+        <v>Greenfield Heights Community</v>
+      </c>
+      <c r="C28" t="str">
+        <v>Family Member</v>
+      </c>
+      <c r="D28" t="str">
+        <v>Farhan Pandey</v>
+      </c>
+      <c r="E28" t="str">
+        <v>family1@greenfield.com</v>
+      </c>
+      <c r="F28" t="str">
+        <v>Test@1234</v>
+      </c>
+      <c r="G28" t="str">
+        <v>family1_greenfield</v>
+      </c>
+      <c r="H28" t="str">
+        <v>+9198101026</v>
+      </c>
+      <c r="I28" t="str">
+        <v>A-101</v>
+      </c>
+      <c r="J28" t="str">
+        <v>Active</v>
+      </c>
+      <c r="K28" t="str">
+        <v>View notices, view community events, raise quick complaints.</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>29</v>
+      </c>
+      <c r="B29" t="str">
+        <v>Greenfield Heights Community</v>
+      </c>
+      <c r="C29" t="str">
+        <v>Family Member</v>
+      </c>
+      <c r="D29" t="str">
+        <v>Varun Ghosh</v>
+      </c>
+      <c r="E29" t="str">
+        <v>family2@greenfield.com</v>
+      </c>
+      <c r="F29" t="str">
+        <v>Test@1234</v>
+      </c>
+      <c r="G29" t="str">
+        <v>family2_greenfield</v>
+      </c>
+      <c r="H29" t="str">
+        <v>+9198101027</v>
+      </c>
+      <c r="I29" t="str">
+        <v>A-102</v>
+      </c>
+      <c r="J29" t="str">
+        <v>Active</v>
+      </c>
+      <c r="K29" t="str">
+        <v>View notices, view community events, raise quick complaints.</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>30</v>
+      </c>
+      <c r="B30" t="str">
+        <v>Greenfield Heights Community</v>
+      </c>
+      <c r="C30" t="str">
+        <v>Family Member</v>
+      </c>
+      <c r="D30" t="str">
+        <v>Nisha Rao</v>
+      </c>
+      <c r="E30" t="str">
+        <v>family3@greenfield.com</v>
+      </c>
+      <c r="F30" t="str">
+        <v>Test@1234</v>
+      </c>
+      <c r="G30" t="str">
+        <v>family3_greenfield</v>
+      </c>
+      <c r="H30" t="str">
+        <v>+9198101028</v>
+      </c>
+      <c r="I30" t="str">
+        <v>A-103</v>
+      </c>
+      <c r="J30" t="str">
+        <v>Active</v>
+      </c>
+      <c r="K30" t="str">
+        <v>View notices, view community events, raise quick complaints.</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>31</v>
+      </c>
+      <c r="B31" t="str">
+        <v>Greenfield Heights Community</v>
+      </c>
+      <c r="C31" t="str">
+        <v>Family Member</v>
+      </c>
+      <c r="D31" t="str">
+        <v>Rajesh Nair</v>
+      </c>
+      <c r="E31" t="str">
+        <v>family4@greenfield.com</v>
+      </c>
+      <c r="F31" t="str">
+        <v>Test@1234</v>
+      </c>
+      <c r="G31" t="str">
+        <v>family4_greenfield</v>
+      </c>
+      <c r="H31" t="str">
+        <v>+9198101029</v>
+      </c>
+      <c r="I31" t="str">
+        <v>A-104</v>
+      </c>
+      <c r="J31" t="str">
+        <v>Active</v>
+      </c>
+      <c r="K31" t="str">
+        <v>View notices, view community events, raise quick complaints.</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K31"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:K21"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>S.No</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Community Name</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Role / Category</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Full Name</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Email / Login</v>
+      </c>
+      <c r="F1" t="str">
+        <v>Password</v>
+      </c>
+      <c r="G1" t="str">
+        <v>Username</v>
+      </c>
+      <c r="H1" t="str">
+        <v>Phone</v>
+      </c>
+      <c r="I1" t="str">
+        <v>Assigned Unit</v>
+      </c>
+      <c r="J1" t="str">
+        <v>Status</v>
+      </c>
+      <c r="K1" t="str">
+        <v>Key Testing Focus</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>32</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Sunrise Valley Estates</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Community Admin</v>
+      </c>
+      <c r="D2" t="str">
+        <v>Varun Pandey</v>
+      </c>
+      <c r="E2" t="str">
+        <v>admin1@sunrisevalley.com</v>
+      </c>
+      <c r="F2" t="str">
+        <v>Test@1234</v>
+      </c>
+      <c r="G2" t="str">
+        <v>admin1_sunrise</v>
+      </c>
+      <c r="H2" t="str">
+        <v>+9198201000</v>
+      </c>
+      <c r="I2" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="J2" t="str">
+        <v>Active</v>
+      </c>
+      <c r="K2" t="str">
+        <v>Full Admin controls, user setup, billing, complaints assignment, notice publishing.</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>33</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Sunrise Valley Estates</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Facility Manager</v>
+      </c>
+      <c r="D3" t="str">
+        <v>Neeraj Kapoor</v>
+      </c>
+      <c r="E3" t="str">
+        <v>fm1@sunrisevalley.com</v>
+      </c>
+      <c r="F3" t="str">
+        <v>Test@1234</v>
+      </c>
+      <c r="G3" t="str">
+        <v>fm1_sunrise</v>
+      </c>
+      <c r="H3" t="str">
+        <v>+9198201001</v>
+      </c>
+      <c r="I3" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="J3" t="str">
+        <v>Active</v>
+      </c>
+      <c r="K3" t="str">
+        <v>Amenity scheduling, maintenance slots, ticket updates, facility inspection.</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>34</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Sunrise Valley Estates</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Security Guard</v>
+      </c>
+      <c r="D4" t="str">
+        <v>Farhan Choudhury</v>
+      </c>
+      <c r="E4" t="str">
+        <v>guard1@sunrisevalley.com</v>
+      </c>
+      <c r="F4" t="str">
+        <v>Test@1234</v>
+      </c>
+      <c r="G4" t="str">
+        <v>guard1_sunrise</v>
+      </c>
+      <c r="H4" t="str">
+        <v>+9198201002</v>
+      </c>
+      <c r="I4" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="J4" t="str">
+        <v>Active</v>
+      </c>
+      <c r="K4" t="str">
+        <v>Gate entry/exit scanner, visitor verification, passcode validation.</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>35</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Sunrise Valley Estates</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Security Guard</v>
+      </c>
+      <c r="D5" t="str">
+        <v>Dev Mishra</v>
+      </c>
+      <c r="E5" t="str">
+        <v>guard2@sunrisevalley.com</v>
+      </c>
+      <c r="F5" t="str">
+        <v>Test@1234</v>
+      </c>
+      <c r="G5" t="str">
+        <v>guard2_sunrise</v>
+      </c>
+      <c r="H5" t="str">
+        <v>+9198201003</v>
+      </c>
+      <c r="I5" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="J5" t="str">
+        <v>Active</v>
+      </c>
+      <c r="K5" t="str">
+        <v>Gate entry/exit scanner, visitor verification, passcode validation.</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>36</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Sunrise Valley Estates</v>
+      </c>
+      <c r="C6" t="str">
+        <v>Resident Owner</v>
+      </c>
+      <c r="D6" t="str">
+        <v>Dev Singh</v>
+      </c>
+      <c r="E6" t="str">
+        <v>owner1@sunrisevalley.com</v>
+      </c>
+      <c r="F6" t="str">
+        <v>Test@1234</v>
+      </c>
+      <c r="G6" t="str">
+        <v>owner1_sunrise</v>
+      </c>
+      <c r="H6" t="str">
+        <v>+9198201004</v>
+      </c>
+      <c r="I6" t="str">
+        <v>P1-01</v>
+      </c>
+      <c r="J6" t="str">
+        <v>Active</v>
+      </c>
+      <c r="K6" t="str">
+        <v>Financial dashboard, tenant arrears, visitor pass generation, amenity booking.</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>37</v>
+      </c>
+      <c r="B7" t="str">
+        <v>Sunrise Valley Estates</v>
+      </c>
+      <c r="C7" t="str">
+        <v>Resident Owner</v>
+      </c>
+      <c r="D7" t="str">
+        <v>Sahil Agarwal</v>
+      </c>
+      <c r="E7" t="str">
+        <v>owner2@sunrisevalley.com</v>
+      </c>
+      <c r="F7" t="str">
+        <v>Test@1234</v>
+      </c>
+      <c r="G7" t="str">
+        <v>owner2_sunrise</v>
+      </c>
+      <c r="H7" t="str">
+        <v>+9198201005</v>
+      </c>
+      <c r="I7" t="str">
+        <v>P1-02</v>
+      </c>
+      <c r="J7" t="str">
+        <v>Active</v>
+      </c>
+      <c r="K7" t="str">
+        <v>Financial dashboard, tenant arrears, visitor pass generation, amenity booking.</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>38</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Sunrise Valley Estates</v>
+      </c>
+      <c r="C8" t="str">
+        <v>Resident Owner</v>
+      </c>
+      <c r="D8" t="str">
+        <v>Vinay Agarwal</v>
+      </c>
+      <c r="E8" t="str">
+        <v>owner3@sunrisevalley.com</v>
+      </c>
+      <c r="F8" t="str">
+        <v>Test@1234</v>
+      </c>
+      <c r="G8" t="str">
+        <v>owner3_sunrise</v>
+      </c>
+      <c r="H8" t="str">
+        <v>+9198201006</v>
+      </c>
+      <c r="I8" t="str">
+        <v>P1-03</v>
+      </c>
+      <c r="J8" t="str">
+        <v>Active</v>
+      </c>
+      <c r="K8" t="str">
+        <v>Financial dashboard, tenant arrears, visitor pass generation, amenity booking.</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>39</v>
+      </c>
+      <c r="B9" t="str">
+        <v>Sunrise Valley Estates</v>
+      </c>
+      <c r="C9" t="str">
+        <v>Resident Owner</v>
+      </c>
+      <c r="D9" t="str">
+        <v>Aarav Desai</v>
+      </c>
+      <c r="E9" t="str">
+        <v>owner4@sunrisevalley.com</v>
+      </c>
+      <c r="F9" t="str">
+        <v>Test@1234</v>
+      </c>
+      <c r="G9" t="str">
+        <v>owner4_sunrise</v>
+      </c>
+      <c r="H9" t="str">
+        <v>+9198201007</v>
+      </c>
+      <c r="I9" t="str">
+        <v>P1-04</v>
+      </c>
+      <c r="J9" t="str">
+        <v>Active</v>
+      </c>
+      <c r="K9" t="str">
+        <v>Financial dashboard, tenant arrears, visitor pass generation, amenity booking.</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>40</v>
+      </c>
+      <c r="B10" t="str">
+        <v>Sunrise Valley Estates</v>
+      </c>
+      <c r="C10" t="str">
+        <v>Resident Owner</v>
+      </c>
+      <c r="D10" t="str">
+        <v>Siddharth Shah</v>
+      </c>
+      <c r="E10" t="str">
+        <v>owner5@sunrisevalley.com</v>
+      </c>
+      <c r="F10" t="str">
+        <v>Test@1234</v>
+      </c>
+      <c r="G10" t="str">
+        <v>owner5_sunrise</v>
+      </c>
+      <c r="H10" t="str">
+        <v>+9198201008</v>
+      </c>
+      <c r="I10" t="str">
+        <v>P1-05</v>
+      </c>
+      <c r="J10" t="str">
+        <v>Active</v>
+      </c>
+      <c r="K10" t="str">
+        <v>Financial dashboard, tenant arrears, visitor pass generation, amenity booking.</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>41</v>
+      </c>
+      <c r="B11" t="str">
+        <v>Sunrise Valley Estates</v>
+      </c>
+      <c r="C11" t="str">
+        <v>Resident Owner</v>
+      </c>
+      <c r="D11" t="str">
+        <v>Kavya Singh</v>
+      </c>
+      <c r="E11" t="str">
+        <v>owner6@sunrisevalley.com</v>
+      </c>
+      <c r="F11" t="str">
+        <v>Test@1234</v>
+      </c>
+      <c r="G11" t="str">
+        <v>owner6_sunrise</v>
+      </c>
+      <c r="H11" t="str">
+        <v>+9198201009</v>
+      </c>
+      <c r="I11" t="str">
+        <v>P1-06</v>
+      </c>
+      <c r="J11" t="str">
+        <v>Active</v>
+      </c>
+      <c r="K11" t="str">
+        <v>Financial dashboard, tenant arrears, visitor pass generation, amenity booking.</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>42</v>
+      </c>
+      <c r="B12" t="str">
+        <v>Sunrise Valley Estates</v>
+      </c>
+      <c r="C12" t="str">
+        <v>Resident Owner</v>
+      </c>
+      <c r="D12" t="str">
+        <v>Nisha Bose</v>
+      </c>
+      <c r="E12" t="str">
+        <v>owner7@sunrisevalley.com</v>
+      </c>
+      <c r="F12" t="str">
+        <v>Test@1234</v>
+      </c>
+      <c r="G12" t="str">
+        <v>owner7_sunrise</v>
+      </c>
+      <c r="H12" t="str">
+        <v>+9198201010</v>
+      </c>
+      <c r="I12" t="str">
+        <v>P1-07</v>
+      </c>
+      <c r="J12" t="str">
+        <v>Active</v>
+      </c>
+      <c r="K12" t="str">
+        <v>Financial dashboard, tenant arrears, visitor pass generation, amenity booking.</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>43</v>
+      </c>
+      <c r="B13" t="str">
+        <v>Sunrise Valley Estates</v>
+      </c>
+      <c r="C13" t="str">
+        <v>Resident Tenant</v>
+      </c>
+      <c r="D13" t="str">
+        <v>Tanvi Pillai</v>
+      </c>
+      <c r="E13" t="str">
+        <v>tenant1@sunrisevalley.com</v>
+      </c>
+      <c r="F13" t="str">
+        <v>Test@1234</v>
+      </c>
+      <c r="G13" t="str">
+        <v>tenant1_sunrise</v>
+      </c>
+      <c r="H13" t="str">
+        <v>+9198201011</v>
+      </c>
+      <c r="I13" t="str">
+        <v>P1-08</v>
+      </c>
+      <c r="J13" t="str">
+        <v>Active</v>
+      </c>
+      <c r="K13" t="str">
+        <v>Raise complaints, pay invoices, book amenities, create guest visitor passes.</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>44</v>
+      </c>
+      <c r="B14" t="str">
+        <v>Sunrise Valley Estates</v>
+      </c>
+      <c r="C14" t="str">
+        <v>Resident Tenant</v>
+      </c>
+      <c r="D14" t="str">
+        <v>Ananya Jain</v>
+      </c>
+      <c r="E14" t="str">
+        <v>tenant2@sunrisevalley.com</v>
+      </c>
+      <c r="F14" t="str">
+        <v>Test@1234</v>
+      </c>
+      <c r="G14" t="str">
+        <v>tenant2_sunrise</v>
+      </c>
+      <c r="H14" t="str">
+        <v>+9198201012</v>
+      </c>
+      <c r="I14" t="str">
+        <v>P1-09</v>
+      </c>
+      <c r="J14" t="str">
+        <v>Active</v>
+      </c>
+      <c r="K14" t="str">
+        <v>Raise complaints, pay invoices, book amenities, create guest visitor passes.</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>45</v>
+      </c>
+      <c r="B15" t="str">
+        <v>Sunrise Valley Estates</v>
+      </c>
+      <c r="C15" t="str">
+        <v>Resident Tenant</v>
+      </c>
+      <c r="D15" t="str">
+        <v>Deepa Shah</v>
+      </c>
+      <c r="E15" t="str">
+        <v>tenant3@sunrisevalley.com</v>
+      </c>
+      <c r="F15" t="str">
+        <v>Test@1234</v>
+      </c>
+      <c r="G15" t="str">
+        <v>tenant3_sunrise</v>
+      </c>
+      <c r="H15" t="str">
+        <v>+9198201013</v>
+      </c>
+      <c r="I15" t="str">
+        <v>P1-10</v>
+      </c>
+      <c r="J15" t="str">
+        <v>Active</v>
+      </c>
+      <c r="K15" t="str">
+        <v>Raise complaints, pay invoices, book amenities, create guest visitor passes.</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>46</v>
+      </c>
+      <c r="B16" t="str">
+        <v>Sunrise Valley Estates</v>
+      </c>
+      <c r="C16" t="str">
+        <v>Resident Tenant</v>
+      </c>
+      <c r="D16" t="str">
+        <v>Pooja Kumar</v>
+      </c>
+      <c r="E16" t="str">
+        <v>tenant4@sunrisevalley.com</v>
+      </c>
+      <c r="F16" t="str">
+        <v>Test@1234</v>
+      </c>
+      <c r="G16" t="str">
+        <v>tenant4_sunrise</v>
+      </c>
+      <c r="H16" t="str">
+        <v>+9198201014</v>
+      </c>
+      <c r="I16" t="str">
+        <v>P2-01</v>
+      </c>
+      <c r="J16" t="str">
+        <v>Active</v>
+      </c>
+      <c r="K16" t="str">
+        <v>Raise complaints, pay invoices, book amenities, create guest visitor passes.</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>47</v>
+      </c>
+      <c r="B17" t="str">
+        <v>Sunrise Valley Estates</v>
+      </c>
+      <c r="C17" t="str">
+        <v>Resident Tenant</v>
+      </c>
+      <c r="D17" t="str">
+        <v>Rohit Patel</v>
+      </c>
+      <c r="E17" t="str">
+        <v>tenant5@sunrisevalley.com</v>
+      </c>
+      <c r="F17" t="str">
+        <v>Test@1234</v>
+      </c>
+      <c r="G17" t="str">
+        <v>tenant5_sunrise</v>
+      </c>
+      <c r="H17" t="str">
+        <v>+9198201015</v>
+      </c>
+      <c r="I17" t="str">
+        <v>P2-02</v>
+      </c>
+      <c r="J17" t="str">
+        <v>Active</v>
+      </c>
+      <c r="K17" t="str">
+        <v>Raise complaints, pay invoices, book amenities, create guest visitor passes.</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>48</v>
+      </c>
+      <c r="B18" t="str">
+        <v>Sunrise Valley Estates</v>
+      </c>
+      <c r="C18" t="str">
+        <v>Resident Tenant</v>
+      </c>
+      <c r="D18" t="str">
+        <v>Lakshmi Sharma</v>
+      </c>
+      <c r="E18" t="str">
+        <v>tenant6@sunrisevalley.com</v>
+      </c>
+      <c r="F18" t="str">
+        <v>Test@1234</v>
+      </c>
+      <c r="G18" t="str">
+        <v>tenant6_sunrise</v>
+      </c>
+      <c r="H18" t="str">
+        <v>+9198201016</v>
+      </c>
+      <c r="I18" t="str">
+        <v>P2-03</v>
+      </c>
+      <c r="J18" t="str">
+        <v>Active</v>
+      </c>
+      <c r="K18" t="str">
+        <v>Raise complaints, pay invoices, book amenities, create guest visitor passes.</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>49</v>
+      </c>
+      <c r="B19" t="str">
+        <v>Sunrise Valley Estates</v>
+      </c>
+      <c r="C19" t="str">
+        <v>Resident Tenant</v>
+      </c>
+      <c r="D19" t="str">
+        <v>Aarav Sinha</v>
+      </c>
+      <c r="E19" t="str">
+        <v>tenant7@sunrisevalley.com</v>
+      </c>
+      <c r="F19" t="str">
+        <v>Test@1234</v>
+      </c>
+      <c r="G19" t="str">
+        <v>tenant7_sunrise</v>
+      </c>
+      <c r="H19" t="str">
+        <v>+9198201017</v>
+      </c>
+      <c r="I19" t="str">
+        <v>P2-04</v>
+      </c>
+      <c r="J19" t="str">
+        <v>Active</v>
+      </c>
+      <c r="K19" t="str">
+        <v>Raise complaints, pay invoices, book amenities, create guest visitor passes.</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>50</v>
+      </c>
+      <c r="B20" t="str">
+        <v>Sunrise Valley Estates</v>
+      </c>
+      <c r="C20" t="str">
+        <v>Family Member</v>
+      </c>
+      <c r="D20" t="str">
+        <v>Zara Joshi</v>
+      </c>
+      <c r="E20" t="str">
+        <v>family1@sunrisevalley.com</v>
+      </c>
+      <c r="F20" t="str">
+        <v>Test@1234</v>
+      </c>
+      <c r="G20" t="str">
+        <v>family1_sunrise</v>
+      </c>
+      <c r="H20" t="str">
+        <v>+9198201018</v>
+      </c>
+      <c r="I20" t="str">
+        <v>P1-01</v>
+      </c>
+      <c r="J20" t="str">
+        <v>Active</v>
+      </c>
+      <c r="K20" t="str">
+        <v>View notices, view community events, raise quick complaints.</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>51</v>
+      </c>
+      <c r="B21" t="str">
+        <v>Sunrise Valley Estates</v>
+      </c>
+      <c r="C21" t="str">
+        <v>Family Member</v>
+      </c>
+      <c r="D21" t="str">
+        <v>Jaya Kumar</v>
+      </c>
+      <c r="E21" t="str">
+        <v>family2@sunrisevalley.com</v>
+      </c>
+      <c r="F21" t="str">
+        <v>Test@1234</v>
+      </c>
+      <c r="G21" t="str">
+        <v>family2_sunrise</v>
+      </c>
+      <c r="H21" t="str">
+        <v>+9198201019</v>
+      </c>
+      <c r="I21" t="str">
+        <v>P1-02</v>
+      </c>
+      <c r="J21" t="str">
+        <v>Active</v>
+      </c>
+      <c r="K21" t="str">
+        <v>View notices, view community events, raise quick complaints.</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:K21"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:K16"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>S.No</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Community Name</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Role / Category</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Full Name</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Email / Login</v>
+      </c>
+      <c r="F1" t="str">
+        <v>Password</v>
+      </c>
+      <c r="G1" t="str">
+        <v>Username</v>
+      </c>
+      <c r="H1" t="str">
+        <v>Phone</v>
+      </c>
+      <c r="I1" t="str">
+        <v>Assigned Unit</v>
+      </c>
+      <c r="J1" t="str">
+        <v>Status</v>
+      </c>
+      <c r="K1" t="str">
+        <v>Key Testing Focus</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>52</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Palm Meadows Residency</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Community Admin</v>
+      </c>
+      <c r="D2" t="str">
+        <v>Rajesh Kapoor</v>
+      </c>
+      <c r="E2" t="str">
+        <v>admin1@palmmeadows.com</v>
+      </c>
+      <c r="F2" t="str">
+        <v>Test@1234</v>
+      </c>
+      <c r="G2" t="str">
+        <v>admin1_palm</v>
+      </c>
+      <c r="H2" t="str">
+        <v>+9198301000</v>
+      </c>
+      <c r="I2" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="J2" t="str">
+        <v>Active</v>
+      </c>
+      <c r="K2" t="str">
+        <v>Full Admin controls, user setup, billing, complaints assignment, notice publishing.</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>53</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Palm Meadows Residency</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Facility Manager</v>
+      </c>
+      <c r="D3" t="str">
+        <v>Zara Iyer</v>
+      </c>
+      <c r="E3" t="str">
+        <v>fm1@palmmeadows.com</v>
+      </c>
+      <c r="F3" t="str">
+        <v>Test@1234</v>
+      </c>
+      <c r="G3" t="str">
+        <v>fm1_palm</v>
+      </c>
+      <c r="H3" t="str">
+        <v>+9198301001</v>
+      </c>
+      <c r="I3" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="J3" t="str">
+        <v>Active</v>
+      </c>
+      <c r="K3" t="str">
+        <v>Amenity scheduling, maintenance slots, ticket updates, facility inspection.</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>54</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Palm Meadows Residency</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Security Guard</v>
+      </c>
+      <c r="D4" t="str">
+        <v>Neeraj Menon</v>
+      </c>
+      <c r="E4" t="str">
+        <v>guard1@palmmeadows.com</v>
+      </c>
+      <c r="F4" t="str">
+        <v>Test@1234</v>
+      </c>
+      <c r="G4" t="str">
+        <v>guard1_palm</v>
+      </c>
+      <c r="H4" t="str">
+        <v>+9198301002</v>
+      </c>
+      <c r="I4" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="J4" t="str">
+        <v>Active</v>
+      </c>
+      <c r="K4" t="str">
+        <v>Gate entry/exit scanner, visitor verification, passcode validation.</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>55</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Palm Meadows Residency</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Resident Owner</v>
+      </c>
+      <c r="D5" t="str">
+        <v>Usha Rao</v>
+      </c>
+      <c r="E5" t="str">
+        <v>owner1@palmmeadows.com</v>
+      </c>
+      <c r="F5" t="str">
+        <v>Test@1234</v>
+      </c>
+      <c r="G5" t="str">
+        <v>owner1_palm</v>
+      </c>
+      <c r="H5" t="str">
+        <v>+9198301003</v>
+      </c>
+      <c r="I5" t="str">
+        <v>T1-101</v>
+      </c>
+      <c r="J5" t="str">
+        <v>Active</v>
+      </c>
+      <c r="K5" t="str">
+        <v>Financial dashboard, tenant arrears, visitor pass generation, amenity booking.</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>56</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Palm Meadows Residency</v>
+      </c>
+      <c r="C6" t="str">
+        <v>Resident Owner</v>
+      </c>
+      <c r="D6" t="str">
+        <v>Sahil Chauhan</v>
+      </c>
+      <c r="E6" t="str">
+        <v>owner2@palmmeadows.com</v>
+      </c>
+      <c r="F6" t="str">
+        <v>Test@1234</v>
+      </c>
+      <c r="G6" t="str">
+        <v>owner2_palm</v>
+      </c>
+      <c r="H6" t="str">
+        <v>+9198301004</v>
+      </c>
+      <c r="I6" t="str">
+        <v>T1-102</v>
+      </c>
+      <c r="J6" t="str">
+        <v>Active</v>
+      </c>
+      <c r="K6" t="str">
+        <v>Financial dashboard, tenant arrears, visitor pass generation, amenity booking.</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>57</v>
+      </c>
+      <c r="B7" t="str">
+        <v>Palm Meadows Residency</v>
+      </c>
+      <c r="C7" t="str">
+        <v>Resident Owner</v>
+      </c>
+      <c r="D7" t="str">
+        <v>Seema Banerjee</v>
+      </c>
+      <c r="E7" t="str">
+        <v>owner3@palmmeadows.com</v>
+      </c>
+      <c r="F7" t="str">
+        <v>Test@1234</v>
+      </c>
+      <c r="G7" t="str">
+        <v>owner3_palm</v>
+      </c>
+      <c r="H7" t="str">
+        <v>+9198301005</v>
+      </c>
+      <c r="I7" t="str">
+        <v>T1-103</v>
+      </c>
+      <c r="J7" t="str">
+        <v>Active</v>
+      </c>
+      <c r="K7" t="str">
+        <v>Financial dashboard, tenant arrears, visitor pass generation, amenity booking.</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>58</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Palm Meadows Residency</v>
+      </c>
+      <c r="C8" t="str">
+        <v>Resident Owner</v>
+      </c>
+      <c r="D8" t="str">
+        <v>Tushar Sinha</v>
+      </c>
+      <c r="E8" t="str">
+        <v>owner4@palmmeadows.com</v>
+      </c>
+      <c r="F8" t="str">
+        <v>Test@1234</v>
+      </c>
+      <c r="G8" t="str">
+        <v>owner4_palm</v>
+      </c>
+      <c r="H8" t="str">
+        <v>+9198301006</v>
+      </c>
+      <c r="I8" t="str">
+        <v>T1-104</v>
+      </c>
+      <c r="J8" t="str">
+        <v>Active</v>
+      </c>
+      <c r="K8" t="str">
+        <v>Financial dashboard, tenant arrears, visitor pass generation, amenity booking.</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>59</v>
+      </c>
+      <c r="B9" t="str">
+        <v>Palm Meadows Residency</v>
+      </c>
+      <c r="C9" t="str">
+        <v>Resident Owner</v>
+      </c>
+      <c r="D9" t="str">
+        <v>Shiv Shah</v>
+      </c>
+      <c r="E9" t="str">
+        <v>owner5@palmmeadows.com</v>
+      </c>
+      <c r="F9" t="str">
+        <v>Test@1234</v>
+      </c>
+      <c r="G9" t="str">
+        <v>owner5_palm</v>
+      </c>
+      <c r="H9" t="str">
+        <v>+9198301007</v>
+      </c>
+      <c r="I9" t="str">
+        <v>T1-105</v>
+      </c>
+      <c r="J9" t="str">
+        <v>Active</v>
+      </c>
+      <c r="K9" t="str">
+        <v>Financial dashboard, tenant arrears, visitor pass generation, amenity booking.</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>60</v>
+      </c>
+      <c r="B10" t="str">
+        <v>Palm Meadows Residency</v>
+      </c>
+      <c r="C10" t="str">
+        <v>Resident Tenant</v>
+      </c>
+      <c r="D10" t="str">
+        <v>Siddharth Verma</v>
+      </c>
+      <c r="E10" t="str">
+        <v>tenant1@palmmeadows.com</v>
+      </c>
+      <c r="F10" t="str">
+        <v>Test@1234</v>
+      </c>
+      <c r="G10" t="str">
+        <v>tenant1_palm</v>
+      </c>
+      <c r="H10" t="str">
+        <v>+9198301008</v>
+      </c>
+      <c r="I10" t="str">
+        <v>T1-106</v>
+      </c>
+      <c r="J10" t="str">
+        <v>Active</v>
+      </c>
+      <c r="K10" t="str">
+        <v>Raise complaints, pay invoices, book amenities, create guest visitor passes.</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>61</v>
+      </c>
+      <c r="B11" t="str">
+        <v>Palm Meadows Residency</v>
+      </c>
+      <c r="C11" t="str">
+        <v>Resident Tenant</v>
+      </c>
+      <c r="D11" t="str">
+        <v>Simran Tiwari</v>
+      </c>
+      <c r="E11" t="str">
+        <v>tenant2@palmmeadows.com</v>
+      </c>
+      <c r="F11" t="str">
+        <v>Test@1234</v>
+      </c>
+      <c r="G11" t="str">
+        <v>tenant2_palm</v>
+      </c>
+      <c r="H11" t="str">
+        <v>+9198301009</v>
+      </c>
+      <c r="I11" t="str">
+        <v>T1-107</v>
+      </c>
+      <c r="J11" t="str">
+        <v>Active</v>
+      </c>
+      <c r="K11" t="str">
+        <v>Raise complaints, pay invoices, book amenities, create guest visitor passes.</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>62</v>
+      </c>
+      <c r="B12" t="str">
+        <v>Palm Meadows Residency</v>
+      </c>
+      <c r="C12" t="str">
+        <v>Resident Tenant</v>
+      </c>
+      <c r="D12" t="str">
+        <v>Priya Das</v>
+      </c>
+      <c r="E12" t="str">
+        <v>tenant3@palmmeadows.com</v>
+      </c>
+      <c r="F12" t="str">
+        <v>Test@1234</v>
+      </c>
+      <c r="G12" t="str">
+        <v>tenant3_palm</v>
+      </c>
+      <c r="H12" t="str">
+        <v>+9198301010</v>
+      </c>
+      <c r="I12" t="str">
+        <v>T1-108</v>
+      </c>
+      <c r="J12" t="str">
+        <v>Active</v>
+      </c>
+      <c r="K12" t="str">
+        <v>Raise complaints, pay invoices, book amenities, create guest visitor passes.</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>63</v>
+      </c>
+      <c r="B13" t="str">
+        <v>Palm Meadows Residency</v>
+      </c>
+      <c r="C13" t="str">
+        <v>Resident Tenant</v>
+      </c>
+      <c r="D13" t="str">
+        <v>Suresh Das</v>
+      </c>
+      <c r="E13" t="str">
+        <v>tenant4@palmmeadows.com</v>
+      </c>
+      <c r="F13" t="str">
+        <v>Test@1234</v>
+      </c>
+      <c r="G13" t="str">
+        <v>tenant4_palm</v>
+      </c>
+      <c r="H13" t="str">
+        <v>+9198301011</v>
+      </c>
+      <c r="I13" t="str">
+        <v>T2-101</v>
+      </c>
+      <c r="J13" t="str">
+        <v>Active</v>
+      </c>
+      <c r="K13" t="str">
+        <v>Raise complaints, pay invoices, book amenities, create guest visitor passes.</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>64</v>
+      </c>
+      <c r="B14" t="str">
+        <v>Palm Meadows Residency</v>
+      </c>
+      <c r="C14" t="str">
+        <v>Resident Tenant</v>
+      </c>
+      <c r="D14" t="str">
+        <v>Sangeeta Reddy</v>
+      </c>
+      <c r="E14" t="str">
+        <v>tenant5@palmmeadows.com</v>
+      </c>
+      <c r="F14" t="str">
+        <v>Test@1234</v>
+      </c>
+      <c r="G14" t="str">
+        <v>tenant5_palm</v>
+      </c>
+      <c r="H14" t="str">
+        <v>+9198301012</v>
+      </c>
+      <c r="I14" t="str">
+        <v>T2-102</v>
+      </c>
+      <c r="J14" t="str">
+        <v>Active</v>
+      </c>
+      <c r="K14" t="str">
+        <v>Raise complaints, pay invoices, book amenities, create guest visitor passes.</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>65</v>
+      </c>
+      <c r="B15" t="str">
+        <v>Palm Meadows Residency</v>
+      </c>
+      <c r="C15" t="str">
+        <v>Family Member</v>
+      </c>
+      <c r="D15" t="str">
+        <v>Vishal Kumar</v>
+      </c>
+      <c r="E15" t="str">
+        <v>family1@palmmeadows.com</v>
+      </c>
+      <c r="F15" t="str">
+        <v>Test@1234</v>
+      </c>
+      <c r="G15" t="str">
+        <v>family1_palm</v>
+      </c>
+      <c r="H15" t="str">
+        <v>+9198301013</v>
+      </c>
+      <c r="I15" t="str">
+        <v>T1-101</v>
+      </c>
+      <c r="J15" t="str">
+        <v>Active</v>
+      </c>
+      <c r="K15" t="str">
+        <v>View notices, view community events, raise quick complaints.</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>66</v>
+      </c>
+      <c r="B16" t="str">
+        <v>Palm Meadows Residency</v>
+      </c>
+      <c r="C16" t="str">
+        <v>Family Member</v>
+      </c>
+      <c r="D16" t="str">
+        <v>Arjun Rao</v>
+      </c>
+      <c r="E16" t="str">
+        <v>family2@palmmeadows.com</v>
+      </c>
+      <c r="F16" t="str">
+        <v>Test@1234</v>
+      </c>
+      <c r="G16" t="str">
+        <v>family2_palm</v>
+      </c>
+      <c r="H16" t="str">
+        <v>+9198301014</v>
+      </c>
+      <c r="I16" t="str">
+        <v>T1-102</v>
+      </c>
+      <c r="J16" t="str">
+        <v>Active</v>
+      </c>
+      <c r="K16" t="str">
+        <v>View notices, view community events, raise quick complaints.</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:K16"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C8"/>
+  <cols>
+    <col min="1" max="1" width="20.83203125" customWidth="1"/>
+    <col min="2" max="2" width="20.83203125" customWidth="1"/>
+    <col min="3" max="3" width="80.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Role Name</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Level</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Permissions</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>Super Admin</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Global Platform</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Full unrestricted access across all organizations and system settings.</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>Community Admin</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Community Level</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Full admin access to User Management, Roles, Billing, Complaints, Amenities, Notices, Integrations.</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>Facility Manager</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Community Level</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Manage Amenities, Maintenance schedules, Complaint assignment &amp; progress tracking, Notice board.</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>Security Guard</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Gate Control</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Gate entry/exit scanner, Visitor pass passcode verification, Security logs, read Notices.</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>Resident Owner</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Resident Level</v>
+      </c>
+      <c r="C6" t="str">
+        <v>View own financials &amp; tenant arrears, Pay invoices, Book amenities, Generate guest passes, Raise complaints.</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>Resident Tenant</v>
+      </c>
+      <c r="B7" t="str">
+        <v>Resident Level</v>
+      </c>
+      <c r="C7" t="str">
+        <v>View &amp; pay rental/unit invoices, Book amenities, Generate guest visitor passes, Submit complaints.</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>Family Member</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Resident Level</v>
+      </c>
+      <c r="C8" t="str">
+        <v>View community notices, view events, submit quick maintenance requests.</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C8"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D9"/>
+  <cols>
+    <col min="1" max="1" width="14.83203125" customWidth="1"/>
+    <col min="2" max="2" width="20.83203125" customWidth="1"/>
+    <col min="3" max="3" width="30.83203125" customWidth="1"/>
+    <col min="4" max="4" width="90.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
         <v>Scenario ID</v>
       </c>
       <c r="B1" t="str">
-        <v>Target Role</v>
+        <v>Actor</v>
       </c>
       <c r="C1" t="str">
-        <v>Feature Tested</v>
+        <v>Target Feature</v>
       </c>
       <c r="D1" t="str">
-        <v>Action Steps</v>
+        <v>Step-by-Step Test Procedure</v>
       </c>
     </row>
     <row r="2" xml:space="preserve">
@@ -716,16 +5316,16 @@
         <v>SCEN-001</v>
       </c>
       <c r="B2" t="str">
-        <v>Community Admin</v>
+        <v>Super Admin</v>
       </c>
       <c r="C2" t="str">
-        <v>Admin Ledger &amp; Verification</v>
+        <v>Platform Multi-Community Switch</v>
       </c>
       <c r="D2" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Login as admin.
-2. Navigate to "Billing" tab.
-3. Observe overall KPIs matching database entries.
-4. Search for Villa B-201 and click "Settle" or "Mark Paid" to reconcile Cheque reference CHQ-118274.</v>
+        <v xml:space="preserve">1. Login with admin@enterprise.com / SuperAdminPwd@123.
+2. Open workspace dropdown in header.
+3. Verify all 3 communities (Greenfield Heights, Sunrise Valley, Palm Meadows) are listed.
+4. Switch workspace and verify context changes.</v>
       </c>
     </row>
     <row r="3" xml:space="preserve">
@@ -733,16 +5333,16 @@
         <v>SCEN-002</v>
       </c>
       <c r="B3" t="str">
-        <v>Resident Owner (owner1)</v>
+        <v>Community Admin</v>
       </c>
       <c r="C3" t="str">
-        <v>My Financials &amp; Tenant Arrears</v>
+        <v>Community Dashboard &amp; Users</v>
       </c>
       <c r="D3" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Login as owner1.
-2. Go to "My Financials" / Resident Action Center.
-3. Check outstanding balance of ₹5,000.
-4. Look at Tenant Arrears list to see Tenant 2 (Aisha) with ₹7,000 in Pending status.</v>
+        <v xml:space="preserve">1. Login with admin1@greenfield.com / Test@1234.
+2. Navigate to User Management.
+3. Verify members list and active roles.
+4. Create a new member or modify roles.</v>
       </c>
     </row>
     <row r="4" xml:space="preserve">
@@ -750,22 +5350,203 @@
         <v>SCEN-003</v>
       </c>
       <c r="B4" t="str">
-        <v>Resident Tenant (tenant1)</v>
+        <v>Facility Manager</v>
       </c>
       <c r="C4" t="str">
-        <v>Outstanding Balance &amp; Pay Now Trigger</v>
+        <v>Amenity Booking Approval</v>
       </c>
       <c r="D4" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Login as tenant1.
-2. Go to "My Financials".
-3. Check outstanding balance of ₹7,000.
-4. Click "Pay Now" and enter a reference code (e.g. "TXN-8827A") to submit settlement.
-5. Log back as admin and verify if status changes to VERIFICATION_PENDING with reference.</v>
+        <v xml:space="preserve">1. Login with fm1@greenfield.com / Test@1234.
+2. Open Amenities tab.
+3. View pending bookings for Banquet Hall.
+4. Click Approve or Reject.
+5. Verify status updates to Confirmed.</v>
+      </c>
+    </row>
+    <row r="5" xml:space="preserve">
+      <c r="A5" t="str">
+        <v>SCEN-004</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Facility Manager</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Complaint Ticket Assignment</v>
+      </c>
+      <c r="D5" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Login with fm1@sunrisevalley.com / Test@1234.
+2. Go to Complaints.
+3. Filter by Open status.
+4. Assign ticket to staff.
+5. Update status to In Progress.</v>
+      </c>
+    </row>
+    <row r="6" xml:space="preserve">
+      <c r="A6" t="str">
+        <v>SCEN-005</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Security Guard</v>
+      </c>
+      <c r="C6" t="str">
+        <v>Gate Visitor Verification</v>
+      </c>
+      <c r="D6" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Login with guard1@greenfield.com / Test@1234.
+2. Open Visitor Log / Guard Portal.
+3. Enter passcode GHC8899.
+4. Click Log Entry (INSIDE).
+5. Confirm visitor record updates.</v>
+      </c>
+    </row>
+    <row r="7" xml:space="preserve">
+      <c r="A7" t="str">
+        <v>SCEN-006</v>
+      </c>
+      <c r="B7" t="str">
+        <v>Resident Owner</v>
+      </c>
+      <c r="C7" t="str">
+        <v>Financials &amp; Tenant Arrears</v>
+      </c>
+      <c r="D7" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Login with owner1@greenfield.com / Test@1234.
+2. Open My Financials.
+3. View maintenance invoice balance.
+4. Check Tenant Arrears tab to see tenant status.</v>
+      </c>
+    </row>
+    <row r="8" xml:space="preserve">
+      <c r="A8" t="str">
+        <v>SCEN-007</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Resident Tenant</v>
+      </c>
+      <c r="C8" t="str">
+        <v>Invoice Settlement &amp; Pass Creation</v>
+      </c>
+      <c r="D8" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Login with tenant1@palmmeadows.com / Test@1234.
+2. Navigate to My Financials -&gt; Pay Invoice.
+3. Navigate to Visitor Passes -&gt; Create Pass for Guest.</v>
+      </c>
+    </row>
+    <row r="9" xml:space="preserve">
+      <c r="A9" t="str">
+        <v>SCEN-008</v>
+      </c>
+      <c r="B9" t="str">
+        <v>Resident Owner/Tenant</v>
+      </c>
+      <c r="C9" t="str">
+        <v>Amenity Slot Discovery &amp; Booking</v>
+      </c>
+      <c r="D9" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Login as owner1@sunrisevalley.com / Test@1234.
+2. Open Amenities -&gt; Discover.
+3. Select Tennis Court, pick tomorrow slot.
+4. Complete booking request.</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D9"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:B10"/>
+  <cols>
+    <col min="1" max="1" width="35.83203125" customWidth="1"/>
+    <col min="2" max="2" width="45.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Metric / Parameter</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Value</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>Total Communities Created</v>
+      </c>
+      <c r="B2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>Community 1</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Greenfield Heights Community (GHC)</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>Community 2</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Sunrise Valley Estates (SVE)</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>Community 3</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Palm Meadows Residency (PMR)</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>Total User Credentials Created</v>
+      </c>
+      <c r="B6">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>Super Admin Account</v>
+      </c>
+      <c r="B7" t="str">
+        <v>admin@enterprise.com (Password: SuperAdminPwd@123)</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>All Other Accounts Password</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Test@1234</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>Total Roles Configured per Org</v>
+      </c>
+      <c r="B9">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>Seed Execution Timestamp</v>
+      </c>
+      <c r="B10" t="str">
+        <v>2026-07-31T10:38:45.636Z</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:B10"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Community_Testing_Credentials.xlsx
+++ b/Community_Testing_Credentials.xlsx
@@ -467,10 +467,10 @@
         <v>Super Admin</v>
       </c>
       <c r="E2" t="str">
-        <v>admin@enterprise.com</v>
+        <v>admin@managemygate.com</v>
       </c>
       <c r="F2" t="str">
-        <v>SuperAdminPwd@123</v>
+        <v>password123</v>
       </c>
       <c r="G2" t="str">
         <v>superadmin</v>
@@ -499,7 +499,7 @@
         <v>Community Admin</v>
       </c>
       <c r="D3" t="str">
-        <v>Rohit Bose</v>
+        <v>Aarav Menon</v>
       </c>
       <c r="E3" t="str">
         <v>admin1@greenfield.com</v>
@@ -534,7 +534,7 @@
         <v>Community Admin</v>
       </c>
       <c r="D4" t="str">
-        <v>Harish Kumar</v>
+        <v>Rohit Gupta</v>
       </c>
       <c r="E4" t="str">
         <v>admin2@greenfield.com</v>
@@ -569,7 +569,7 @@
         <v>Facility Manager</v>
       </c>
       <c r="D5" t="str">
-        <v>Sanjay Kapoor</v>
+        <v>Rajesh Banerjee</v>
       </c>
       <c r="E5" t="str">
         <v>fm1@greenfield.com</v>
@@ -604,7 +604,7 @@
         <v>Facility Manager</v>
       </c>
       <c r="D6" t="str">
-        <v>Zara Sharma</v>
+        <v>Aarav Joshi</v>
       </c>
       <c r="E6" t="str">
         <v>fm2@greenfield.com</v>
@@ -639,7 +639,7 @@
         <v>Security Guard</v>
       </c>
       <c r="D7" t="str">
-        <v>Vikram Mehta</v>
+        <v>Tanvi Bhat</v>
       </c>
       <c r="E7" t="str">
         <v>guard1@greenfield.com</v>
@@ -674,7 +674,7 @@
         <v>Security Guard</v>
       </c>
       <c r="D8" t="str">
-        <v>Siddharth Gupta</v>
+        <v>Arjun Singh</v>
       </c>
       <c r="E8" t="str">
         <v>guard2@greenfield.com</v>
@@ -709,7 +709,7 @@
         <v>Resident Owner</v>
       </c>
       <c r="D9" t="str">
-        <v>Ishaan Sinha</v>
+        <v>Sanjay Sharma</v>
       </c>
       <c r="E9" t="str">
         <v>owner1@greenfield.com</v>
@@ -744,7 +744,7 @@
         <v>Resident Owner</v>
       </c>
       <c r="D10" t="str">
-        <v>Bhavna Shah</v>
+        <v>Akash Iyer</v>
       </c>
       <c r="E10" t="str">
         <v>owner2@greenfield.com</v>
@@ -779,7 +779,7 @@
         <v>Resident Owner</v>
       </c>
       <c r="D11" t="str">
-        <v>Aditi Ghosh</v>
+        <v>Arjun Desai</v>
       </c>
       <c r="E11" t="str">
         <v>owner3@greenfield.com</v>
@@ -814,7 +814,7 @@
         <v>Resident Owner</v>
       </c>
       <c r="D12" t="str">
-        <v>Rajesh Mehta</v>
+        <v>Yamini Bose</v>
       </c>
       <c r="E12" t="str">
         <v>owner4@greenfield.com</v>
@@ -849,7 +849,7 @@
         <v>Resident Owner</v>
       </c>
       <c r="D13" t="str">
-        <v>Siddharth Iyer</v>
+        <v>Tanvi Iyer</v>
       </c>
       <c r="E13" t="str">
         <v>owner5@greenfield.com</v>
@@ -884,7 +884,7 @@
         <v>Resident Owner</v>
       </c>
       <c r="D14" t="str">
-        <v>Rahul Patel</v>
+        <v>Rekha Mishra</v>
       </c>
       <c r="E14" t="str">
         <v>owner6@greenfield.com</v>
@@ -919,7 +919,7 @@
         <v>Resident Owner</v>
       </c>
       <c r="D15" t="str">
-        <v>Priya Verma</v>
+        <v>Ananya Iyer</v>
       </c>
       <c r="E15" t="str">
         <v>owner7@greenfield.com</v>
@@ -954,7 +954,7 @@
         <v>Resident Owner</v>
       </c>
       <c r="D16" t="str">
-        <v>Tanvi Shah</v>
+        <v>Rahul Verma</v>
       </c>
       <c r="E16" t="str">
         <v>owner8@greenfield.com</v>
@@ -989,7 +989,7 @@
         <v>Resident Owner</v>
       </c>
       <c r="D17" t="str">
-        <v>Jaya Mehta</v>
+        <v>Sanjay Mehta</v>
       </c>
       <c r="E17" t="str">
         <v>owner9@greenfield.com</v>
@@ -1024,7 +1024,7 @@
         <v>Resident Owner</v>
       </c>
       <c r="D18" t="str">
-        <v>Sahil Kumar</v>
+        <v>Sahil Rao</v>
       </c>
       <c r="E18" t="str">
         <v>owner10@greenfield.com</v>
@@ -1059,7 +1059,7 @@
         <v>Resident Tenant</v>
       </c>
       <c r="D19" t="str">
-        <v>Siddharth Mehta</v>
+        <v>Om Banerjee</v>
       </c>
       <c r="E19" t="str">
         <v>tenant1@greenfield.com</v>
@@ -1094,7 +1094,7 @@
         <v>Resident Tenant</v>
       </c>
       <c r="D20" t="str">
-        <v>Harish Banerjee</v>
+        <v>Aditi Agarwal</v>
       </c>
       <c r="E20" t="str">
         <v>tenant2@greenfield.com</v>
@@ -1129,7 +1129,7 @@
         <v>Resident Tenant</v>
       </c>
       <c r="D21" t="str">
-        <v>Chirag Rao</v>
+        <v>Rajesh Pillai</v>
       </c>
       <c r="E21" t="str">
         <v>tenant3@greenfield.com</v>
@@ -1164,7 +1164,7 @@
         <v>Resident Tenant</v>
       </c>
       <c r="D22" t="str">
-        <v>Yamini Gupta</v>
+        <v>Meera Patel</v>
       </c>
       <c r="E22" t="str">
         <v>tenant4@greenfield.com</v>
@@ -1199,7 +1199,7 @@
         <v>Resident Tenant</v>
       </c>
       <c r="D23" t="str">
-        <v>Rajesh Banerjee</v>
+        <v>Vikram Singh</v>
       </c>
       <c r="E23" t="str">
         <v>tenant5@greenfield.com</v>
@@ -1234,7 +1234,7 @@
         <v>Resident Tenant</v>
       </c>
       <c r="D24" t="str">
-        <v>Kavya Patel</v>
+        <v>Shiv Reddy</v>
       </c>
       <c r="E24" t="str">
         <v>tenant6@greenfield.com</v>
@@ -1269,7 +1269,7 @@
         <v>Resident Tenant</v>
       </c>
       <c r="D25" t="str">
-        <v>Ananya Banerjee</v>
+        <v>Arjun Verma</v>
       </c>
       <c r="E25" t="str">
         <v>tenant7@greenfield.com</v>
@@ -1304,7 +1304,7 @@
         <v>Resident Tenant</v>
       </c>
       <c r="D26" t="str">
-        <v>Vinay Banerjee</v>
+        <v>Priya Ghosh</v>
       </c>
       <c r="E26" t="str">
         <v>tenant8@greenfield.com</v>
@@ -1339,7 +1339,7 @@
         <v>Resident Tenant</v>
       </c>
       <c r="D27" t="str">
-        <v>Divya Singh</v>
+        <v>Meera Mehta</v>
       </c>
       <c r="E27" t="str">
         <v>tenant9@greenfield.com</v>
@@ -1374,7 +1374,7 @@
         <v>Resident Tenant</v>
       </c>
       <c r="D28" t="str">
-        <v>Kavya Bose</v>
+        <v>Jaya Kumar</v>
       </c>
       <c r="E28" t="str">
         <v>tenant10@greenfield.com</v>
@@ -1409,7 +1409,7 @@
         <v>Family Member</v>
       </c>
       <c r="D29" t="str">
-        <v>Farhan Pandey</v>
+        <v>Divya Bose</v>
       </c>
       <c r="E29" t="str">
         <v>family1@greenfield.com</v>
@@ -1444,7 +1444,7 @@
         <v>Family Member</v>
       </c>
       <c r="D30" t="str">
-        <v>Varun Ghosh</v>
+        <v>Ishaan Sharma</v>
       </c>
       <c r="E30" t="str">
         <v>family2@greenfield.com</v>
@@ -1479,7 +1479,7 @@
         <v>Family Member</v>
       </c>
       <c r="D31" t="str">
-        <v>Nisha Rao</v>
+        <v>Zara Verma</v>
       </c>
       <c r="E31" t="str">
         <v>family3@greenfield.com</v>
@@ -1514,7 +1514,7 @@
         <v>Family Member</v>
       </c>
       <c r="D32" t="str">
-        <v>Rajesh Nair</v>
+        <v>Chirag Bhat</v>
       </c>
       <c r="E32" t="str">
         <v>family4@greenfield.com</v>
@@ -1549,7 +1549,7 @@
         <v>Community Admin</v>
       </c>
       <c r="D33" t="str">
-        <v>Varun Pandey</v>
+        <v>Karan Pillai</v>
       </c>
       <c r="E33" t="str">
         <v>admin1@sunrisevalley.com</v>
@@ -1584,7 +1584,7 @@
         <v>Facility Manager</v>
       </c>
       <c r="D34" t="str">
-        <v>Neeraj Kapoor</v>
+        <v>Chirag Das</v>
       </c>
       <c r="E34" t="str">
         <v>fm1@sunrisevalley.com</v>
@@ -1619,7 +1619,7 @@
         <v>Security Guard</v>
       </c>
       <c r="D35" t="str">
-        <v>Farhan Choudhury</v>
+        <v>Chirag Menon</v>
       </c>
       <c r="E35" t="str">
         <v>guard1@sunrisevalley.com</v>
@@ -1654,7 +1654,7 @@
         <v>Security Guard</v>
       </c>
       <c r="D36" t="str">
-        <v>Dev Mishra</v>
+        <v>Vishal Pillai</v>
       </c>
       <c r="E36" t="str">
         <v>guard2@sunrisevalley.com</v>
@@ -1689,7 +1689,7 @@
         <v>Resident Owner</v>
       </c>
       <c r="D37" t="str">
-        <v>Dev Singh</v>
+        <v>Gayatri Ghosh</v>
       </c>
       <c r="E37" t="str">
         <v>owner1@sunrisevalley.com</v>
@@ -1724,7 +1724,7 @@
         <v>Resident Owner</v>
       </c>
       <c r="D38" t="str">
-        <v>Sahil Agarwal</v>
+        <v>Varun Rao</v>
       </c>
       <c r="E38" t="str">
         <v>owner2@sunrisevalley.com</v>
@@ -1759,7 +1759,7 @@
         <v>Resident Owner</v>
       </c>
       <c r="D39" t="str">
-        <v>Vinay Agarwal</v>
+        <v>Neeraj Mishra</v>
       </c>
       <c r="E39" t="str">
         <v>owner3@sunrisevalley.com</v>
@@ -1794,7 +1794,7 @@
         <v>Resident Owner</v>
       </c>
       <c r="D40" t="str">
-        <v>Aarav Desai</v>
+        <v>Manav Banerjee</v>
       </c>
       <c r="E40" t="str">
         <v>owner4@sunrisevalley.com</v>
@@ -1829,7 +1829,7 @@
         <v>Resident Owner</v>
       </c>
       <c r="D41" t="str">
-        <v>Siddharth Shah</v>
+        <v>Yamini Iyer</v>
       </c>
       <c r="E41" t="str">
         <v>owner5@sunrisevalley.com</v>
@@ -1864,7 +1864,7 @@
         <v>Resident Owner</v>
       </c>
       <c r="D42" t="str">
-        <v>Kavya Singh</v>
+        <v>Manav Desai</v>
       </c>
       <c r="E42" t="str">
         <v>owner6@sunrisevalley.com</v>
@@ -1899,7 +1899,7 @@
         <v>Resident Owner</v>
       </c>
       <c r="D43" t="str">
-        <v>Nisha Bose</v>
+        <v>Chirag Iyer</v>
       </c>
       <c r="E43" t="str">
         <v>owner7@sunrisevalley.com</v>
@@ -1934,7 +1934,7 @@
         <v>Resident Tenant</v>
       </c>
       <c r="D44" t="str">
-        <v>Tanvi Pillai</v>
+        <v>Seema Menon</v>
       </c>
       <c r="E44" t="str">
         <v>tenant1@sunrisevalley.com</v>
@@ -1969,7 +1969,7 @@
         <v>Resident Tenant</v>
       </c>
       <c r="D45" t="str">
-        <v>Ananya Jain</v>
+        <v>Varun Iyer</v>
       </c>
       <c r="E45" t="str">
         <v>tenant2@sunrisevalley.com</v>
@@ -2004,7 +2004,7 @@
         <v>Resident Tenant</v>
       </c>
       <c r="D46" t="str">
-        <v>Deepa Shah</v>
+        <v>Sangeeta Joshi</v>
       </c>
       <c r="E46" t="str">
         <v>tenant3@sunrisevalley.com</v>
@@ -2039,7 +2039,7 @@
         <v>Resident Tenant</v>
       </c>
       <c r="D47" t="str">
-        <v>Pooja Kumar</v>
+        <v>Dev Pillai</v>
       </c>
       <c r="E47" t="str">
         <v>tenant4@sunrisevalley.com</v>
@@ -2074,7 +2074,7 @@
         <v>Resident Tenant</v>
       </c>
       <c r="D48" t="str">
-        <v>Rohit Patel</v>
+        <v>Rajesh Choudhury</v>
       </c>
       <c r="E48" t="str">
         <v>tenant5@sunrisevalley.com</v>
@@ -2109,7 +2109,7 @@
         <v>Resident Tenant</v>
       </c>
       <c r="D49" t="str">
-        <v>Lakshmi Sharma</v>
+        <v>Simran Mehta</v>
       </c>
       <c r="E49" t="str">
         <v>tenant6@sunrisevalley.com</v>
@@ -2144,7 +2144,7 @@
         <v>Resident Tenant</v>
       </c>
       <c r="D50" t="str">
-        <v>Aarav Sinha</v>
+        <v>Yamini Menon</v>
       </c>
       <c r="E50" t="str">
         <v>tenant7@sunrisevalley.com</v>
@@ -2179,7 +2179,7 @@
         <v>Family Member</v>
       </c>
       <c r="D51" t="str">
-        <v>Zara Joshi</v>
+        <v>Sanjay Joshi</v>
       </c>
       <c r="E51" t="str">
         <v>family1@sunrisevalley.com</v>
@@ -2214,7 +2214,7 @@
         <v>Family Member</v>
       </c>
       <c r="D52" t="str">
-        <v>Jaya Kumar</v>
+        <v>Vishal Bhat</v>
       </c>
       <c r="E52" t="str">
         <v>family2@sunrisevalley.com</v>
@@ -2249,7 +2249,7 @@
         <v>Community Admin</v>
       </c>
       <c r="D53" t="str">
-        <v>Rajesh Kapoor</v>
+        <v>Lakshmi Ghosh</v>
       </c>
       <c r="E53" t="str">
         <v>admin1@palmmeadows.com</v>
@@ -2284,7 +2284,7 @@
         <v>Facility Manager</v>
       </c>
       <c r="D54" t="str">
-        <v>Zara Iyer</v>
+        <v>Deepa Choudhury</v>
       </c>
       <c r="E54" t="str">
         <v>fm1@palmmeadows.com</v>
@@ -2319,7 +2319,7 @@
         <v>Security Guard</v>
       </c>
       <c r="D55" t="str">
-        <v>Neeraj Menon</v>
+        <v>Pooja Das</v>
       </c>
       <c r="E55" t="str">
         <v>guard1@palmmeadows.com</v>
@@ -2354,7 +2354,7 @@
         <v>Resident Owner</v>
       </c>
       <c r="D56" t="str">
-        <v>Usha Rao</v>
+        <v>Harish Bhat</v>
       </c>
       <c r="E56" t="str">
         <v>owner1@palmmeadows.com</v>
@@ -2389,7 +2389,7 @@
         <v>Resident Owner</v>
       </c>
       <c r="D57" t="str">
-        <v>Sahil Chauhan</v>
+        <v>Sangeeta Pillai</v>
       </c>
       <c r="E57" t="str">
         <v>owner2@palmmeadows.com</v>
@@ -2424,7 +2424,7 @@
         <v>Resident Owner</v>
       </c>
       <c r="D58" t="str">
-        <v>Seema Banerjee</v>
+        <v>Varun Joshi</v>
       </c>
       <c r="E58" t="str">
         <v>owner3@palmmeadows.com</v>
@@ -2459,7 +2459,7 @@
         <v>Resident Owner</v>
       </c>
       <c r="D59" t="str">
-        <v>Tushar Sinha</v>
+        <v>Ananya Bhat</v>
       </c>
       <c r="E59" t="str">
         <v>owner4@palmmeadows.com</v>
@@ -2494,7 +2494,7 @@
         <v>Resident Owner</v>
       </c>
       <c r="D60" t="str">
-        <v>Shiv Shah</v>
+        <v>Pooja Tiwari</v>
       </c>
       <c r="E60" t="str">
         <v>owner5@palmmeadows.com</v>
@@ -2529,7 +2529,7 @@
         <v>Resident Tenant</v>
       </c>
       <c r="D61" t="str">
-        <v>Siddharth Verma</v>
+        <v>Tanvi Nair</v>
       </c>
       <c r="E61" t="str">
         <v>tenant1@palmmeadows.com</v>
@@ -2564,7 +2564,7 @@
         <v>Resident Tenant</v>
       </c>
       <c r="D62" t="str">
-        <v>Simran Tiwari</v>
+        <v>Sneha Bose</v>
       </c>
       <c r="E62" t="str">
         <v>tenant2@palmmeadows.com</v>
@@ -2599,7 +2599,7 @@
         <v>Resident Tenant</v>
       </c>
       <c r="D63" t="str">
-        <v>Priya Das</v>
+        <v>Shiv Mehta</v>
       </c>
       <c r="E63" t="str">
         <v>tenant3@palmmeadows.com</v>
@@ -2634,7 +2634,7 @@
         <v>Resident Tenant</v>
       </c>
       <c r="D64" t="str">
-        <v>Suresh Das</v>
+        <v>Siddharth Joshi</v>
       </c>
       <c r="E64" t="str">
         <v>tenant4@palmmeadows.com</v>
@@ -2669,7 +2669,7 @@
         <v>Resident Tenant</v>
       </c>
       <c r="D65" t="str">
-        <v>Sangeeta Reddy</v>
+        <v>Akash Tiwari</v>
       </c>
       <c r="E65" t="str">
         <v>tenant5@palmmeadows.com</v>
@@ -2704,7 +2704,7 @@
         <v>Family Member</v>
       </c>
       <c r="D66" t="str">
-        <v>Vishal Kumar</v>
+        <v>Tushar Desai</v>
       </c>
       <c r="E66" t="str">
         <v>family1@palmmeadows.com</v>
@@ -2739,7 +2739,7 @@
         <v>Family Member</v>
       </c>
       <c r="D67" t="str">
-        <v>Arjun Rao</v>
+        <v>Arjun Mehta</v>
       </c>
       <c r="E67" t="str">
         <v>family2@palmmeadows.com</v>
@@ -2820,7 +2820,7 @@
         <v>Community Admin</v>
       </c>
       <c r="D2" t="str">
-        <v>Rohit Bose</v>
+        <v>Aarav Menon</v>
       </c>
       <c r="E2" t="str">
         <v>admin1@greenfield.com</v>
@@ -2855,7 +2855,7 @@
         <v>Community Admin</v>
       </c>
       <c r="D3" t="str">
-        <v>Harish Kumar</v>
+        <v>Rohit Gupta</v>
       </c>
       <c r="E3" t="str">
         <v>admin2@greenfield.com</v>
@@ -2890,7 +2890,7 @@
         <v>Facility Manager</v>
       </c>
       <c r="D4" t="str">
-        <v>Sanjay Kapoor</v>
+        <v>Rajesh Banerjee</v>
       </c>
       <c r="E4" t="str">
         <v>fm1@greenfield.com</v>
@@ -2925,7 +2925,7 @@
         <v>Facility Manager</v>
       </c>
       <c r="D5" t="str">
-        <v>Zara Sharma</v>
+        <v>Aarav Joshi</v>
       </c>
       <c r="E5" t="str">
         <v>fm2@greenfield.com</v>
@@ -2960,7 +2960,7 @@
         <v>Security Guard</v>
       </c>
       <c r="D6" t="str">
-        <v>Vikram Mehta</v>
+        <v>Tanvi Bhat</v>
       </c>
       <c r="E6" t="str">
         <v>guard1@greenfield.com</v>
@@ -2995,7 +2995,7 @@
         <v>Security Guard</v>
       </c>
       <c r="D7" t="str">
-        <v>Siddharth Gupta</v>
+        <v>Arjun Singh</v>
       </c>
       <c r="E7" t="str">
         <v>guard2@greenfield.com</v>
@@ -3030,7 +3030,7 @@
         <v>Resident Owner</v>
       </c>
       <c r="D8" t="str">
-        <v>Ishaan Sinha</v>
+        <v>Sanjay Sharma</v>
       </c>
       <c r="E8" t="str">
         <v>owner1@greenfield.com</v>
@@ -3065,7 +3065,7 @@
         <v>Resident Owner</v>
       </c>
       <c r="D9" t="str">
-        <v>Bhavna Shah</v>
+        <v>Akash Iyer</v>
       </c>
       <c r="E9" t="str">
         <v>owner2@greenfield.com</v>
@@ -3100,7 +3100,7 @@
         <v>Resident Owner</v>
       </c>
       <c r="D10" t="str">
-        <v>Aditi Ghosh</v>
+        <v>Arjun Desai</v>
       </c>
       <c r="E10" t="str">
         <v>owner3@greenfield.com</v>
@@ -3135,7 +3135,7 @@
         <v>Resident Owner</v>
       </c>
       <c r="D11" t="str">
-        <v>Rajesh Mehta</v>
+        <v>Yamini Bose</v>
       </c>
       <c r="E11" t="str">
         <v>owner4@greenfield.com</v>
@@ -3170,7 +3170,7 @@
         <v>Resident Owner</v>
       </c>
       <c r="D12" t="str">
-        <v>Siddharth Iyer</v>
+        <v>Tanvi Iyer</v>
       </c>
       <c r="E12" t="str">
         <v>owner5@greenfield.com</v>
@@ -3205,7 +3205,7 @@
         <v>Resident Owner</v>
       </c>
       <c r="D13" t="str">
-        <v>Rahul Patel</v>
+        <v>Rekha Mishra</v>
       </c>
       <c r="E13" t="str">
         <v>owner6@greenfield.com</v>
@@ -3240,7 +3240,7 @@
         <v>Resident Owner</v>
       </c>
       <c r="D14" t="str">
-        <v>Priya Verma</v>
+        <v>Ananya Iyer</v>
       </c>
       <c r="E14" t="str">
         <v>owner7@greenfield.com</v>
@@ -3275,7 +3275,7 @@
         <v>Resident Owner</v>
       </c>
       <c r="D15" t="str">
-        <v>Tanvi Shah</v>
+        <v>Rahul Verma</v>
       </c>
       <c r="E15" t="str">
         <v>owner8@greenfield.com</v>
@@ -3310,7 +3310,7 @@
         <v>Resident Owner</v>
       </c>
       <c r="D16" t="str">
-        <v>Jaya Mehta</v>
+        <v>Sanjay Mehta</v>
       </c>
       <c r="E16" t="str">
         <v>owner9@greenfield.com</v>
@@ -3345,7 +3345,7 @@
         <v>Resident Owner</v>
       </c>
       <c r="D17" t="str">
-        <v>Sahil Kumar</v>
+        <v>Sahil Rao</v>
       </c>
       <c r="E17" t="str">
         <v>owner10@greenfield.com</v>
@@ -3380,7 +3380,7 @@
         <v>Resident Tenant</v>
       </c>
       <c r="D18" t="str">
-        <v>Siddharth Mehta</v>
+        <v>Om Banerjee</v>
       </c>
       <c r="E18" t="str">
         <v>tenant1@greenfield.com</v>
@@ -3415,7 +3415,7 @@
         <v>Resident Tenant</v>
       </c>
       <c r="D19" t="str">
-        <v>Harish Banerjee</v>
+        <v>Aditi Agarwal</v>
       </c>
       <c r="E19" t="str">
         <v>tenant2@greenfield.com</v>
@@ -3450,7 +3450,7 @@
         <v>Resident Tenant</v>
       </c>
       <c r="D20" t="str">
-        <v>Chirag Rao</v>
+        <v>Rajesh Pillai</v>
       </c>
       <c r="E20" t="str">
         <v>tenant3@greenfield.com</v>
@@ -3485,7 +3485,7 @@
         <v>Resident Tenant</v>
       </c>
       <c r="D21" t="str">
-        <v>Yamini Gupta</v>
+        <v>Meera Patel</v>
       </c>
       <c r="E21" t="str">
         <v>tenant4@greenfield.com</v>
@@ -3520,7 +3520,7 @@
         <v>Resident Tenant</v>
       </c>
       <c r="D22" t="str">
-        <v>Rajesh Banerjee</v>
+        <v>Vikram Singh</v>
       </c>
       <c r="E22" t="str">
         <v>tenant5@greenfield.com</v>
@@ -3555,7 +3555,7 @@
         <v>Resident Tenant</v>
       </c>
       <c r="D23" t="str">
-        <v>Kavya Patel</v>
+        <v>Shiv Reddy</v>
       </c>
       <c r="E23" t="str">
         <v>tenant6@greenfield.com</v>
@@ -3590,7 +3590,7 @@
         <v>Resident Tenant</v>
       </c>
       <c r="D24" t="str">
-        <v>Ananya Banerjee</v>
+        <v>Arjun Verma</v>
       </c>
       <c r="E24" t="str">
         <v>tenant7@greenfield.com</v>
@@ -3625,7 +3625,7 @@
         <v>Resident Tenant</v>
       </c>
       <c r="D25" t="str">
-        <v>Vinay Banerjee</v>
+        <v>Priya Ghosh</v>
       </c>
       <c r="E25" t="str">
         <v>tenant8@greenfield.com</v>
@@ -3660,7 +3660,7 @@
         <v>Resident Tenant</v>
       </c>
       <c r="D26" t="str">
-        <v>Divya Singh</v>
+        <v>Meera Mehta</v>
       </c>
       <c r="E26" t="str">
         <v>tenant9@greenfield.com</v>
@@ -3695,7 +3695,7 @@
         <v>Resident Tenant</v>
       </c>
       <c r="D27" t="str">
-        <v>Kavya Bose</v>
+        <v>Jaya Kumar</v>
       </c>
       <c r="E27" t="str">
         <v>tenant10@greenfield.com</v>
@@ -3730,7 +3730,7 @@
         <v>Family Member</v>
       </c>
       <c r="D28" t="str">
-        <v>Farhan Pandey</v>
+        <v>Divya Bose</v>
       </c>
       <c r="E28" t="str">
         <v>family1@greenfield.com</v>
@@ -3765,7 +3765,7 @@
         <v>Family Member</v>
       </c>
       <c r="D29" t="str">
-        <v>Varun Ghosh</v>
+        <v>Ishaan Sharma</v>
       </c>
       <c r="E29" t="str">
         <v>family2@greenfield.com</v>
@@ -3800,7 +3800,7 @@
         <v>Family Member</v>
       </c>
       <c r="D30" t="str">
-        <v>Nisha Rao</v>
+        <v>Zara Verma</v>
       </c>
       <c r="E30" t="str">
         <v>family3@greenfield.com</v>
@@ -3835,7 +3835,7 @@
         <v>Family Member</v>
       </c>
       <c r="D31" t="str">
-        <v>Rajesh Nair</v>
+        <v>Chirag Bhat</v>
       </c>
       <c r="E31" t="str">
         <v>family4@greenfield.com</v>
@@ -3916,7 +3916,7 @@
         <v>Community Admin</v>
       </c>
       <c r="D2" t="str">
-        <v>Varun Pandey</v>
+        <v>Karan Pillai</v>
       </c>
       <c r="E2" t="str">
         <v>admin1@sunrisevalley.com</v>
@@ -3951,7 +3951,7 @@
         <v>Facility Manager</v>
       </c>
       <c r="D3" t="str">
-        <v>Neeraj Kapoor</v>
+        <v>Chirag Das</v>
       </c>
       <c r="E3" t="str">
         <v>fm1@sunrisevalley.com</v>
@@ -3986,7 +3986,7 @@
         <v>Security Guard</v>
       </c>
       <c r="D4" t="str">
-        <v>Farhan Choudhury</v>
+        <v>Chirag Menon</v>
       </c>
       <c r="E4" t="str">
         <v>guard1@sunrisevalley.com</v>
@@ -4021,7 +4021,7 @@
         <v>Security Guard</v>
       </c>
       <c r="D5" t="str">
-        <v>Dev Mishra</v>
+        <v>Vishal Pillai</v>
       </c>
       <c r="E5" t="str">
         <v>guard2@sunrisevalley.com</v>
@@ -4056,7 +4056,7 @@
         <v>Resident Owner</v>
       </c>
       <c r="D6" t="str">
-        <v>Dev Singh</v>
+        <v>Gayatri Ghosh</v>
       </c>
       <c r="E6" t="str">
         <v>owner1@sunrisevalley.com</v>
@@ -4091,7 +4091,7 @@
         <v>Resident Owner</v>
       </c>
       <c r="D7" t="str">
-        <v>Sahil Agarwal</v>
+        <v>Varun Rao</v>
       </c>
       <c r="E7" t="str">
         <v>owner2@sunrisevalley.com</v>
@@ -4126,7 +4126,7 @@
         <v>Resident Owner</v>
       </c>
       <c r="D8" t="str">
-        <v>Vinay Agarwal</v>
+        <v>Neeraj Mishra</v>
       </c>
       <c r="E8" t="str">
         <v>owner3@sunrisevalley.com</v>
@@ -4161,7 +4161,7 @@
         <v>Resident Owner</v>
       </c>
       <c r="D9" t="str">
-        <v>Aarav Desai</v>
+        <v>Manav Banerjee</v>
       </c>
       <c r="E9" t="str">
         <v>owner4@sunrisevalley.com</v>
@@ -4196,7 +4196,7 @@
         <v>Resident Owner</v>
       </c>
       <c r="D10" t="str">
-        <v>Siddharth Shah</v>
+        <v>Yamini Iyer</v>
       </c>
       <c r="E10" t="str">
         <v>owner5@sunrisevalley.com</v>
@@ -4231,7 +4231,7 @@
         <v>Resident Owner</v>
       </c>
       <c r="D11" t="str">
-        <v>Kavya Singh</v>
+        <v>Manav Desai</v>
       </c>
       <c r="E11" t="str">
         <v>owner6@sunrisevalley.com</v>
@@ -4266,7 +4266,7 @@
         <v>Resident Owner</v>
       </c>
       <c r="D12" t="str">
-        <v>Nisha Bose</v>
+        <v>Chirag Iyer</v>
       </c>
       <c r="E12" t="str">
         <v>owner7@sunrisevalley.com</v>
@@ -4301,7 +4301,7 @@
         <v>Resident Tenant</v>
       </c>
       <c r="D13" t="str">
-        <v>Tanvi Pillai</v>
+        <v>Seema Menon</v>
       </c>
       <c r="E13" t="str">
         <v>tenant1@sunrisevalley.com</v>
@@ -4336,7 +4336,7 @@
         <v>Resident Tenant</v>
       </c>
       <c r="D14" t="str">
-        <v>Ananya Jain</v>
+        <v>Varun Iyer</v>
       </c>
       <c r="E14" t="str">
         <v>tenant2@sunrisevalley.com</v>
@@ -4371,7 +4371,7 @@
         <v>Resident Tenant</v>
       </c>
       <c r="D15" t="str">
-        <v>Deepa Shah</v>
+        <v>Sangeeta Joshi</v>
       </c>
       <c r="E15" t="str">
         <v>tenant3@sunrisevalley.com</v>
@@ -4406,7 +4406,7 @@
         <v>Resident Tenant</v>
       </c>
       <c r="D16" t="str">
-        <v>Pooja Kumar</v>
+        <v>Dev Pillai</v>
       </c>
       <c r="E16" t="str">
         <v>tenant4@sunrisevalley.com</v>
@@ -4441,7 +4441,7 @@
         <v>Resident Tenant</v>
       </c>
       <c r="D17" t="str">
-        <v>Rohit Patel</v>
+        <v>Rajesh Choudhury</v>
       </c>
       <c r="E17" t="str">
         <v>tenant5@sunrisevalley.com</v>
@@ -4476,7 +4476,7 @@
         <v>Resident Tenant</v>
       </c>
       <c r="D18" t="str">
-        <v>Lakshmi Sharma</v>
+        <v>Simran Mehta</v>
       </c>
       <c r="E18" t="str">
         <v>tenant6@sunrisevalley.com</v>
@@ -4511,7 +4511,7 @@
         <v>Resident Tenant</v>
       </c>
       <c r="D19" t="str">
-        <v>Aarav Sinha</v>
+        <v>Yamini Menon</v>
       </c>
       <c r="E19" t="str">
         <v>tenant7@sunrisevalley.com</v>
@@ -4546,7 +4546,7 @@
         <v>Family Member</v>
       </c>
       <c r="D20" t="str">
-        <v>Zara Joshi</v>
+        <v>Sanjay Joshi</v>
       </c>
       <c r="E20" t="str">
         <v>family1@sunrisevalley.com</v>
@@ -4581,7 +4581,7 @@
         <v>Family Member</v>
       </c>
       <c r="D21" t="str">
-        <v>Jaya Kumar</v>
+        <v>Vishal Bhat</v>
       </c>
       <c r="E21" t="str">
         <v>family2@sunrisevalley.com</v>
@@ -4662,7 +4662,7 @@
         <v>Community Admin</v>
       </c>
       <c r="D2" t="str">
-        <v>Rajesh Kapoor</v>
+        <v>Lakshmi Ghosh</v>
       </c>
       <c r="E2" t="str">
         <v>admin1@palmmeadows.com</v>
@@ -4697,7 +4697,7 @@
         <v>Facility Manager</v>
       </c>
       <c r="D3" t="str">
-        <v>Zara Iyer</v>
+        <v>Deepa Choudhury</v>
       </c>
       <c r="E3" t="str">
         <v>fm1@palmmeadows.com</v>
@@ -4732,7 +4732,7 @@
         <v>Security Guard</v>
       </c>
       <c r="D4" t="str">
-        <v>Neeraj Menon</v>
+        <v>Pooja Das</v>
       </c>
       <c r="E4" t="str">
         <v>guard1@palmmeadows.com</v>
@@ -4767,7 +4767,7 @@
         <v>Resident Owner</v>
       </c>
       <c r="D5" t="str">
-        <v>Usha Rao</v>
+        <v>Harish Bhat</v>
       </c>
       <c r="E5" t="str">
         <v>owner1@palmmeadows.com</v>
@@ -4802,7 +4802,7 @@
         <v>Resident Owner</v>
       </c>
       <c r="D6" t="str">
-        <v>Sahil Chauhan</v>
+        <v>Sangeeta Pillai</v>
       </c>
       <c r="E6" t="str">
         <v>owner2@palmmeadows.com</v>
@@ -4837,7 +4837,7 @@
         <v>Resident Owner</v>
       </c>
       <c r="D7" t="str">
-        <v>Seema Banerjee</v>
+        <v>Varun Joshi</v>
       </c>
       <c r="E7" t="str">
         <v>owner3@palmmeadows.com</v>
@@ -4872,7 +4872,7 @@
         <v>Resident Owner</v>
       </c>
       <c r="D8" t="str">
-        <v>Tushar Sinha</v>
+        <v>Ananya Bhat</v>
       </c>
       <c r="E8" t="str">
         <v>owner4@palmmeadows.com</v>
@@ -4907,7 +4907,7 @@
         <v>Resident Owner</v>
       </c>
       <c r="D9" t="str">
-        <v>Shiv Shah</v>
+        <v>Pooja Tiwari</v>
       </c>
       <c r="E9" t="str">
         <v>owner5@palmmeadows.com</v>
@@ -4942,7 +4942,7 @@
         <v>Resident Tenant</v>
       </c>
       <c r="D10" t="str">
-        <v>Siddharth Verma</v>
+        <v>Tanvi Nair</v>
       </c>
       <c r="E10" t="str">
         <v>tenant1@palmmeadows.com</v>
@@ -4977,7 +4977,7 @@
         <v>Resident Tenant</v>
       </c>
       <c r="D11" t="str">
-        <v>Simran Tiwari</v>
+        <v>Sneha Bose</v>
       </c>
       <c r="E11" t="str">
         <v>tenant2@palmmeadows.com</v>
@@ -5012,7 +5012,7 @@
         <v>Resident Tenant</v>
       </c>
       <c r="D12" t="str">
-        <v>Priya Das</v>
+        <v>Shiv Mehta</v>
       </c>
       <c r="E12" t="str">
         <v>tenant3@palmmeadows.com</v>
@@ -5047,7 +5047,7 @@
         <v>Resident Tenant</v>
       </c>
       <c r="D13" t="str">
-        <v>Suresh Das</v>
+        <v>Siddharth Joshi</v>
       </c>
       <c r="E13" t="str">
         <v>tenant4@palmmeadows.com</v>
@@ -5082,7 +5082,7 @@
         <v>Resident Tenant</v>
       </c>
       <c r="D14" t="str">
-        <v>Sangeeta Reddy</v>
+        <v>Akash Tiwari</v>
       </c>
       <c r="E14" t="str">
         <v>tenant5@palmmeadows.com</v>
@@ -5117,7 +5117,7 @@
         <v>Family Member</v>
       </c>
       <c r="D15" t="str">
-        <v>Vishal Kumar</v>
+        <v>Tushar Desai</v>
       </c>
       <c r="E15" t="str">
         <v>family1@palmmeadows.com</v>
@@ -5152,7 +5152,7 @@
         <v>Family Member</v>
       </c>
       <c r="D16" t="str">
-        <v>Arjun Rao</v>
+        <v>Arjun Mehta</v>
       </c>
       <c r="E16" t="str">
         <v>family2@palmmeadows.com</v>
@@ -5322,7 +5322,7 @@
         <v>Platform Multi-Community Switch</v>
       </c>
       <c r="D2" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Login with admin@enterprise.com / SuperAdminPwd@123.
+        <v xml:space="preserve">1. Login with admin@managemygate.com / password123.
 2. Open workspace dropdown in header.
 3. Verify all 3 communities (Greenfield Heights, Sunrise Valley, Palm Meadows) are listed.
 4. Switch workspace and verify context changes.</v>
@@ -5517,7 +5517,7 @@
         <v>Super Admin Account</v>
       </c>
       <c r="B7" t="str">
-        <v>admin@enterprise.com (Password: SuperAdminPwd@123)</v>
+        <v>admin@managemygate.com (Password: password123)</v>
       </c>
     </row>
     <row r="8">
@@ -5541,7 +5541,7 @@
         <v>Seed Execution Timestamp</v>
       </c>
       <c r="B10" t="str">
-        <v>2026-07-31T10:38:45.636Z</v>
+        <v>2026-08-20T09:13:54.920Z</v>
       </c>
     </row>
   </sheetData>

--- a/Community_Testing_Credentials.xlsx
+++ b/Community_Testing_Credentials.xlsx
@@ -499,7 +499,7 @@
         <v>Community Admin</v>
       </c>
       <c r="D3" t="str">
-        <v>Aarav Menon</v>
+        <v>Sapna Singh</v>
       </c>
       <c r="E3" t="str">
         <v>admin1@greenfield.com</v>
@@ -534,7 +534,7 @@
         <v>Community Admin</v>
       </c>
       <c r="D4" t="str">
-        <v>Rohit Gupta</v>
+        <v>Shreya Bhat</v>
       </c>
       <c r="E4" t="str">
         <v>admin2@greenfield.com</v>
@@ -569,7 +569,7 @@
         <v>Facility Manager</v>
       </c>
       <c r="D5" t="str">
-        <v>Rajesh Banerjee</v>
+        <v>Suresh Verma</v>
       </c>
       <c r="E5" t="str">
         <v>fm1@greenfield.com</v>
@@ -604,7 +604,7 @@
         <v>Facility Manager</v>
       </c>
       <c r="D6" t="str">
-        <v>Aarav Joshi</v>
+        <v>Dev Tiwari</v>
       </c>
       <c r="E6" t="str">
         <v>fm2@greenfield.com</v>
@@ -639,7 +639,7 @@
         <v>Security Guard</v>
       </c>
       <c r="D7" t="str">
-        <v>Tanvi Bhat</v>
+        <v>Meera Sinha</v>
       </c>
       <c r="E7" t="str">
         <v>guard1@greenfield.com</v>
@@ -674,7 +674,7 @@
         <v>Security Guard</v>
       </c>
       <c r="D8" t="str">
-        <v>Arjun Singh</v>
+        <v>Arjun Jain</v>
       </c>
       <c r="E8" t="str">
         <v>guard2@greenfield.com</v>
@@ -709,7 +709,7 @@
         <v>Resident Owner</v>
       </c>
       <c r="D9" t="str">
-        <v>Sanjay Sharma</v>
+        <v>Karan Rao</v>
       </c>
       <c r="E9" t="str">
         <v>owner1@greenfield.com</v>
@@ -744,7 +744,7 @@
         <v>Resident Owner</v>
       </c>
       <c r="D10" t="str">
-        <v>Akash Iyer</v>
+        <v>Akash Joshi</v>
       </c>
       <c r="E10" t="str">
         <v>owner2@greenfield.com</v>
@@ -779,7 +779,7 @@
         <v>Resident Owner</v>
       </c>
       <c r="D11" t="str">
-        <v>Arjun Desai</v>
+        <v>Siddharth Sharma</v>
       </c>
       <c r="E11" t="str">
         <v>owner3@greenfield.com</v>
@@ -814,7 +814,7 @@
         <v>Resident Owner</v>
       </c>
       <c r="D12" t="str">
-        <v>Yamini Bose</v>
+        <v>Ananya Pillai</v>
       </c>
       <c r="E12" t="str">
         <v>owner4@greenfield.com</v>
@@ -849,7 +849,7 @@
         <v>Resident Owner</v>
       </c>
       <c r="D13" t="str">
-        <v>Tanvi Iyer</v>
+        <v>Vinay Sharma</v>
       </c>
       <c r="E13" t="str">
         <v>owner5@greenfield.com</v>
@@ -884,7 +884,7 @@
         <v>Resident Owner</v>
       </c>
       <c r="D14" t="str">
-        <v>Rekha Mishra</v>
+        <v>Pranav Kapoor</v>
       </c>
       <c r="E14" t="str">
         <v>owner6@greenfield.com</v>
@@ -919,7 +919,7 @@
         <v>Resident Owner</v>
       </c>
       <c r="D15" t="str">
-        <v>Ananya Iyer</v>
+        <v>Meera Iyer</v>
       </c>
       <c r="E15" t="str">
         <v>owner7@greenfield.com</v>
@@ -954,7 +954,7 @@
         <v>Resident Owner</v>
       </c>
       <c r="D16" t="str">
-        <v>Rahul Verma</v>
+        <v>Seema Menon</v>
       </c>
       <c r="E16" t="str">
         <v>owner8@greenfield.com</v>
@@ -989,7 +989,7 @@
         <v>Resident Owner</v>
       </c>
       <c r="D17" t="str">
-        <v>Sanjay Mehta</v>
+        <v>Divya Pandey</v>
       </c>
       <c r="E17" t="str">
         <v>owner9@greenfield.com</v>
@@ -1024,7 +1024,7 @@
         <v>Resident Owner</v>
       </c>
       <c r="D18" t="str">
-        <v>Sahil Rao</v>
+        <v>Vinay Das</v>
       </c>
       <c r="E18" t="str">
         <v>owner10@greenfield.com</v>
@@ -1059,7 +1059,7 @@
         <v>Resident Tenant</v>
       </c>
       <c r="D19" t="str">
-        <v>Om Banerjee</v>
+        <v>Priya Reddy</v>
       </c>
       <c r="E19" t="str">
         <v>tenant1@greenfield.com</v>
@@ -1094,7 +1094,7 @@
         <v>Resident Tenant</v>
       </c>
       <c r="D20" t="str">
-        <v>Aditi Agarwal</v>
+        <v>Priya Mishra</v>
       </c>
       <c r="E20" t="str">
         <v>tenant2@greenfield.com</v>
@@ -1129,7 +1129,7 @@
         <v>Resident Tenant</v>
       </c>
       <c r="D21" t="str">
-        <v>Rajesh Pillai</v>
+        <v>Ananya Pillai</v>
       </c>
       <c r="E21" t="str">
         <v>tenant3@greenfield.com</v>
@@ -1164,7 +1164,7 @@
         <v>Resident Tenant</v>
       </c>
       <c r="D22" t="str">
-        <v>Meera Patel</v>
+        <v>Shreya Chauhan</v>
       </c>
       <c r="E22" t="str">
         <v>tenant4@greenfield.com</v>
@@ -1199,7 +1199,7 @@
         <v>Resident Tenant</v>
       </c>
       <c r="D23" t="str">
-        <v>Vikram Singh</v>
+        <v>Rekha Pandey</v>
       </c>
       <c r="E23" t="str">
         <v>tenant5@greenfield.com</v>
@@ -1234,7 +1234,7 @@
         <v>Resident Tenant</v>
       </c>
       <c r="D24" t="str">
-        <v>Shiv Reddy</v>
+        <v>Priya Mehta</v>
       </c>
       <c r="E24" t="str">
         <v>tenant6@greenfield.com</v>
@@ -1269,7 +1269,7 @@
         <v>Resident Tenant</v>
       </c>
       <c r="D25" t="str">
-        <v>Arjun Verma</v>
+        <v>Manav Jain</v>
       </c>
       <c r="E25" t="str">
         <v>tenant7@greenfield.com</v>
@@ -1304,7 +1304,7 @@
         <v>Resident Tenant</v>
       </c>
       <c r="D26" t="str">
-        <v>Priya Ghosh</v>
+        <v>Sangeeta Pillai</v>
       </c>
       <c r="E26" t="str">
         <v>tenant8@greenfield.com</v>
@@ -1339,7 +1339,7 @@
         <v>Resident Tenant</v>
       </c>
       <c r="D27" t="str">
-        <v>Meera Mehta</v>
+        <v>Nisha Pandey</v>
       </c>
       <c r="E27" t="str">
         <v>tenant9@greenfield.com</v>
@@ -1374,7 +1374,7 @@
         <v>Resident Tenant</v>
       </c>
       <c r="D28" t="str">
-        <v>Jaya Kumar</v>
+        <v>Karan Bhat</v>
       </c>
       <c r="E28" t="str">
         <v>tenant10@greenfield.com</v>
@@ -1409,7 +1409,7 @@
         <v>Family Member</v>
       </c>
       <c r="D29" t="str">
-        <v>Divya Bose</v>
+        <v>Siddharth Mehta</v>
       </c>
       <c r="E29" t="str">
         <v>family1@greenfield.com</v>
@@ -1444,7 +1444,7 @@
         <v>Family Member</v>
       </c>
       <c r="D30" t="str">
-        <v>Ishaan Sharma</v>
+        <v>Tanvi Ghosh</v>
       </c>
       <c r="E30" t="str">
         <v>family2@greenfield.com</v>
@@ -1479,7 +1479,7 @@
         <v>Family Member</v>
       </c>
       <c r="D31" t="str">
-        <v>Zara Verma</v>
+        <v>Pranav Bose</v>
       </c>
       <c r="E31" t="str">
         <v>family3@greenfield.com</v>
@@ -1514,7 +1514,7 @@
         <v>Family Member</v>
       </c>
       <c r="D32" t="str">
-        <v>Chirag Bhat</v>
+        <v>Ananya Verma</v>
       </c>
       <c r="E32" t="str">
         <v>family4@greenfield.com</v>
@@ -1549,7 +1549,7 @@
         <v>Community Admin</v>
       </c>
       <c r="D33" t="str">
-        <v>Karan Pillai</v>
+        <v>Aditi Bose</v>
       </c>
       <c r="E33" t="str">
         <v>admin1@sunrisevalley.com</v>
@@ -1584,7 +1584,7 @@
         <v>Facility Manager</v>
       </c>
       <c r="D34" t="str">
-        <v>Chirag Das</v>
+        <v>Manav Pandey</v>
       </c>
       <c r="E34" t="str">
         <v>fm1@sunrisevalley.com</v>
@@ -1619,7 +1619,7 @@
         <v>Security Guard</v>
       </c>
       <c r="D35" t="str">
-        <v>Chirag Menon</v>
+        <v>Sangeeta Pandey</v>
       </c>
       <c r="E35" t="str">
         <v>guard1@sunrisevalley.com</v>
@@ -1654,7 +1654,7 @@
         <v>Security Guard</v>
       </c>
       <c r="D36" t="str">
-        <v>Vishal Pillai</v>
+        <v>Yamini Agarwal</v>
       </c>
       <c r="E36" t="str">
         <v>guard2@sunrisevalley.com</v>
@@ -1689,7 +1689,7 @@
         <v>Resident Owner</v>
       </c>
       <c r="D37" t="str">
-        <v>Gayatri Ghosh</v>
+        <v>Dev Nair</v>
       </c>
       <c r="E37" t="str">
         <v>owner1@sunrisevalley.com</v>
@@ -1724,7 +1724,7 @@
         <v>Resident Owner</v>
       </c>
       <c r="D38" t="str">
-        <v>Varun Rao</v>
+        <v>Harish Rao</v>
       </c>
       <c r="E38" t="str">
         <v>owner2@sunrisevalley.com</v>
@@ -1759,7 +1759,7 @@
         <v>Resident Owner</v>
       </c>
       <c r="D39" t="str">
-        <v>Neeraj Mishra</v>
+        <v>Ananya Desai</v>
       </c>
       <c r="E39" t="str">
         <v>owner3@sunrisevalley.com</v>
@@ -1794,7 +1794,7 @@
         <v>Resident Owner</v>
       </c>
       <c r="D40" t="str">
-        <v>Manav Banerjee</v>
+        <v>Zara Mehta</v>
       </c>
       <c r="E40" t="str">
         <v>owner4@sunrisevalley.com</v>
@@ -1829,7 +1829,7 @@
         <v>Resident Owner</v>
       </c>
       <c r="D41" t="str">
-        <v>Yamini Iyer</v>
+        <v>Tanvi Joshi</v>
       </c>
       <c r="E41" t="str">
         <v>owner5@sunrisevalley.com</v>
@@ -1864,7 +1864,7 @@
         <v>Resident Owner</v>
       </c>
       <c r="D42" t="str">
-        <v>Manav Desai</v>
+        <v>Gayatri Kapoor</v>
       </c>
       <c r="E42" t="str">
         <v>owner6@sunrisevalley.com</v>
@@ -1899,7 +1899,7 @@
         <v>Resident Owner</v>
       </c>
       <c r="D43" t="str">
-        <v>Chirag Iyer</v>
+        <v>Kavya Bhat</v>
       </c>
       <c r="E43" t="str">
         <v>owner7@sunrisevalley.com</v>
@@ -1934,7 +1934,7 @@
         <v>Resident Tenant</v>
       </c>
       <c r="D44" t="str">
-        <v>Seema Menon</v>
+        <v>Usha Chauhan</v>
       </c>
       <c r="E44" t="str">
         <v>tenant1@sunrisevalley.com</v>
@@ -1969,7 +1969,7 @@
         <v>Resident Tenant</v>
       </c>
       <c r="D45" t="str">
-        <v>Varun Iyer</v>
+        <v>Vinay Chauhan</v>
       </c>
       <c r="E45" t="str">
         <v>tenant2@sunrisevalley.com</v>
@@ -2004,7 +2004,7 @@
         <v>Resident Tenant</v>
       </c>
       <c r="D46" t="str">
-        <v>Sangeeta Joshi</v>
+        <v>Priya Desai</v>
       </c>
       <c r="E46" t="str">
         <v>tenant3@sunrisevalley.com</v>
@@ -2039,7 +2039,7 @@
         <v>Resident Tenant</v>
       </c>
       <c r="D47" t="str">
-        <v>Dev Pillai</v>
+        <v>Vikram Nair</v>
       </c>
       <c r="E47" t="str">
         <v>tenant4@sunrisevalley.com</v>
@@ -2074,7 +2074,7 @@
         <v>Resident Tenant</v>
       </c>
       <c r="D48" t="str">
-        <v>Rajesh Choudhury</v>
+        <v>Usha Iyer</v>
       </c>
       <c r="E48" t="str">
         <v>tenant5@sunrisevalley.com</v>
@@ -2109,7 +2109,7 @@
         <v>Resident Tenant</v>
       </c>
       <c r="D49" t="str">
-        <v>Simran Mehta</v>
+        <v>Shreya Reddy</v>
       </c>
       <c r="E49" t="str">
         <v>tenant6@sunrisevalley.com</v>
@@ -2144,7 +2144,7 @@
         <v>Resident Tenant</v>
       </c>
       <c r="D50" t="str">
-        <v>Yamini Menon</v>
+        <v>Bhavna Agarwal</v>
       </c>
       <c r="E50" t="str">
         <v>tenant7@sunrisevalley.com</v>
@@ -2179,7 +2179,7 @@
         <v>Family Member</v>
       </c>
       <c r="D51" t="str">
-        <v>Sanjay Joshi</v>
+        <v>Rohit Chauhan</v>
       </c>
       <c r="E51" t="str">
         <v>family1@sunrisevalley.com</v>
@@ -2214,7 +2214,7 @@
         <v>Family Member</v>
       </c>
       <c r="D52" t="str">
-        <v>Vishal Bhat</v>
+        <v>Bhavna Patel</v>
       </c>
       <c r="E52" t="str">
         <v>family2@sunrisevalley.com</v>
@@ -2249,7 +2249,7 @@
         <v>Community Admin</v>
       </c>
       <c r="D53" t="str">
-        <v>Lakshmi Ghosh</v>
+        <v>Aditi Rao</v>
       </c>
       <c r="E53" t="str">
         <v>admin1@palmmeadows.com</v>
@@ -2284,7 +2284,7 @@
         <v>Facility Manager</v>
       </c>
       <c r="D54" t="str">
-        <v>Deepa Choudhury</v>
+        <v>Vinay Desai</v>
       </c>
       <c r="E54" t="str">
         <v>fm1@palmmeadows.com</v>
@@ -2319,7 +2319,7 @@
         <v>Security Guard</v>
       </c>
       <c r="D55" t="str">
-        <v>Pooja Das</v>
+        <v>Rajesh Bose</v>
       </c>
       <c r="E55" t="str">
         <v>guard1@palmmeadows.com</v>
@@ -2354,7 +2354,7 @@
         <v>Resident Owner</v>
       </c>
       <c r="D56" t="str">
-        <v>Harish Bhat</v>
+        <v>Meera Nair</v>
       </c>
       <c r="E56" t="str">
         <v>owner1@palmmeadows.com</v>
@@ -2389,7 +2389,7 @@
         <v>Resident Owner</v>
       </c>
       <c r="D57" t="str">
-        <v>Sangeeta Pillai</v>
+        <v>Ananya Patel</v>
       </c>
       <c r="E57" t="str">
         <v>owner2@palmmeadows.com</v>
@@ -2424,7 +2424,7 @@
         <v>Resident Owner</v>
       </c>
       <c r="D58" t="str">
-        <v>Varun Joshi</v>
+        <v>Yamini Bose</v>
       </c>
       <c r="E58" t="str">
         <v>owner3@palmmeadows.com</v>
@@ -2459,7 +2459,7 @@
         <v>Resident Owner</v>
       </c>
       <c r="D59" t="str">
-        <v>Ananya Bhat</v>
+        <v>Farhan Reddy</v>
       </c>
       <c r="E59" t="str">
         <v>owner4@palmmeadows.com</v>
@@ -2494,7 +2494,7 @@
         <v>Resident Owner</v>
       </c>
       <c r="D60" t="str">
-        <v>Pooja Tiwari</v>
+        <v>Farhan Tiwari</v>
       </c>
       <c r="E60" t="str">
         <v>owner5@palmmeadows.com</v>
@@ -2529,7 +2529,7 @@
         <v>Resident Tenant</v>
       </c>
       <c r="D61" t="str">
-        <v>Tanvi Nair</v>
+        <v>Vishal Jain</v>
       </c>
       <c r="E61" t="str">
         <v>tenant1@palmmeadows.com</v>
@@ -2564,7 +2564,7 @@
         <v>Resident Tenant</v>
       </c>
       <c r="D62" t="str">
-        <v>Sneha Bose</v>
+        <v>Karan Iyer</v>
       </c>
       <c r="E62" t="str">
         <v>tenant2@palmmeadows.com</v>
@@ -2599,7 +2599,7 @@
         <v>Resident Tenant</v>
       </c>
       <c r="D63" t="str">
-        <v>Shiv Mehta</v>
+        <v>Siddharth Verma</v>
       </c>
       <c r="E63" t="str">
         <v>tenant3@palmmeadows.com</v>
@@ -2634,7 +2634,7 @@
         <v>Resident Tenant</v>
       </c>
       <c r="D64" t="str">
-        <v>Siddharth Joshi</v>
+        <v>Bhavna Bhat</v>
       </c>
       <c r="E64" t="str">
         <v>tenant4@palmmeadows.com</v>
@@ -2669,7 +2669,7 @@
         <v>Resident Tenant</v>
       </c>
       <c r="D65" t="str">
-        <v>Akash Tiwari</v>
+        <v>Shiv Nair</v>
       </c>
       <c r="E65" t="str">
         <v>tenant5@palmmeadows.com</v>
@@ -2704,7 +2704,7 @@
         <v>Family Member</v>
       </c>
       <c r="D66" t="str">
-        <v>Tushar Desai</v>
+        <v>Arjun Patel</v>
       </c>
       <c r="E66" t="str">
         <v>family1@palmmeadows.com</v>
@@ -2739,7 +2739,7 @@
         <v>Family Member</v>
       </c>
       <c r="D67" t="str">
-        <v>Arjun Mehta</v>
+        <v>Pranav Kumar</v>
       </c>
       <c r="E67" t="str">
         <v>family2@palmmeadows.com</v>
@@ -2820,7 +2820,7 @@
         <v>Community Admin</v>
       </c>
       <c r="D2" t="str">
-        <v>Aarav Menon</v>
+        <v>Sapna Singh</v>
       </c>
       <c r="E2" t="str">
         <v>admin1@greenfield.com</v>
@@ -2855,7 +2855,7 @@
         <v>Community Admin</v>
       </c>
       <c r="D3" t="str">
-        <v>Rohit Gupta</v>
+        <v>Shreya Bhat</v>
       </c>
       <c r="E3" t="str">
         <v>admin2@greenfield.com</v>
@@ -2890,7 +2890,7 @@
         <v>Facility Manager</v>
       </c>
       <c r="D4" t="str">
-        <v>Rajesh Banerjee</v>
+        <v>Suresh Verma</v>
       </c>
       <c r="E4" t="str">
         <v>fm1@greenfield.com</v>
@@ -2925,7 +2925,7 @@
         <v>Facility Manager</v>
       </c>
       <c r="D5" t="str">
-        <v>Aarav Joshi</v>
+        <v>Dev Tiwari</v>
       </c>
       <c r="E5" t="str">
         <v>fm2@greenfield.com</v>
@@ -2960,7 +2960,7 @@
         <v>Security Guard</v>
       </c>
       <c r="D6" t="str">
-        <v>Tanvi Bhat</v>
+        <v>Meera Sinha</v>
       </c>
       <c r="E6" t="str">
         <v>guard1@greenfield.com</v>
@@ -2995,7 +2995,7 @@
         <v>Security Guard</v>
       </c>
       <c r="D7" t="str">
-        <v>Arjun Singh</v>
+        <v>Arjun Jain</v>
       </c>
       <c r="E7" t="str">
         <v>guard2@greenfield.com</v>
@@ -3030,7 +3030,7 @@
         <v>Resident Owner</v>
       </c>
       <c r="D8" t="str">
-        <v>Sanjay Sharma</v>
+        <v>Karan Rao</v>
       </c>
       <c r="E8" t="str">
         <v>owner1@greenfield.com</v>
@@ -3065,7 +3065,7 @@
         <v>Resident Owner</v>
       </c>
       <c r="D9" t="str">
-        <v>Akash Iyer</v>
+        <v>Akash Joshi</v>
       </c>
       <c r="E9" t="str">
         <v>owner2@greenfield.com</v>
@@ -3100,7 +3100,7 @@
         <v>Resident Owner</v>
       </c>
       <c r="D10" t="str">
-        <v>Arjun Desai</v>
+        <v>Siddharth Sharma</v>
       </c>
       <c r="E10" t="str">
         <v>owner3@greenfield.com</v>
@@ -3135,7 +3135,7 @@
         <v>Resident Owner</v>
       </c>
       <c r="D11" t="str">
-        <v>Yamini Bose</v>
+        <v>Ananya Pillai</v>
       </c>
       <c r="E11" t="str">
         <v>owner4@greenfield.com</v>
@@ -3170,7 +3170,7 @@
         <v>Resident Owner</v>
       </c>
       <c r="D12" t="str">
-        <v>Tanvi Iyer</v>
+        <v>Vinay Sharma</v>
       </c>
       <c r="E12" t="str">
         <v>owner5@greenfield.com</v>
@@ -3205,7 +3205,7 @@
         <v>Resident Owner</v>
       </c>
       <c r="D13" t="str">
-        <v>Rekha Mishra</v>
+        <v>Pranav Kapoor</v>
       </c>
       <c r="E13" t="str">
         <v>owner6@greenfield.com</v>
@@ -3240,7 +3240,7 @@
         <v>Resident Owner</v>
       </c>
       <c r="D14" t="str">
-        <v>Ananya Iyer</v>
+        <v>Meera Iyer</v>
       </c>
       <c r="E14" t="str">
         <v>owner7@greenfield.com</v>
@@ -3275,7 +3275,7 @@
         <v>Resident Owner</v>
       </c>
       <c r="D15" t="str">
-        <v>Rahul Verma</v>
+        <v>Seema Menon</v>
       </c>
       <c r="E15" t="str">
         <v>owner8@greenfield.com</v>
@@ -3310,7 +3310,7 @@
         <v>Resident Owner</v>
       </c>
       <c r="D16" t="str">
-        <v>Sanjay Mehta</v>
+        <v>Divya Pandey</v>
       </c>
       <c r="E16" t="str">
         <v>owner9@greenfield.com</v>
@@ -3345,7 +3345,7 @@
         <v>Resident Owner</v>
       </c>
       <c r="D17" t="str">
-        <v>Sahil Rao</v>
+        <v>Vinay Das</v>
       </c>
       <c r="E17" t="str">
         <v>owner10@greenfield.com</v>
@@ -3380,7 +3380,7 @@
         <v>Resident Tenant</v>
       </c>
       <c r="D18" t="str">
-        <v>Om Banerjee</v>
+        <v>Priya Reddy</v>
       </c>
       <c r="E18" t="str">
         <v>tenant1@greenfield.com</v>
@@ -3415,7 +3415,7 @@
         <v>Resident Tenant</v>
       </c>
       <c r="D19" t="str">
-        <v>Aditi Agarwal</v>
+        <v>Priya Mishra</v>
       </c>
       <c r="E19" t="str">
         <v>tenant2@greenfield.com</v>
@@ -3450,7 +3450,7 @@
         <v>Resident Tenant</v>
       </c>
       <c r="D20" t="str">
-        <v>Rajesh Pillai</v>
+        <v>Ananya Pillai</v>
       </c>
       <c r="E20" t="str">
         <v>tenant3@greenfield.com</v>
@@ -3485,7 +3485,7 @@
         <v>Resident Tenant</v>
       </c>
       <c r="D21" t="str">
-        <v>Meera Patel</v>
+        <v>Shreya Chauhan</v>
       </c>
       <c r="E21" t="str">
         <v>tenant4@greenfield.com</v>
@@ -3520,7 +3520,7 @@
         <v>Resident Tenant</v>
       </c>
       <c r="D22" t="str">
-        <v>Vikram Singh</v>
+        <v>Rekha Pandey</v>
       </c>
       <c r="E22" t="str">
         <v>tenant5@greenfield.com</v>
@@ -3555,7 +3555,7 @@
         <v>Resident Tenant</v>
       </c>
       <c r="D23" t="str">
-        <v>Shiv Reddy</v>
+        <v>Priya Mehta</v>
       </c>
       <c r="E23" t="str">
         <v>tenant6@greenfield.com</v>
@@ -3590,7 +3590,7 @@
         <v>Resident Tenant</v>
       </c>
       <c r="D24" t="str">
-        <v>Arjun Verma</v>
+        <v>Manav Jain</v>
       </c>
       <c r="E24" t="str">
         <v>tenant7@greenfield.com</v>
@@ -3625,7 +3625,7 @@
         <v>Resident Tenant</v>
       </c>
       <c r="D25" t="str">
-        <v>Priya Ghosh</v>
+        <v>Sangeeta Pillai</v>
       </c>
       <c r="E25" t="str">
         <v>tenant8@greenfield.com</v>
@@ -3660,7 +3660,7 @@
         <v>Resident Tenant</v>
       </c>
       <c r="D26" t="str">
-        <v>Meera Mehta</v>
+        <v>Nisha Pandey</v>
       </c>
       <c r="E26" t="str">
         <v>tenant9@greenfield.com</v>
@@ -3695,7 +3695,7 @@
         <v>Resident Tenant</v>
       </c>
       <c r="D27" t="str">
-        <v>Jaya Kumar</v>
+        <v>Karan Bhat</v>
       </c>
       <c r="E27" t="str">
         <v>tenant10@greenfield.com</v>
@@ -3730,7 +3730,7 @@
         <v>Family Member</v>
       </c>
       <c r="D28" t="str">
-        <v>Divya Bose</v>
+        <v>Siddharth Mehta</v>
       </c>
       <c r="E28" t="str">
         <v>family1@greenfield.com</v>
@@ -3765,7 +3765,7 @@
         <v>Family Member</v>
       </c>
       <c r="D29" t="str">
-        <v>Ishaan Sharma</v>
+        <v>Tanvi Ghosh</v>
       </c>
       <c r="E29" t="str">
         <v>family2@greenfield.com</v>
@@ -3800,7 +3800,7 @@
         <v>Family Member</v>
       </c>
       <c r="D30" t="str">
-        <v>Zara Verma</v>
+        <v>Pranav Bose</v>
       </c>
       <c r="E30" t="str">
         <v>family3@greenfield.com</v>
@@ -3835,7 +3835,7 @@
         <v>Family Member</v>
       </c>
       <c r="D31" t="str">
-        <v>Chirag Bhat</v>
+        <v>Ananya Verma</v>
       </c>
       <c r="E31" t="str">
         <v>family4@greenfield.com</v>
@@ -3916,7 +3916,7 @@
         <v>Community Admin</v>
       </c>
       <c r="D2" t="str">
-        <v>Karan Pillai</v>
+        <v>Aditi Bose</v>
       </c>
       <c r="E2" t="str">
         <v>admin1@sunrisevalley.com</v>
@@ -3951,7 +3951,7 @@
         <v>Facility Manager</v>
       </c>
       <c r="D3" t="str">
-        <v>Chirag Das</v>
+        <v>Manav Pandey</v>
       </c>
       <c r="E3" t="str">
         <v>fm1@sunrisevalley.com</v>
@@ -3986,7 +3986,7 @@
         <v>Security Guard</v>
       </c>
       <c r="D4" t="str">
-        <v>Chirag Menon</v>
+        <v>Sangeeta Pandey</v>
       </c>
       <c r="E4" t="str">
         <v>guard1@sunrisevalley.com</v>
@@ -4021,7 +4021,7 @@
         <v>Security Guard</v>
       </c>
       <c r="D5" t="str">
-        <v>Vishal Pillai</v>
+        <v>Yamini Agarwal</v>
       </c>
       <c r="E5" t="str">
         <v>guard2@sunrisevalley.com</v>
@@ -4056,7 +4056,7 @@
         <v>Resident Owner</v>
       </c>
       <c r="D6" t="str">
-        <v>Gayatri Ghosh</v>
+        <v>Dev Nair</v>
       </c>
       <c r="E6" t="str">
         <v>owner1@sunrisevalley.com</v>
@@ -4091,7 +4091,7 @@
         <v>Resident Owner</v>
       </c>
       <c r="D7" t="str">
-        <v>Varun Rao</v>
+        <v>Harish Rao</v>
       </c>
       <c r="E7" t="str">
         <v>owner2@sunrisevalley.com</v>
@@ -4126,7 +4126,7 @@
         <v>Resident Owner</v>
       </c>
       <c r="D8" t="str">
-        <v>Neeraj Mishra</v>
+        <v>Ananya Desai</v>
       </c>
       <c r="E8" t="str">
         <v>owner3@sunrisevalley.com</v>
@@ -4161,7 +4161,7 @@
         <v>Resident Owner</v>
       </c>
       <c r="D9" t="str">
-        <v>Manav Banerjee</v>
+        <v>Zara Mehta</v>
       </c>
       <c r="E9" t="str">
         <v>owner4@sunrisevalley.com</v>
@@ -4196,7 +4196,7 @@
         <v>Resident Owner</v>
       </c>
       <c r="D10" t="str">
-        <v>Yamini Iyer</v>
+        <v>Tanvi Joshi</v>
       </c>
       <c r="E10" t="str">
         <v>owner5@sunrisevalley.com</v>
@@ -4231,7 +4231,7 @@
         <v>Resident Owner</v>
       </c>
       <c r="D11" t="str">
-        <v>Manav Desai</v>
+        <v>Gayatri Kapoor</v>
       </c>
       <c r="E11" t="str">
         <v>owner6@sunrisevalley.com</v>
@@ -4266,7 +4266,7 @@
         <v>Resident Owner</v>
       </c>
       <c r="D12" t="str">
-        <v>Chirag Iyer</v>
+        <v>Kavya Bhat</v>
       </c>
       <c r="E12" t="str">
         <v>owner7@sunrisevalley.com</v>
@@ -4301,7 +4301,7 @@
         <v>Resident Tenant</v>
       </c>
       <c r="D13" t="str">
-        <v>Seema Menon</v>
+        <v>Usha Chauhan</v>
       </c>
       <c r="E13" t="str">
         <v>tenant1@sunrisevalley.com</v>
@@ -4336,7 +4336,7 @@
         <v>Resident Tenant</v>
       </c>
       <c r="D14" t="str">
-        <v>Varun Iyer</v>
+        <v>Vinay Chauhan</v>
       </c>
       <c r="E14" t="str">
         <v>tenant2@sunrisevalley.com</v>
@@ -4371,7 +4371,7 @@
         <v>Resident Tenant</v>
       </c>
       <c r="D15" t="str">
-        <v>Sangeeta Joshi</v>
+        <v>Priya Desai</v>
       </c>
       <c r="E15" t="str">
         <v>tenant3@sunrisevalley.com</v>
@@ -4406,7 +4406,7 @@
         <v>Resident Tenant</v>
       </c>
       <c r="D16" t="str">
-        <v>Dev Pillai</v>
+        <v>Vikram Nair</v>
       </c>
       <c r="E16" t="str">
         <v>tenant4@sunrisevalley.com</v>
@@ -4441,7 +4441,7 @@
         <v>Resident Tenant</v>
       </c>
       <c r="D17" t="str">
-        <v>Rajesh Choudhury</v>
+        <v>Usha Iyer</v>
       </c>
       <c r="E17" t="str">
         <v>tenant5@sunrisevalley.com</v>
@@ -4476,7 +4476,7 @@
         <v>Resident Tenant</v>
       </c>
       <c r="D18" t="str">
-        <v>Simran Mehta</v>
+        <v>Shreya Reddy</v>
       </c>
       <c r="E18" t="str">
         <v>tenant6@sunrisevalley.com</v>
@@ -4511,7 +4511,7 @@
         <v>Resident Tenant</v>
       </c>
       <c r="D19" t="str">
-        <v>Yamini Menon</v>
+        <v>Bhavna Agarwal</v>
       </c>
       <c r="E19" t="str">
         <v>tenant7@sunrisevalley.com</v>
@@ -4546,7 +4546,7 @@
         <v>Family Member</v>
       </c>
       <c r="D20" t="str">
-        <v>Sanjay Joshi</v>
+        <v>Rohit Chauhan</v>
       </c>
       <c r="E20" t="str">
         <v>family1@sunrisevalley.com</v>
@@ -4581,7 +4581,7 @@
         <v>Family Member</v>
       </c>
       <c r="D21" t="str">
-        <v>Vishal Bhat</v>
+        <v>Bhavna Patel</v>
       </c>
       <c r="E21" t="str">
         <v>family2@sunrisevalley.com</v>
@@ -4662,7 +4662,7 @@
         <v>Community Admin</v>
       </c>
       <c r="D2" t="str">
-        <v>Lakshmi Ghosh</v>
+        <v>Aditi Rao</v>
       </c>
       <c r="E2" t="str">
         <v>admin1@palmmeadows.com</v>
@@ -4697,7 +4697,7 @@
         <v>Facility Manager</v>
       </c>
       <c r="D3" t="str">
-        <v>Deepa Choudhury</v>
+        <v>Vinay Desai</v>
       </c>
       <c r="E3" t="str">
         <v>fm1@palmmeadows.com</v>
@@ -4732,7 +4732,7 @@
         <v>Security Guard</v>
       </c>
       <c r="D4" t="str">
-        <v>Pooja Das</v>
+        <v>Rajesh Bose</v>
       </c>
       <c r="E4" t="str">
         <v>guard1@palmmeadows.com</v>
@@ -4767,7 +4767,7 @@
         <v>Resident Owner</v>
       </c>
       <c r="D5" t="str">
-        <v>Harish Bhat</v>
+        <v>Meera Nair</v>
       </c>
       <c r="E5" t="str">
         <v>owner1@palmmeadows.com</v>
@@ -4802,7 +4802,7 @@
         <v>Resident Owner</v>
       </c>
       <c r="D6" t="str">
-        <v>Sangeeta Pillai</v>
+        <v>Ananya Patel</v>
       </c>
       <c r="E6" t="str">
         <v>owner2@palmmeadows.com</v>
@@ -4837,7 +4837,7 @@
         <v>Resident Owner</v>
       </c>
       <c r="D7" t="str">
-        <v>Varun Joshi</v>
+        <v>Yamini Bose</v>
       </c>
       <c r="E7" t="str">
         <v>owner3@palmmeadows.com</v>
@@ -4872,7 +4872,7 @@
         <v>Resident Owner</v>
       </c>
       <c r="D8" t="str">
-        <v>Ananya Bhat</v>
+        <v>Farhan Reddy</v>
       </c>
       <c r="E8" t="str">
         <v>owner4@palmmeadows.com</v>
@@ -4907,7 +4907,7 @@
         <v>Resident Owner</v>
       </c>
       <c r="D9" t="str">
-        <v>Pooja Tiwari</v>
+        <v>Farhan Tiwari</v>
       </c>
       <c r="E9" t="str">
         <v>owner5@palmmeadows.com</v>
@@ -4942,7 +4942,7 @@
         <v>Resident Tenant</v>
       </c>
       <c r="D10" t="str">
-        <v>Tanvi Nair</v>
+        <v>Vishal Jain</v>
       </c>
       <c r="E10" t="str">
         <v>tenant1@palmmeadows.com</v>
@@ -4977,7 +4977,7 @@
         <v>Resident Tenant</v>
       </c>
       <c r="D11" t="str">
-        <v>Sneha Bose</v>
+        <v>Karan Iyer</v>
       </c>
       <c r="E11" t="str">
         <v>tenant2@palmmeadows.com</v>
@@ -5012,7 +5012,7 @@
         <v>Resident Tenant</v>
       </c>
       <c r="D12" t="str">
-        <v>Shiv Mehta</v>
+        <v>Siddharth Verma</v>
       </c>
       <c r="E12" t="str">
         <v>tenant3@palmmeadows.com</v>
@@ -5047,7 +5047,7 @@
         <v>Resident Tenant</v>
       </c>
       <c r="D13" t="str">
-        <v>Siddharth Joshi</v>
+        <v>Bhavna Bhat</v>
       </c>
       <c r="E13" t="str">
         <v>tenant4@palmmeadows.com</v>
@@ -5082,7 +5082,7 @@
         <v>Resident Tenant</v>
       </c>
       <c r="D14" t="str">
-        <v>Akash Tiwari</v>
+        <v>Shiv Nair</v>
       </c>
       <c r="E14" t="str">
         <v>tenant5@palmmeadows.com</v>
@@ -5117,7 +5117,7 @@
         <v>Family Member</v>
       </c>
       <c r="D15" t="str">
-        <v>Tushar Desai</v>
+        <v>Arjun Patel</v>
       </c>
       <c r="E15" t="str">
         <v>family1@palmmeadows.com</v>
@@ -5152,7 +5152,7 @@
         <v>Family Member</v>
       </c>
       <c r="D16" t="str">
-        <v>Arjun Mehta</v>
+        <v>Pranav Kumar</v>
       </c>
       <c r="E16" t="str">
         <v>family2@palmmeadows.com</v>
@@ -5541,7 +5541,7 @@
         <v>Seed Execution Timestamp</v>
       </c>
       <c r="B10" t="str">
-        <v>2026-08-20T09:13:54.920Z</v>
+        <v>2026-08-25T04:57:21.969Z</v>
       </c>
     </row>
   </sheetData>

--- a/Community_Testing_Credentials.xlsx
+++ b/Community_Testing_Credentials.xlsx
@@ -467,10 +467,10 @@
         <v>Super Admin</v>
       </c>
       <c r="E2" t="str">
-        <v>admin@managemygate.com</v>
+        <v>admin@enterprise.com</v>
       </c>
       <c r="F2" t="str">
-        <v>password123</v>
+        <v>SuperAdminPwd@123</v>
       </c>
       <c r="G2" t="str">
         <v>superadmin</v>
@@ -499,7 +499,7 @@
         <v>Community Admin</v>
       </c>
       <c r="D3" t="str">
-        <v>Sapna Singh</v>
+        <v>Shiv Joshi</v>
       </c>
       <c r="E3" t="str">
         <v>admin1@greenfield.com</v>
@@ -534,7 +534,7 @@
         <v>Community Admin</v>
       </c>
       <c r="D4" t="str">
-        <v>Shreya Bhat</v>
+        <v>Pranav Rao</v>
       </c>
       <c r="E4" t="str">
         <v>admin2@greenfield.com</v>
@@ -569,7 +569,7 @@
         <v>Facility Manager</v>
       </c>
       <c r="D5" t="str">
-        <v>Suresh Verma</v>
+        <v>Tushar Tiwari</v>
       </c>
       <c r="E5" t="str">
         <v>fm1@greenfield.com</v>
@@ -604,7 +604,7 @@
         <v>Facility Manager</v>
       </c>
       <c r="D6" t="str">
-        <v>Dev Tiwari</v>
+        <v>Seema Banerjee</v>
       </c>
       <c r="E6" t="str">
         <v>fm2@greenfield.com</v>
@@ -639,7 +639,7 @@
         <v>Security Guard</v>
       </c>
       <c r="D7" t="str">
-        <v>Meera Sinha</v>
+        <v>Vinay Agarwal</v>
       </c>
       <c r="E7" t="str">
         <v>guard1@greenfield.com</v>
@@ -674,7 +674,7 @@
         <v>Security Guard</v>
       </c>
       <c r="D8" t="str">
-        <v>Arjun Jain</v>
+        <v>Jaya Sinha</v>
       </c>
       <c r="E8" t="str">
         <v>guard2@greenfield.com</v>
@@ -709,7 +709,7 @@
         <v>Resident Owner</v>
       </c>
       <c r="D9" t="str">
-        <v>Karan Rao</v>
+        <v>Harish Sharma</v>
       </c>
       <c r="E9" t="str">
         <v>owner1@greenfield.com</v>
@@ -744,7 +744,7 @@
         <v>Resident Owner</v>
       </c>
       <c r="D10" t="str">
-        <v>Akash Joshi</v>
+        <v>Harish Ghosh</v>
       </c>
       <c r="E10" t="str">
         <v>owner2@greenfield.com</v>
@@ -779,7 +779,7 @@
         <v>Resident Owner</v>
       </c>
       <c r="D11" t="str">
-        <v>Siddharth Sharma</v>
+        <v>Simran Pandey</v>
       </c>
       <c r="E11" t="str">
         <v>owner3@greenfield.com</v>
@@ -814,7 +814,7 @@
         <v>Resident Owner</v>
       </c>
       <c r="D12" t="str">
-        <v>Ananya Pillai</v>
+        <v>Simran Gupta</v>
       </c>
       <c r="E12" t="str">
         <v>owner4@greenfield.com</v>
@@ -849,7 +849,7 @@
         <v>Resident Owner</v>
       </c>
       <c r="D13" t="str">
-        <v>Vinay Sharma</v>
+        <v>Neeraj Agarwal</v>
       </c>
       <c r="E13" t="str">
         <v>owner5@greenfield.com</v>
@@ -884,7 +884,7 @@
         <v>Resident Owner</v>
       </c>
       <c r="D14" t="str">
-        <v>Pranav Kapoor</v>
+        <v>Aditi Nair</v>
       </c>
       <c r="E14" t="str">
         <v>owner6@greenfield.com</v>
@@ -919,7 +919,7 @@
         <v>Resident Owner</v>
       </c>
       <c r="D15" t="str">
-        <v>Meera Iyer</v>
+        <v>Tushar Agarwal</v>
       </c>
       <c r="E15" t="str">
         <v>owner7@greenfield.com</v>
@@ -954,7 +954,7 @@
         <v>Resident Owner</v>
       </c>
       <c r="D16" t="str">
-        <v>Seema Menon</v>
+        <v>Neeraj Singh</v>
       </c>
       <c r="E16" t="str">
         <v>owner8@greenfield.com</v>
@@ -989,7 +989,7 @@
         <v>Resident Owner</v>
       </c>
       <c r="D17" t="str">
-        <v>Divya Pandey</v>
+        <v>Aditi Agarwal</v>
       </c>
       <c r="E17" t="str">
         <v>owner9@greenfield.com</v>
@@ -1024,7 +1024,7 @@
         <v>Resident Owner</v>
       </c>
       <c r="D18" t="str">
-        <v>Vinay Das</v>
+        <v>Jaya Choudhury</v>
       </c>
       <c r="E18" t="str">
         <v>owner10@greenfield.com</v>
@@ -1059,7 +1059,7 @@
         <v>Resident Tenant</v>
       </c>
       <c r="D19" t="str">
-        <v>Priya Reddy</v>
+        <v>Bhavna Tiwari</v>
       </c>
       <c r="E19" t="str">
         <v>tenant1@greenfield.com</v>
@@ -1094,7 +1094,7 @@
         <v>Resident Tenant</v>
       </c>
       <c r="D20" t="str">
-        <v>Priya Mishra</v>
+        <v>Neeraj Sinha</v>
       </c>
       <c r="E20" t="str">
         <v>tenant2@greenfield.com</v>
@@ -1129,7 +1129,7 @@
         <v>Resident Tenant</v>
       </c>
       <c r="D21" t="str">
-        <v>Ananya Pillai</v>
+        <v>Aditi Verma</v>
       </c>
       <c r="E21" t="str">
         <v>tenant3@greenfield.com</v>
@@ -1164,7 +1164,7 @@
         <v>Resident Tenant</v>
       </c>
       <c r="D22" t="str">
-        <v>Shreya Chauhan</v>
+        <v>Usha Gupta</v>
       </c>
       <c r="E22" t="str">
         <v>tenant4@greenfield.com</v>
@@ -1199,7 +1199,7 @@
         <v>Resident Tenant</v>
       </c>
       <c r="D23" t="str">
-        <v>Rekha Pandey</v>
+        <v>Nisha Pandey</v>
       </c>
       <c r="E23" t="str">
         <v>tenant5@greenfield.com</v>
@@ -1234,7 +1234,7 @@
         <v>Resident Tenant</v>
       </c>
       <c r="D24" t="str">
-        <v>Priya Mehta</v>
+        <v>Siddharth Kumar</v>
       </c>
       <c r="E24" t="str">
         <v>tenant6@greenfield.com</v>
@@ -1269,7 +1269,7 @@
         <v>Resident Tenant</v>
       </c>
       <c r="D25" t="str">
-        <v>Manav Jain</v>
+        <v>Shiv Joshi</v>
       </c>
       <c r="E25" t="str">
         <v>tenant7@greenfield.com</v>
@@ -1304,7 +1304,7 @@
         <v>Resident Tenant</v>
       </c>
       <c r="D26" t="str">
-        <v>Sangeeta Pillai</v>
+        <v>Aditi Kumar</v>
       </c>
       <c r="E26" t="str">
         <v>tenant8@greenfield.com</v>
@@ -1339,7 +1339,7 @@
         <v>Resident Tenant</v>
       </c>
       <c r="D27" t="str">
-        <v>Nisha Pandey</v>
+        <v>Sneha Reddy</v>
       </c>
       <c r="E27" t="str">
         <v>tenant9@greenfield.com</v>
@@ -1374,7 +1374,7 @@
         <v>Resident Tenant</v>
       </c>
       <c r="D28" t="str">
-        <v>Karan Bhat</v>
+        <v>Dev Sinha</v>
       </c>
       <c r="E28" t="str">
         <v>tenant10@greenfield.com</v>
@@ -1409,7 +1409,7 @@
         <v>Family Member</v>
       </c>
       <c r="D29" t="str">
-        <v>Siddharth Mehta</v>
+        <v>Farhan Nair</v>
       </c>
       <c r="E29" t="str">
         <v>family1@greenfield.com</v>
@@ -1444,7 +1444,7 @@
         <v>Family Member</v>
       </c>
       <c r="D30" t="str">
-        <v>Tanvi Ghosh</v>
+        <v>Harish Shah</v>
       </c>
       <c r="E30" t="str">
         <v>family2@greenfield.com</v>
@@ -1479,7 +1479,7 @@
         <v>Family Member</v>
       </c>
       <c r="D31" t="str">
-        <v>Pranav Bose</v>
+        <v>Akash Shah</v>
       </c>
       <c r="E31" t="str">
         <v>family3@greenfield.com</v>
@@ -1514,7 +1514,7 @@
         <v>Family Member</v>
       </c>
       <c r="D32" t="str">
-        <v>Ananya Verma</v>
+        <v>Suresh Choudhury</v>
       </c>
       <c r="E32" t="str">
         <v>family4@greenfield.com</v>
@@ -1549,7 +1549,7 @@
         <v>Community Admin</v>
       </c>
       <c r="D33" t="str">
-        <v>Aditi Bose</v>
+        <v>Gayatri Joshi</v>
       </c>
       <c r="E33" t="str">
         <v>admin1@sunrisevalley.com</v>
@@ -1584,7 +1584,7 @@
         <v>Facility Manager</v>
       </c>
       <c r="D34" t="str">
-        <v>Manav Pandey</v>
+        <v>Vinay Iyer</v>
       </c>
       <c r="E34" t="str">
         <v>fm1@sunrisevalley.com</v>
@@ -1619,7 +1619,7 @@
         <v>Security Guard</v>
       </c>
       <c r="D35" t="str">
-        <v>Sangeeta Pandey</v>
+        <v>Vinay Agarwal</v>
       </c>
       <c r="E35" t="str">
         <v>guard1@sunrisevalley.com</v>
@@ -1654,7 +1654,7 @@
         <v>Security Guard</v>
       </c>
       <c r="D36" t="str">
-        <v>Yamini Agarwal</v>
+        <v>Yamini Kapoor</v>
       </c>
       <c r="E36" t="str">
         <v>guard2@sunrisevalley.com</v>
@@ -1689,7 +1689,7 @@
         <v>Resident Owner</v>
       </c>
       <c r="D37" t="str">
-        <v>Dev Nair</v>
+        <v>Farhan Pandey</v>
       </c>
       <c r="E37" t="str">
         <v>owner1@sunrisevalley.com</v>
@@ -1724,7 +1724,7 @@
         <v>Resident Owner</v>
       </c>
       <c r="D38" t="str">
-        <v>Harish Rao</v>
+        <v>Siddharth Banerjee</v>
       </c>
       <c r="E38" t="str">
         <v>owner2@sunrisevalley.com</v>
@@ -1759,7 +1759,7 @@
         <v>Resident Owner</v>
       </c>
       <c r="D39" t="str">
-        <v>Ananya Desai</v>
+        <v>Rohit Gupta</v>
       </c>
       <c r="E39" t="str">
         <v>owner3@sunrisevalley.com</v>
@@ -1794,7 +1794,7 @@
         <v>Resident Owner</v>
       </c>
       <c r="D40" t="str">
-        <v>Zara Mehta</v>
+        <v>Zara Pillai</v>
       </c>
       <c r="E40" t="str">
         <v>owner4@sunrisevalley.com</v>
@@ -1829,7 +1829,7 @@
         <v>Resident Owner</v>
       </c>
       <c r="D41" t="str">
-        <v>Tanvi Joshi</v>
+        <v>Farhan Reddy</v>
       </c>
       <c r="E41" t="str">
         <v>owner5@sunrisevalley.com</v>
@@ -1864,7 +1864,7 @@
         <v>Resident Owner</v>
       </c>
       <c r="D42" t="str">
-        <v>Gayatri Kapoor</v>
+        <v>Sanjay Gupta</v>
       </c>
       <c r="E42" t="str">
         <v>owner6@sunrisevalley.com</v>
@@ -1899,7 +1899,7 @@
         <v>Resident Owner</v>
       </c>
       <c r="D43" t="str">
-        <v>Kavya Bhat</v>
+        <v>Sneha Ghosh</v>
       </c>
       <c r="E43" t="str">
         <v>owner7@sunrisevalley.com</v>
@@ -1934,7 +1934,7 @@
         <v>Resident Tenant</v>
       </c>
       <c r="D44" t="str">
-        <v>Usha Chauhan</v>
+        <v>Siddharth Jain</v>
       </c>
       <c r="E44" t="str">
         <v>tenant1@sunrisevalley.com</v>
@@ -1969,7 +1969,7 @@
         <v>Resident Tenant</v>
       </c>
       <c r="D45" t="str">
-        <v>Vinay Chauhan</v>
+        <v>Usha Desai</v>
       </c>
       <c r="E45" t="str">
         <v>tenant2@sunrisevalley.com</v>
@@ -2004,7 +2004,7 @@
         <v>Resident Tenant</v>
       </c>
       <c r="D46" t="str">
-        <v>Priya Desai</v>
+        <v>Sanjay Mehta</v>
       </c>
       <c r="E46" t="str">
         <v>tenant3@sunrisevalley.com</v>
@@ -2039,7 +2039,7 @@
         <v>Resident Tenant</v>
       </c>
       <c r="D47" t="str">
-        <v>Vikram Nair</v>
+        <v>Vishal Desai</v>
       </c>
       <c r="E47" t="str">
         <v>tenant4@sunrisevalley.com</v>
@@ -2074,7 +2074,7 @@
         <v>Resident Tenant</v>
       </c>
       <c r="D48" t="str">
-        <v>Usha Iyer</v>
+        <v>Gayatri Kapoor</v>
       </c>
       <c r="E48" t="str">
         <v>tenant5@sunrisevalley.com</v>
@@ -2109,7 +2109,7 @@
         <v>Resident Tenant</v>
       </c>
       <c r="D49" t="str">
-        <v>Shreya Reddy</v>
+        <v>Simran Jain</v>
       </c>
       <c r="E49" t="str">
         <v>tenant6@sunrisevalley.com</v>
@@ -2144,7 +2144,7 @@
         <v>Resident Tenant</v>
       </c>
       <c r="D50" t="str">
-        <v>Bhavna Agarwal</v>
+        <v>Ishaan Iyer</v>
       </c>
       <c r="E50" t="str">
         <v>tenant7@sunrisevalley.com</v>
@@ -2179,7 +2179,7 @@
         <v>Family Member</v>
       </c>
       <c r="D51" t="str">
-        <v>Rohit Chauhan</v>
+        <v>Vishal Desai</v>
       </c>
       <c r="E51" t="str">
         <v>family1@sunrisevalley.com</v>
@@ -2214,7 +2214,7 @@
         <v>Family Member</v>
       </c>
       <c r="D52" t="str">
-        <v>Bhavna Patel</v>
+        <v>Rajesh Iyer</v>
       </c>
       <c r="E52" t="str">
         <v>family2@sunrisevalley.com</v>
@@ -2249,7 +2249,7 @@
         <v>Community Admin</v>
       </c>
       <c r="D53" t="str">
-        <v>Aditi Rao</v>
+        <v>Dev Mishra</v>
       </c>
       <c r="E53" t="str">
         <v>admin1@palmmeadows.com</v>
@@ -2284,7 +2284,7 @@
         <v>Facility Manager</v>
       </c>
       <c r="D54" t="str">
-        <v>Vinay Desai</v>
+        <v>Aditi Bose</v>
       </c>
       <c r="E54" t="str">
         <v>fm1@palmmeadows.com</v>
@@ -2319,7 +2319,7 @@
         <v>Security Guard</v>
       </c>
       <c r="D55" t="str">
-        <v>Rajesh Bose</v>
+        <v>Suresh Rao</v>
       </c>
       <c r="E55" t="str">
         <v>guard1@palmmeadows.com</v>
@@ -2354,7 +2354,7 @@
         <v>Resident Owner</v>
       </c>
       <c r="D56" t="str">
-        <v>Meera Nair</v>
+        <v>Shreya Kumar</v>
       </c>
       <c r="E56" t="str">
         <v>owner1@palmmeadows.com</v>
@@ -2389,7 +2389,7 @@
         <v>Resident Owner</v>
       </c>
       <c r="D57" t="str">
-        <v>Ananya Patel</v>
+        <v>Rajesh Reddy</v>
       </c>
       <c r="E57" t="str">
         <v>owner2@palmmeadows.com</v>
@@ -2424,7 +2424,7 @@
         <v>Resident Owner</v>
       </c>
       <c r="D58" t="str">
-        <v>Yamini Bose</v>
+        <v>Om Sinha</v>
       </c>
       <c r="E58" t="str">
         <v>owner3@palmmeadows.com</v>
@@ -2459,7 +2459,7 @@
         <v>Resident Owner</v>
       </c>
       <c r="D59" t="str">
-        <v>Farhan Reddy</v>
+        <v>Suresh Banerjee</v>
       </c>
       <c r="E59" t="str">
         <v>owner4@palmmeadows.com</v>
@@ -2494,7 +2494,7 @@
         <v>Resident Owner</v>
       </c>
       <c r="D60" t="str">
-        <v>Farhan Tiwari</v>
+        <v>Tanvi Pillai</v>
       </c>
       <c r="E60" t="str">
         <v>owner5@palmmeadows.com</v>
@@ -2529,7 +2529,7 @@
         <v>Resident Tenant</v>
       </c>
       <c r="D61" t="str">
-        <v>Vishal Jain</v>
+        <v>Bhavna Singh</v>
       </c>
       <c r="E61" t="str">
         <v>tenant1@palmmeadows.com</v>
@@ -2564,7 +2564,7 @@
         <v>Resident Tenant</v>
       </c>
       <c r="D62" t="str">
-        <v>Karan Iyer</v>
+        <v>Arjun Mehta</v>
       </c>
       <c r="E62" t="str">
         <v>tenant2@palmmeadows.com</v>
@@ -2599,7 +2599,7 @@
         <v>Resident Tenant</v>
       </c>
       <c r="D63" t="str">
-        <v>Siddharth Verma</v>
+        <v>Pooja Verma</v>
       </c>
       <c r="E63" t="str">
         <v>tenant3@palmmeadows.com</v>
@@ -2634,7 +2634,7 @@
         <v>Resident Tenant</v>
       </c>
       <c r="D64" t="str">
-        <v>Bhavna Bhat</v>
+        <v>Pranav Pandey</v>
       </c>
       <c r="E64" t="str">
         <v>tenant4@palmmeadows.com</v>
@@ -2669,7 +2669,7 @@
         <v>Resident Tenant</v>
       </c>
       <c r="D65" t="str">
-        <v>Shiv Nair</v>
+        <v>Karan Chauhan</v>
       </c>
       <c r="E65" t="str">
         <v>tenant5@palmmeadows.com</v>
@@ -2704,7 +2704,7 @@
         <v>Family Member</v>
       </c>
       <c r="D66" t="str">
-        <v>Arjun Patel</v>
+        <v>Dev Banerjee</v>
       </c>
       <c r="E66" t="str">
         <v>family1@palmmeadows.com</v>
@@ -2739,7 +2739,7 @@
         <v>Family Member</v>
       </c>
       <c r="D67" t="str">
-        <v>Pranav Kumar</v>
+        <v>Seema Rao</v>
       </c>
       <c r="E67" t="str">
         <v>family2@palmmeadows.com</v>
@@ -2820,7 +2820,7 @@
         <v>Community Admin</v>
       </c>
       <c r="D2" t="str">
-        <v>Sapna Singh</v>
+        <v>Shiv Joshi</v>
       </c>
       <c r="E2" t="str">
         <v>admin1@greenfield.com</v>
@@ -2855,7 +2855,7 @@
         <v>Community Admin</v>
       </c>
       <c r="D3" t="str">
-        <v>Shreya Bhat</v>
+        <v>Pranav Rao</v>
       </c>
       <c r="E3" t="str">
         <v>admin2@greenfield.com</v>
@@ -2890,7 +2890,7 @@
         <v>Facility Manager</v>
       </c>
       <c r="D4" t="str">
-        <v>Suresh Verma</v>
+        <v>Tushar Tiwari</v>
       </c>
       <c r="E4" t="str">
         <v>fm1@greenfield.com</v>
@@ -2925,7 +2925,7 @@
         <v>Facility Manager</v>
       </c>
       <c r="D5" t="str">
-        <v>Dev Tiwari</v>
+        <v>Seema Banerjee</v>
       </c>
       <c r="E5" t="str">
         <v>fm2@greenfield.com</v>
@@ -2960,7 +2960,7 @@
         <v>Security Guard</v>
       </c>
       <c r="D6" t="str">
-        <v>Meera Sinha</v>
+        <v>Vinay Agarwal</v>
       </c>
       <c r="E6" t="str">
         <v>guard1@greenfield.com</v>
@@ -2995,7 +2995,7 @@
         <v>Security Guard</v>
       </c>
       <c r="D7" t="str">
-        <v>Arjun Jain</v>
+        <v>Jaya Sinha</v>
       </c>
       <c r="E7" t="str">
         <v>guard2@greenfield.com</v>
@@ -3030,7 +3030,7 @@
         <v>Resident Owner</v>
       </c>
       <c r="D8" t="str">
-        <v>Karan Rao</v>
+        <v>Harish Sharma</v>
       </c>
       <c r="E8" t="str">
         <v>owner1@greenfield.com</v>
@@ -3065,7 +3065,7 @@
         <v>Resident Owner</v>
       </c>
       <c r="D9" t="str">
-        <v>Akash Joshi</v>
+        <v>Harish Ghosh</v>
       </c>
       <c r="E9" t="str">
         <v>owner2@greenfield.com</v>
@@ -3100,7 +3100,7 @@
         <v>Resident Owner</v>
       </c>
       <c r="D10" t="str">
-        <v>Siddharth Sharma</v>
+        <v>Simran Pandey</v>
       </c>
       <c r="E10" t="str">
         <v>owner3@greenfield.com</v>
@@ -3135,7 +3135,7 @@
         <v>Resident Owner</v>
       </c>
       <c r="D11" t="str">
-        <v>Ananya Pillai</v>
+        <v>Simran Gupta</v>
       </c>
       <c r="E11" t="str">
         <v>owner4@greenfield.com</v>
@@ -3170,7 +3170,7 @@
         <v>Resident Owner</v>
       </c>
       <c r="D12" t="str">
-        <v>Vinay Sharma</v>
+        <v>Neeraj Agarwal</v>
       </c>
       <c r="E12" t="str">
         <v>owner5@greenfield.com</v>
@@ -3205,7 +3205,7 @@
         <v>Resident Owner</v>
       </c>
       <c r="D13" t="str">
-        <v>Pranav Kapoor</v>
+        <v>Aditi Nair</v>
       </c>
       <c r="E13" t="str">
         <v>owner6@greenfield.com</v>
@@ -3240,7 +3240,7 @@
         <v>Resident Owner</v>
       </c>
       <c r="D14" t="str">
-        <v>Meera Iyer</v>
+        <v>Tushar Agarwal</v>
       </c>
       <c r="E14" t="str">
         <v>owner7@greenfield.com</v>
@@ -3275,7 +3275,7 @@
         <v>Resident Owner</v>
       </c>
       <c r="D15" t="str">
-        <v>Seema Menon</v>
+        <v>Neeraj Singh</v>
       </c>
       <c r="E15" t="str">
         <v>owner8@greenfield.com</v>
@@ -3310,7 +3310,7 @@
         <v>Resident Owner</v>
       </c>
       <c r="D16" t="str">
-        <v>Divya Pandey</v>
+        <v>Aditi Agarwal</v>
       </c>
       <c r="E16" t="str">
         <v>owner9@greenfield.com</v>
@@ -3345,7 +3345,7 @@
         <v>Resident Owner</v>
       </c>
       <c r="D17" t="str">
-        <v>Vinay Das</v>
+        <v>Jaya Choudhury</v>
       </c>
       <c r="E17" t="str">
         <v>owner10@greenfield.com</v>
@@ -3380,7 +3380,7 @@
         <v>Resident Tenant</v>
       </c>
       <c r="D18" t="str">
-        <v>Priya Reddy</v>
+        <v>Bhavna Tiwari</v>
       </c>
       <c r="E18" t="str">
         <v>tenant1@greenfield.com</v>
@@ -3415,7 +3415,7 @@
         <v>Resident Tenant</v>
       </c>
       <c r="D19" t="str">
-        <v>Priya Mishra</v>
+        <v>Neeraj Sinha</v>
       </c>
       <c r="E19" t="str">
         <v>tenant2@greenfield.com</v>
@@ -3450,7 +3450,7 @@
         <v>Resident Tenant</v>
       </c>
       <c r="D20" t="str">
-        <v>Ananya Pillai</v>
+        <v>Aditi Verma</v>
       </c>
       <c r="E20" t="str">
         <v>tenant3@greenfield.com</v>
@@ -3485,7 +3485,7 @@
         <v>Resident Tenant</v>
       </c>
       <c r="D21" t="str">
-        <v>Shreya Chauhan</v>
+        <v>Usha Gupta</v>
       </c>
       <c r="E21" t="str">
         <v>tenant4@greenfield.com</v>
@@ -3520,7 +3520,7 @@
         <v>Resident Tenant</v>
       </c>
       <c r="D22" t="str">
-        <v>Rekha Pandey</v>
+        <v>Nisha Pandey</v>
       </c>
       <c r="E22" t="str">
         <v>tenant5@greenfield.com</v>
@@ -3555,7 +3555,7 @@
         <v>Resident Tenant</v>
       </c>
       <c r="D23" t="str">
-        <v>Priya Mehta</v>
+        <v>Siddharth Kumar</v>
       </c>
       <c r="E23" t="str">
         <v>tenant6@greenfield.com</v>
@@ -3590,7 +3590,7 @@
         <v>Resident Tenant</v>
       </c>
       <c r="D24" t="str">
-        <v>Manav Jain</v>
+        <v>Shiv Joshi</v>
       </c>
       <c r="E24" t="str">
         <v>tenant7@greenfield.com</v>
@@ -3625,7 +3625,7 @@
         <v>Resident Tenant</v>
       </c>
       <c r="D25" t="str">
-        <v>Sangeeta Pillai</v>
+        <v>Aditi Kumar</v>
       </c>
       <c r="E25" t="str">
         <v>tenant8@greenfield.com</v>
@@ -3660,7 +3660,7 @@
         <v>Resident Tenant</v>
       </c>
       <c r="D26" t="str">
-        <v>Nisha Pandey</v>
+        <v>Sneha Reddy</v>
       </c>
       <c r="E26" t="str">
         <v>tenant9@greenfield.com</v>
@@ -3695,7 +3695,7 @@
         <v>Resident Tenant</v>
       </c>
       <c r="D27" t="str">
-        <v>Karan Bhat</v>
+        <v>Dev Sinha</v>
       </c>
       <c r="E27" t="str">
         <v>tenant10@greenfield.com</v>
@@ -3730,7 +3730,7 @@
         <v>Family Member</v>
       </c>
       <c r="D28" t="str">
-        <v>Siddharth Mehta</v>
+        <v>Farhan Nair</v>
       </c>
       <c r="E28" t="str">
         <v>family1@greenfield.com</v>
@@ -3765,7 +3765,7 @@
         <v>Family Member</v>
       </c>
       <c r="D29" t="str">
-        <v>Tanvi Ghosh</v>
+        <v>Harish Shah</v>
       </c>
       <c r="E29" t="str">
         <v>family2@greenfield.com</v>
@@ -3800,7 +3800,7 @@
         <v>Family Member</v>
       </c>
       <c r="D30" t="str">
-        <v>Pranav Bose</v>
+        <v>Akash Shah</v>
       </c>
       <c r="E30" t="str">
         <v>family3@greenfield.com</v>
@@ -3835,7 +3835,7 @@
         <v>Family Member</v>
       </c>
       <c r="D31" t="str">
-        <v>Ananya Verma</v>
+        <v>Suresh Choudhury</v>
       </c>
       <c r="E31" t="str">
         <v>family4@greenfield.com</v>
@@ -3916,7 +3916,7 @@
         <v>Community Admin</v>
       </c>
       <c r="D2" t="str">
-        <v>Aditi Bose</v>
+        <v>Gayatri Joshi</v>
       </c>
       <c r="E2" t="str">
         <v>admin1@sunrisevalley.com</v>
@@ -3951,7 +3951,7 @@
         <v>Facility Manager</v>
       </c>
       <c r="D3" t="str">
-        <v>Manav Pandey</v>
+        <v>Vinay Iyer</v>
       </c>
       <c r="E3" t="str">
         <v>fm1@sunrisevalley.com</v>
@@ -3986,7 +3986,7 @@
         <v>Security Guard</v>
       </c>
       <c r="D4" t="str">
-        <v>Sangeeta Pandey</v>
+        <v>Vinay Agarwal</v>
       </c>
       <c r="E4" t="str">
         <v>guard1@sunrisevalley.com</v>
@@ -4021,7 +4021,7 @@
         <v>Security Guard</v>
       </c>
       <c r="D5" t="str">
-        <v>Yamini Agarwal</v>
+        <v>Yamini Kapoor</v>
       </c>
       <c r="E5" t="str">
         <v>guard2@sunrisevalley.com</v>
@@ -4056,7 +4056,7 @@
         <v>Resident Owner</v>
       </c>
       <c r="D6" t="str">
-        <v>Dev Nair</v>
+        <v>Farhan Pandey</v>
       </c>
       <c r="E6" t="str">
         <v>owner1@sunrisevalley.com</v>
@@ -4091,7 +4091,7 @@
         <v>Resident Owner</v>
       </c>
       <c r="D7" t="str">
-        <v>Harish Rao</v>
+        <v>Siddharth Banerjee</v>
       </c>
       <c r="E7" t="str">
         <v>owner2@sunrisevalley.com</v>
@@ -4126,7 +4126,7 @@
         <v>Resident Owner</v>
       </c>
       <c r="D8" t="str">
-        <v>Ananya Desai</v>
+        <v>Rohit Gupta</v>
       </c>
       <c r="E8" t="str">
         <v>owner3@sunrisevalley.com</v>
@@ -4161,7 +4161,7 @@
         <v>Resident Owner</v>
       </c>
       <c r="D9" t="str">
-        <v>Zara Mehta</v>
+        <v>Zara Pillai</v>
       </c>
       <c r="E9" t="str">
         <v>owner4@sunrisevalley.com</v>
@@ -4196,7 +4196,7 @@
         <v>Resident Owner</v>
       </c>
       <c r="D10" t="str">
-        <v>Tanvi Joshi</v>
+        <v>Farhan Reddy</v>
       </c>
       <c r="E10" t="str">
         <v>owner5@sunrisevalley.com</v>
@@ -4231,7 +4231,7 @@
         <v>Resident Owner</v>
       </c>
       <c r="D11" t="str">
-        <v>Gayatri Kapoor</v>
+        <v>Sanjay Gupta</v>
       </c>
       <c r="E11" t="str">
         <v>owner6@sunrisevalley.com</v>
@@ -4266,7 +4266,7 @@
         <v>Resident Owner</v>
       </c>
       <c r="D12" t="str">
-        <v>Kavya Bhat</v>
+        <v>Sneha Ghosh</v>
       </c>
       <c r="E12" t="str">
         <v>owner7@sunrisevalley.com</v>
@@ -4301,7 +4301,7 @@
         <v>Resident Tenant</v>
       </c>
       <c r="D13" t="str">
-        <v>Usha Chauhan</v>
+        <v>Siddharth Jain</v>
       </c>
       <c r="E13" t="str">
         <v>tenant1@sunrisevalley.com</v>
@@ -4336,7 +4336,7 @@
         <v>Resident Tenant</v>
       </c>
       <c r="D14" t="str">
-        <v>Vinay Chauhan</v>
+        <v>Usha Desai</v>
       </c>
       <c r="E14" t="str">
         <v>tenant2@sunrisevalley.com</v>
@@ -4371,7 +4371,7 @@
         <v>Resident Tenant</v>
       </c>
       <c r="D15" t="str">
-        <v>Priya Desai</v>
+        <v>Sanjay Mehta</v>
       </c>
       <c r="E15" t="str">
         <v>tenant3@sunrisevalley.com</v>
@@ -4406,7 +4406,7 @@
         <v>Resident Tenant</v>
       </c>
       <c r="D16" t="str">
-        <v>Vikram Nair</v>
+        <v>Vishal Desai</v>
       </c>
       <c r="E16" t="str">
         <v>tenant4@sunrisevalley.com</v>
@@ -4441,7 +4441,7 @@
         <v>Resident Tenant</v>
       </c>
       <c r="D17" t="str">
-        <v>Usha Iyer</v>
+        <v>Gayatri Kapoor</v>
       </c>
       <c r="E17" t="str">
         <v>tenant5@sunrisevalley.com</v>
@@ -4476,7 +4476,7 @@
         <v>Resident Tenant</v>
       </c>
       <c r="D18" t="str">
-        <v>Shreya Reddy</v>
+        <v>Simran Jain</v>
       </c>
       <c r="E18" t="str">
         <v>tenant6@sunrisevalley.com</v>
@@ -4511,7 +4511,7 @@
         <v>Resident Tenant</v>
       </c>
       <c r="D19" t="str">
-        <v>Bhavna Agarwal</v>
+        <v>Ishaan Iyer</v>
       </c>
       <c r="E19" t="str">
         <v>tenant7@sunrisevalley.com</v>
@@ -4546,7 +4546,7 @@
         <v>Family Member</v>
       </c>
       <c r="D20" t="str">
-        <v>Rohit Chauhan</v>
+        <v>Vishal Desai</v>
       </c>
       <c r="E20" t="str">
         <v>family1@sunrisevalley.com</v>
@@ -4581,7 +4581,7 @@
         <v>Family Member</v>
       </c>
       <c r="D21" t="str">
-        <v>Bhavna Patel</v>
+        <v>Rajesh Iyer</v>
       </c>
       <c r="E21" t="str">
         <v>family2@sunrisevalley.com</v>
@@ -4662,7 +4662,7 @@
         <v>Community Admin</v>
       </c>
       <c r="D2" t="str">
-        <v>Aditi Rao</v>
+        <v>Dev Mishra</v>
       </c>
       <c r="E2" t="str">
         <v>admin1@palmmeadows.com</v>
@@ -4697,7 +4697,7 @@
         <v>Facility Manager</v>
       </c>
       <c r="D3" t="str">
-        <v>Vinay Desai</v>
+        <v>Aditi Bose</v>
       </c>
       <c r="E3" t="str">
         <v>fm1@palmmeadows.com</v>
@@ -4732,7 +4732,7 @@
         <v>Security Guard</v>
       </c>
       <c r="D4" t="str">
-        <v>Rajesh Bose</v>
+        <v>Suresh Rao</v>
       </c>
       <c r="E4" t="str">
         <v>guard1@palmmeadows.com</v>
@@ -4767,7 +4767,7 @@
         <v>Resident Owner</v>
       </c>
       <c r="D5" t="str">
-        <v>Meera Nair</v>
+        <v>Shreya Kumar</v>
       </c>
       <c r="E5" t="str">
         <v>owner1@palmmeadows.com</v>
@@ -4802,7 +4802,7 @@
         <v>Resident Owner</v>
       </c>
       <c r="D6" t="str">
-        <v>Ananya Patel</v>
+        <v>Rajesh Reddy</v>
       </c>
       <c r="E6" t="str">
         <v>owner2@palmmeadows.com</v>
@@ -4837,7 +4837,7 @@
         <v>Resident Owner</v>
       </c>
       <c r="D7" t="str">
-        <v>Yamini Bose</v>
+        <v>Om Sinha</v>
       </c>
       <c r="E7" t="str">
         <v>owner3@palmmeadows.com</v>
@@ -4872,7 +4872,7 @@
         <v>Resident Owner</v>
       </c>
       <c r="D8" t="str">
-        <v>Farhan Reddy</v>
+        <v>Suresh Banerjee</v>
       </c>
       <c r="E8" t="str">
         <v>owner4@palmmeadows.com</v>
@@ -4907,7 +4907,7 @@
         <v>Resident Owner</v>
       </c>
       <c r="D9" t="str">
-        <v>Farhan Tiwari</v>
+        <v>Tanvi Pillai</v>
       </c>
       <c r="E9" t="str">
         <v>owner5@palmmeadows.com</v>
@@ -4942,7 +4942,7 @@
         <v>Resident Tenant</v>
       </c>
       <c r="D10" t="str">
-        <v>Vishal Jain</v>
+        <v>Bhavna Singh</v>
       </c>
       <c r="E10" t="str">
         <v>tenant1@palmmeadows.com</v>
@@ -4977,7 +4977,7 @@
         <v>Resident Tenant</v>
       </c>
       <c r="D11" t="str">
-        <v>Karan Iyer</v>
+        <v>Arjun Mehta</v>
       </c>
       <c r="E11" t="str">
         <v>tenant2@palmmeadows.com</v>
@@ -5012,7 +5012,7 @@
         <v>Resident Tenant</v>
       </c>
       <c r="D12" t="str">
-        <v>Siddharth Verma</v>
+        <v>Pooja Verma</v>
       </c>
       <c r="E12" t="str">
         <v>tenant3@palmmeadows.com</v>
@@ -5047,7 +5047,7 @@
         <v>Resident Tenant</v>
       </c>
       <c r="D13" t="str">
-        <v>Bhavna Bhat</v>
+        <v>Pranav Pandey</v>
       </c>
       <c r="E13" t="str">
         <v>tenant4@palmmeadows.com</v>
@@ -5082,7 +5082,7 @@
         <v>Resident Tenant</v>
       </c>
       <c r="D14" t="str">
-        <v>Shiv Nair</v>
+        <v>Karan Chauhan</v>
       </c>
       <c r="E14" t="str">
         <v>tenant5@palmmeadows.com</v>
@@ -5117,7 +5117,7 @@
         <v>Family Member</v>
       </c>
       <c r="D15" t="str">
-        <v>Arjun Patel</v>
+        <v>Dev Banerjee</v>
       </c>
       <c r="E15" t="str">
         <v>family1@palmmeadows.com</v>
@@ -5152,7 +5152,7 @@
         <v>Family Member</v>
       </c>
       <c r="D16" t="str">
-        <v>Pranav Kumar</v>
+        <v>Seema Rao</v>
       </c>
       <c r="E16" t="str">
         <v>family2@palmmeadows.com</v>
@@ -5322,7 +5322,7 @@
         <v>Platform Multi-Community Switch</v>
       </c>
       <c r="D2" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Login with admin@managemygate.com / password123.
+        <v xml:space="preserve">1. Login with admin@enterprise.com / SuperAdminPwd@123.
 2. Open workspace dropdown in header.
 3. Verify all 3 communities (Greenfield Heights, Sunrise Valley, Palm Meadows) are listed.
 4. Switch workspace and verify context changes.</v>
@@ -5517,7 +5517,7 @@
         <v>Super Admin Account</v>
       </c>
       <c r="B7" t="str">
-        <v>admin@managemygate.com (Password: password123)</v>
+        <v>admin@enterprise.com (Password: SuperAdminPwd@123)</v>
       </c>
     </row>
     <row r="8">
@@ -5541,7 +5541,7 @@
         <v>Seed Execution Timestamp</v>
       </c>
       <c r="B10" t="str">
-        <v>2026-08-25T04:57:21.969Z</v>
+        <v>2026-08-31T11:04:51.348Z</v>
       </c>
     </row>
   </sheetData>
